--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -1489,7 +1489,7 @@
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Create Purchase Orders is set to OFF (see SF-SET-03).
+2. Create Purchase Orders is set to OFF.
 3. An open work order with an approved vendor-part line exists.</t>
         </is>
       </c>
@@ -7682,7 +7682,7 @@
       <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Create Purchase Orders is OFF (see SF-SET-03).
+2. Create Purchase Orders is OFF.
 3. A work order with a vendor/found part exists.</t>
         </is>
       </c>

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J157"/>
+  <dimension ref="A1:J160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1003,21 +1003,22 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1. A non-admin user account exists for this org.
-2. You can sign in as that non-admin user.</t>
+          <t>1. A user without the App Settings permission (e.g. Service Advisor or Technician) exists for this org.
+2. You can sign in as that user.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Sign in as the non-admin user.
+          <t>1. Sign in as the user without App Settings.
 2. Attempt to open /administration/settings → Work Orders tab.
-3. Attempt to change and save a Work Order setting.</t>
+3. Attempt to change and save a Work Order setting, including a direct API save.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. The non-admin cannot reach the Work Order settings, OR the settings are read-only for them.
-2. The non-admin cannot save changes to Work Order settings.</t>
+          <t>1. A role without the App Settings permission cannot reach the Work Order settings, or sees them read-only.
+2. That role cannot save changes to Work Order settings.
+3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -3259,7 +3260,8 @@
         <is>
           <t>1. The part saves successfully.
 2. The part appears on the line with its description, quantity and sell price.
-3. It is treated as a vendorless part downstream.</t>
+3. It is treated as a vendorless part downstream.
+4. Adding a vendorless / no-part-number part requires WO Lines: Create &amp; Edit and See Financial Data, because the sell price is mandatory and has no catalog source.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3301,14 +3303,16 @@
         <is>
           <t>1. Leave the description empty and try to save.
 2. Fill description, leave quantity empty and try to save.
-3. Fill quantity, leave sell price empty and try to save.</t>
+3. Fill quantity, leave sell price empty and try to save.
+4. As a role without See Financial Data (e.g. Technician), attempt to add a vendorless / no-part-number part.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. Saving is blocked when the description is empty.
 2. Saving is blocked when the quantity is empty.
-3. Saving is blocked when the sell price is empty.</t>
+3. Saving is blocked when the sell price is empty.
+4. A user without See Financial Data (for example a Technician) cannot add a vendorless / no-part-number part, because they cannot enter the mandatory sell price.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -5167,20 +5171,20 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>1. An office / readonly user credential exists.
+          <t>1. An Office / read-only user credential (no Order Parts) exists.
 2. A fulfilled PO and an unfulfilled PO exist.</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>1. Sign in as an office/readonly user and open the PO list.
+          <t>1. Sign in as an Office / read-only user and open the PO list.
 2. Confirm the Receive action is hidden for them.
 3. As an authorized user, confirm the Receive action is hidden on a fulfilled PO.</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1. Office and readonly users do not see the Receive action, per the Story 11 behavior.
+          <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or detail.
 2. Fulfilled POs do not show the Receive action.</t>
         </is>
       </c>
@@ -6248,7 +6252,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is available only to manager/foreman and disabled for an advisor with 'Awaiting review'</t>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -6268,21 +6272,22 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>1. Manager/foreman and advisor credentials exist.
-2. A work order is in Review state.</t>
+          <t>1. A role with Review Work Orders and a role without it both exist.
+2. A work order is in Review state, sent to review by a known user.</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>1. Sign in as an advisor and open the work order in Review.
+          <t>1. Sign in as a role without Review Work Orders and open the work order in Review.
 2. Confirm Mark Reviewed is disabled with 'Awaiting review'.
-3. Sign in as a manager/foreman and confirm Mark Reviewed is available.</t>
+3. Sign in as a role with Review Work Orders (system defaults grant it broadly; it can be limited to manager/foreman via custom roles) and confirm Mark Reviewed is available.</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1. An advisor sees Mark Reviewed disabled with an 'Awaiting review' indicator.
-2. A manager or foreman can Mark Reviewed and sign off, per the Story 16 review sign-off behavior.</t>
+          <t>1. A role without the Review Work Orders permission sees Mark Reviewed disabled with an 'Awaiting review' indicator.
+2. A role with the Review Work Orders permission can Mark Reviewed and sign off.
+3. The user who completed / sent the work order to review cannot Mark Reviewed even with the permission; a different qualified reviewer can.</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6789,19 +6794,22 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>1. A non-admin user account exists.
-2. You can sign in as that user.</t>
+          <t>1. A role with the App Settings permission (e.g. Admin) and a role without it (e.g. Service Advisor or Technician) both exist.
+2. You can sign in as each.</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>1. Sign in as the non-admin user.
-2. Attempt to open and modify /administration/settings → Work Orders.</t>
+          <t>1. Sign in as a role with App Settings and open and modify /administration/settings → Work Orders.
+2. Sign in as a role without App Settings and attempt to open and modify the same page.
+3. As the role without App Settings, attempt to save a Work Order settings change directly (API), and note the response.</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>1. The non-admin user cannot open or modify the Work Order settings; the settings area is not available to them.</t>
+          <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can view and modify the Work Order settings page.
+2. A role without App Settings cannot open or change the Work Order settings.
+3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -6847,7 +6855,9 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>1. A user who can edit and complete work orders can perform Simple completion; completion uses the same access as standard work-order completion. Record the result for each role tested.</t>
+          <t>1. Roles with Work Orders: Create &amp; Edit plus WO Lines: Create &amp; Edit and Full View (needed to approve all lines) can complete a work order: Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
+2. Technician and Parts Tech cannot complete (Technician cannot approve lines in Tech View and/or lacks Work Orders: Create &amp; Edit; Parts Tech is a receiver, not a completer).
+3. Office, Sales Rep and Time Clock cannot complete a work order.</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -6893,7 +6903,9 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>1. A user who can receive purchase orders can reach and use Bulk Receive; it uses the same access as the existing Receive action on purchase orders. Record the result for each role tested.</t>
+          <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
+2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot receive.
+3. Sales Rep and Time Clock cannot reach Bulk Receive.</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -6927,8 +6939,8 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>1. Credentials for manager/foreman and other roles exist.
-2. A work order in Review state exists.</t>
+          <t>1. Credentials for roles with and without Review Work Orders exist.
+2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -6939,7 +6951,9 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>1. Mark Reviewed (review sign-off) is available to managers and foremen per the Story 16 behavior; other roles see it disabled with an 'Awaiting review' indicator. Record the result for each role tested.</t>
+          <t>1. Mark Reviewed (review sign-off) requires the Review Work Orders permission; system defaults grant it broadly, and it can be narrowed to manager/foreman via custom roles.
+2. A role without Review Work Orders sees Mark Reviewed disabled with an 'Awaiting review' indicator.
+3. The user who completed / sent the work order to review cannot Mark Reviewed it; a different user who holds Review Work Orders can sign off.</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -6973,20 +6987,21 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>1. An office/readonly credential exists.
-2. A WO-originated PO exists.</t>
+          <t>1. An Office / read-only credential (no Order Parts) exists.
+2. A WO-originated PO exists, plus a fulfilled PO.</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>1. Sign in as an office/readonly user.
+          <t>1. Sign in as an Office / read-only user.
 2. Open the PO list and detail.
-3. Confirm the Receive action is not shown.</t>
+3. Confirm the Receive action is not shown, and confirm it is also absent on a fulfilled PO.</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>1. Office and readonly users do not see the PO Receive action, per the Story 11 behavior.</t>
+          <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or PO detail.
+2. Receive is also hidden for fulfilled (already-received) POs.</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7000,7 +7015,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Verify whether the backend enforces the Simple-Flow settings or they are front-end display gates only</t>
+          <t>Verify the backend enforces the Simple-Flow settings and permission atoms (not front-end only)</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -7026,13 +7041,16 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>1. Attempt the gated action directly via the API (bypassing the UI), e.g. completing without the required invoice.
-2. Observe whether the backend rejects (403/422) or allows it (200/201).</t>
+          <t>1. Attempt a setting-violating action directly via the API (bypassing the UI), e.g. completing without the required invoice, and note the response.
+2. As a role that lacks the mapped atom, attempt the gated action via the API and note the response.
+3. As a role that has only Work Orders: Create &amp; Edit, attempt to receive onto a work order and note the response.</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>1. The API response is recorded: a rejection (403/422) shows the backend enforces the setting; a success (200/201) shows the gate is front-end only.</t>
+          <t>1. The backend enforces the Simple-Flow settings and the permission atoms (it is not front-end only): a setting-violating or unauthorized request is rejected.
+2. Because several work-order atoms collapse to the same backend role pair, any role with Work Orders: Create &amp; Edit can receive onto a work order.
+3. The receive endpoint accepts the documented OR of ROLE_DELIVERY_CREATE_AND_EDIT, ROLE_WORK_ORDER_PART_CREATE and ROLE_WORK_ORDER_CREATE_AND_EDIT.</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7046,7 +7064,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Verify whether review role-gating uses custom roles or is open for v1</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -7066,19 +7084,20 @@
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>1. Credentials for several roles exist.
-2. A work order in Review state exists.</t>
+          <t>1. Credentials for roles with and without Review Work Orders exist.
+2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>1. Determine which roles can sign off review.
-2. Determine whether this is governed by a custom-role permission or open to all.</t>
+          <t>1. Confirm that only roles holding Review Work Orders can sign off, and roles without it cannot.
+2. Confirm the user who completed / sent the work order to review cannot sign it off.</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>1. The set of roles that can sign off review is recorded, along with whether sign-off is governed by a role permission or available to all users.</t>
+          <t>1. Review sign-off is governed by the Review Work Orders custom-role permission (it is NOT open to all users for v1).
+2. The permission gates the Mark Reviewed action, and the reviewer-not-completer rule is enforced (the completer cannot sign off).</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7092,901 +7111,1048 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>1. Two different users who both hold the Review Work Orders permission exist.
+2. User A has completed / sent a work order to review; it is in Review state.</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign in as User A (who sent the work order to review) and open the work order in Review.
+2. Attempt to Mark Reviewed.
+3. Sign in as User B (a different user who holds Review Work Orders) and Mark Reviewed.</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>1. User A cannot Mark Reviewed the work order they completed / sent to review; the action is blocked or disabled.
+2. User B, a different user who holds the Review Work Orders permission, can Mark Reviewed and sign off.
+3. The reviewer must be a different person from the completer.</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (R7 (reviewer != completer))</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>1. A Technician credential exists (WO Lines: Create &amp; Edit, no See Financial Data).
+2. An open work order with a line is available.</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign in as the Technician and open the work order line.
+2. Attempt to add a vendorless / no-part-number part (description + quantity + sell price).</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>1. The Technician cannot add a vendorless / no-part-number part.
+2. The mandatory sell price cannot be entered without See Financial Data, so the add is prevented.</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>SV-7700 (S5 / §9 (See Financial Data gate))</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>1. Credentials for each system role exist (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Technician, Parts Manager, Parts Tech, Office, Sales Rep, Time Clock).
+2. A work order ready to complete is available.</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>1. For each role, open the work order and check whether the Complete Work Order action is available and usable.
+2. Record the result per role against the checklist below.
+3. Roles expected to be able to complete: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager.
+4. Roles expected NOT to be able to complete: Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>1. Complete Work Order is available for Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
+2. Complete Work Order is NOT available for Technician, Parts Tech, Office, Sales Rep or Time Clock.
+3. Technician and Parts Tech are blocked because they cannot approve lines and/or lack Work Orders: Create &amp; Edit; Office is view-only; Sales Rep and Time Clock have no work-order edit access.</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>§9 per-role completion matrix</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage is ON and the work order has no mileage.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave mileage empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until mileage is entered.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>SV-7697, SV-7698, SV-7699 (S2-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. VIN is required for this org's completion and the work order has no VIN.
 3. Require Review is OFF (VIN is collected at completion in the non-review flow).</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave VIN empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until the VIN is entered.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7710 (S15-R2 / S3-R3)</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Engine Hours is ON and the work order has no engine hours.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave engine hours empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until engine hours are entered.</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open on a line.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Leave the story textarea empty.
 2. Check the Next/Continue button.
 3. Type any text and check again.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. With the textarea empty, Next/Continue is disabled.
 2. After typing text, Next/Continue becomes enabled.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R4)</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is ON and a part is being received.</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. On the receive surface, leave the vendor invoice number empty.
 2. Attempt to receive.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor invoice number.
 2. Once an invoice number is entered, receiving is allowed.</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R5 / §4)</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing part is on a receive surface.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to receive with no vendor.
 2. Attempt to receive with a vendor but no part number.
 3. Provide both and receive.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor.
 2. Receiving is blocked without a part number.
 3. Receiving succeeds only with both.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>SV-7705, SV-7707, SV-7708 (S10 / S12-R2 / S13)</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open on a WO with no VIN on the asset.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Clear the VIN field.
 2. Check the Confirm Review button.
 3. Enter a VIN and check again.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Review is disabled while VIN is empty.
 2. Confirm Review enables after a VIN is entered.</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7)</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part-bearing work order had completion started and cancelled once.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Cancel the first completion attempt.
 2. Start and complete again.
 3. Inspect the POs.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. No duplicate POs are created on the second attempt.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>SV-7698 (S3-R9 (idempotency))</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid work order is on a receive surface.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the invoiced/paid WO part.
 2. Try to edit the sell field.
 3. Hover the lock icon.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. The sell field is locked (not editable).
 2. A lock icon and tooltip 'Locked — this part is already invoiced or paid' are shown.
 3. Only cost remains editable.</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R7 / §4 field locking)</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same vendor are being received.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Enter the same invoice number on both POs.
 2. Receive both.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. The reused invoice number is accepted (uniqueness is relaxed).
 2. Both POs receive successfully.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R3 / §4 (uniqueness relaxed))</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Verify the approve-line error text appears when completing with an unapproved line</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has one unapproved line and all other gates satisfied.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
 2. Read the error shown at the final confirm.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. The existing 'you need to approve the line to complete the work order' error is shown.
 2. Completion does not proceed until the line is approved.</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Key Decision (line approval)</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has an in-stock inventory part; its on-hand quantity is noted.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order via the simple (skip) path.
 2. Check the part's on-hand quantity and Part History.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. The in-stock part's on-hand quantity decrements.
 2. A Part History entry is written.
 3. The skip path's status setter does not bypass inventory movement / Part History / catalog / delivery.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 1</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create Purchase Orders is OFF.
 3. A work order with a vendor/found part exists.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order with Create POs OFF.
 2. Check for any PO, vendor bill, AP sync.
 3. Check for any catalog/inventory sync of the vendor/found part.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. No PO, no vendor bill, no AP sync.
 2. No catalog/inventory sync (part is received at request time only).</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>§5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create POs is on and a work order has a receivable vendor part.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Receive the part via Accept Delivery.
 2. Check that a Delivery, then a Vendor Bill, then a QuickBooks sync occur.
 3. Repeat via the Bulk Receive surface (once built) and confirm it also syncs.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. Receiving creates a Delivery, then a Vendor Bill, then syncs to QuickBooks.
 2. Both receive surfaces sync the vendor bill (only complete-simple bypasses this).</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 2</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless / no-PN part exists on a work order.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Before adding a vendor/PN, check inventory and Part History for the part.
 2. Add a vendor and PN, then re-check.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. Before a vendor/PN, there is zero inventory interaction (no item, no history).
 2. After a vendor and PN are added, normal inventory handling applies.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. Check QuickBooks sync for the Vendor Missing PO.
 2. Provide a vendor and part number and re-check.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. While vendor/PN are missing, the PO is excluded from QuickBooks.
 2. Once both are provided, it becomes eligible for QuickBooks.</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (§5 / S6-R3)</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a part with no cost recorded at completion.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order.
 2. Check the resulting cost/margin figures that flow to QuickBooks.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
-        <is>
-          <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.</t>
-        </is>
-      </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.
+2. For vendorless / no-part-number parts the mandatory sell price is captured at add time behind the See Financial Data gate, so a completing user has a sell figure and $0-cost margins are avoided.</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>§8 (cost at completion)</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completed work order is ready to invoice.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Create the invoice.
 2. Check for the Journal Entry / Inventory sync to QuickBooks.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. The Journal Entry / Inventory sync to QuickBooks fires on invoice creation.
 2. This sync is not dependent on a PO existing.</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part transitions to inventory-tracked (e.g. a part number is added and it is received).</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Add a part number to a previously untracked part and receive it.
 2. Open the item's Part History.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. Part History is preserved / created for the now inventory-tracked part.</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 3</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>API — Work Order Settings</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>API — Work Order Settings</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>API — Work Order Settings</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>API — Work Order Settings</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>API — Work Order Settings</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>API — Permissions</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>API — Permissions</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J160"/>
+  <dimension ref="A1:J163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -867,7 +867,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. Auto-approve Lines = OFF.
+          <t>1. Auto-approve Lines = OFF (spec default — authoritative).
 2. Create Purchase Orders = ON.
 3. Vendor Invoice = REQUIRED.</t>
         </is>
@@ -1112,8 +1112,8 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. EXPECTED (typical UX): with no changes, Save Settings is disabled.
-2. After a change, Save Settings becomes enabled.</t>
+          <t>1. Saving persists the settings changes.
+2. Dirty-state gating (disabling Save until a change is made) is NOT required in v1 — Save being always enabled is acceptable (low-priority polish, not a blocker).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1799,8 +1799,10 @@
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1. The modal shows the number of parts waiting to receive (e.g. '2 parts waiting to receive').
-2. Background POs are created for the vendor parts (a vendorless part goes on the WO's PO flagged Vendor Missing).
-3. Inventory-pick status is reflected in the modal.</t>
+2. Background POs are created for the vendor parts (a vendorless / sell-price-only part goes on the work order's PO flagged Vendor Missing).
+3. All approved-line parts are actually ordered and reach waiting-to-receive, so 'Receive Parts' always has something to receive.
+4. No approved part is left in 'requested' and routed to an empty receive screen.
+5. Inventory-pick status is reflected in the modal.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2092,7 +2094,8 @@
         <is>
           <t>1. The wizard shows a Receive step ('2 parts waiting to receive').
 2. The primary Complete Work Order CTA is DISABLED until all parts are received.
-3. There is NO 'Complete without receiving' option.</t>
+3. There is NO 'Complete without receiving' option.
+4. Approved sell-price-only parts (missing vendor and/or cost) are ordered too and reach waiting-to-receive before the receive gate — no approved part is left in 'requested' with nothing to receive.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2142,7 +2145,8 @@
         <is>
           <t>1. The receive page collects qty, tax, date, note and invoice # per vendor.
 2. On return, once all parts are received the Complete Work Order CTA is enabled.
-3. Completing shows the Success screen.</t>
+3. Completing shows the Success screen.
+4. Sell-price-only parts were ordered to waiting-to-receive, so they appear in the receive round-trip and are not left in 'requested'.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2350,7 +2354,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Verify inventory cores are gated in the completion modal after Pick with Ok/Not OK per core</t>
+          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2377,17 +2381,17 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1. Click Complete Work Order.
-2. Complete the Pick step.
-3. Observe the Resolve Cores step and mark each core Ok (returned) or Not OK (keep + charge).
-4. Try to continue before resolving all cores.</t>
+          <t>1. Add a cored inventory part to a work order line and open the line's Parts view.
+2. Confirm the part generates a Core sub-line with per-core Ok / Not-OK controls and a $ amount.
+3. Click Complete Work Order and step through the completion wizard.
+4. Confirm there is no distinct Resolve Cores step and completion goes Details -&gt; Success.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. A Resolve Cores step appears after Pick, listing only the core lines.
-2. Each core offers Ok (returned, no charge) and Not OK (keep + charge).
-3. Continue is disabled until all cores are resolved.</t>
+          <t>1. The cored part generates a Core sub-line on the line's Parts view with per-core Ok (returned, no charge) and Not-OK (keep + charge) controls and a $ amount ($0 until Not-OK).
+2. The completion wizard has NO distinct Resolve Cores step; a work order whose only remaining action is core resolution completes Details -&gt; Success.
+3. Core resolution is a line-level control, not a wizard step.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2401,7 +2405,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step is skipped when the work order has no cores</t>
+          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2434,8 +2438,8 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1. No Resolve Cores step appears.
-2. Completion proceeds directly through the normal steps.</t>
+          <t>1. No core sub-lines appear (the work order has no cores).
+2. There is no distinct Resolve Cores wizard step; completion proceeds directly Details -&gt; Success.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2786,7 +2790,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Verify the Resolve Cores step shows a live running '+$ to invoice' total as cores are marked Not OK</t>
+          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2812,16 +2816,16 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1. Mark one core Not OK (keep + charge).
-2. Observe the running total.
-3. Mark another core Not OK and observe again.</t>
+          <t>1. On the line's Parts view, mark a Core sub-line Not-OK (keep + charge).
+2. Observe the $ amount on that Core sub-line.
+3. Mark the core Ok and observe the $ amount again.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. A live '+$ to invoice' total is shown.
-2. The total increases as each core is marked Not OK.
-3. Marking a core Ok does not add to the total.</t>
+          <t>1. The Core sub-line shows a $ amount on the line's Parts view ($0 until it is marked Not-OK).
+2. Marking the core Not-OK sets the +$ to invoice on that line.
+3. There is no distinct Resolve Cores wizard step with a running total; the core $ is a line-level control.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3258,10 +3262,11 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. The part saves successfully.
-2. The part appears on the line with its description, quantity and sell price.
-3. It is treated as a vendorless part downstream.
-4. Adding a vendorless / no-part-number part requires WO Lines: Create &amp; Edit and See Financial Data, because the sell price is mandatory and has no catalog source.</t>
+          <t>1. The part saves successfully with only description, quantity and sell price entered.
+2. Sell price is the only mandatory financial field and is validated at save (inline) — the part cannot be saved without it (not deferred to completion).
+3. The part appears on the line with its description, quantity and sell price and is treated as a vendorless part downstream.
+4. A sell-price-only part (missing vendor and/or cost) is orderable from the line — Order creates/joins the Vendor-Missing PO and moves it to waiting-to-receive.
+5. Adding a vendorless / no-part-number part requires WO Lines: Create &amp; Edit and See Financial Data, because the sell price is mandatory and has no catalog source.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3309,9 +3314,9 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. Saving is blocked when the description is empty.
-2. Saving is blocked when the quantity is empty.
-3. Saving is blocked when the sell price is empty.
+          <t>1. Saving is blocked inline at save when the description is empty.
+2. Saving is blocked inline at save when the quantity is empty.
+3. Saving is blocked inline at save when the sell price is empty — sell price is validated at save, not deferred to completion.
 4. A user without See Financial Data (for example a Technician) cannot add a vendorless / no-part-number part, because they cannot enter the mandatory sell price.</t>
         </is>
       </c>
@@ -3853,185 +3858,189 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Vendor Missing on WO PO (Story 6)</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
+2. An open work order has a sell-price-only line part (sell price set; vendor and/or cost missing; part number empty).</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>1. On the line, use the Order action for the sell-price-only part.
+2. Open the PO list at /parts/orders and find the work order's PO.
+3. Confirm the part's status.</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>1. Ordering from the line creates or joins the work order's Vendor-Missing PO (no separate dummy PO).
+2. The part moves from 'requested' to 'waiting-to-receive' without completing the work order.
+3. At receive, a vendor and part number are still required (cost editable — Story 10).</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>SV-7701 (S6-R7)</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
           <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The PO list at /parts/orders has multiple POs.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open /parts/orders.
 2. Look for a select-all checkbox in the header.
 3. Look for a checkbox on each PO row.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. A select-all checkbox is present.
 2. Each PO row has its own checkbox.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7-R1)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The PO list has selectable POs.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Select one or more POs.
 2. Observe the action bar.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. A bar appears reading 'N purchase orders selected'.
 2. The bar has Clear and Receive Selected actions.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7-R2)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two or more POs are selected on the PO list.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Click Receive Selected.
 2. Observe the destination page and the POs shown.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The PO Bulk Receive page opens (Story 8).
 2. It contains the POs that were selected.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7-R3)</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>PO Multi-Select (Story 7)</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. The PO list contains at least one fulfilled PO.</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>1. Attempt to select a fulfilled PO's checkbox.</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>1. The fulfilled PO cannot be selected (checkbox disabled).</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>SV-7702 (S7-R4)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4040,268 +4049,313 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>PO Multi-Select (Story 7)</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. The PO list contains at least one fulfilled PO.</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>1. Attempt to select a fulfilled PO's checkbox.</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>1. The fulfilled PO cannot be selected (checkbox disabled).</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>SV-7702 (S7-R4)</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
           <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The PO list contains a Vendor Missing PO.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Select a Vendor Missing PO.
 2. Confirm its Vendor Missing indication is shown while selected.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The Vendor Missing PO is selectable.
 2. Its Vendor Missing status remains clearly indicated.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7-R5)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The PO list has more POs than fit on one page (or a filter is applied).</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter or page the list.
 2. Click select-all.
 3. Check which POs are selected.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. Select-all only selects POs in the current page/filter, not the whole dataset.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7 (select-all scope))</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You reached the Bulk Receive page via Receive Selected.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Locate the top-left 'Back to Purchase Orders' link.
 2. Click it.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. A 'Back to Purchase Orders' link is present top-left.
 2. Clicking it returns to the PO list.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R1)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Multiple POs across multiple vendors were sent to the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1. Read the vendor group headers and counts.
 2. Use one vendor's Expand/Collapse all control.
 3. Confirm each vendor has its own control (not one global).</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>1. POs are grouped by vendor with a count per vendor.
 2. Each vendor group has its own Expand/Collapse all control.
 3. POs within a group are collapsible.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R2 / S8-R3)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page is open with several POs.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. Read a PO row's details.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. The row shows the PO number.
 2. It shows the related work order, or an inventory / no-WO indicator.
 3. It shows the parts count.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R4)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page is open with POs and parts.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Confirm nothing is selected on load.
 2. Select a PO and confirm all its parts get selected.
@@ -4309,389 +4363,390 @@
 4. Confirm the receive action is locked when nothing is checked.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. Nothing is selected by default.
 2. Selecting a PO selects all its parts; individual parts can be toggled.
 3. Actions are locked until at least one item is checked.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R5)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO's parts are selected on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the 'Receive parts (N)' button state with no invoice number.
 2. Enter a vendor invoice number.
 3. Confirm the button state again.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. The Receive button is disabled without a vendor invoice number.
 2. For a vendor-missing PO it also requires a vendor assigned and the missing part number entered.
 3. Once satisfied, the Receive button enables.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R6)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has a PO whose WO is NOT yet invoiced/paid, and another whose WO IS invoiced/paid.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. On the not-yet-invoiced PO, edit quantity, cost and sell.
 2. On the invoiced/paid PO, try to edit sell.
 3. Hover the locked sell field.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>1. Quantity and cost are editable; sell is editable while the WO is not invoiced/paid.
-2. After the WO is invoiced/paid, sell is locked with a lock icon and tooltip 'Locked — this part is already invoiced or paid'.
-3. After locking, only cost remains editable.</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>1. Quantity and cost are editable; sell is editable while the work order is not invoiced/paid.
+2. After the work order is invoiced/paid, sell is locked with a lock icon and tooltip 'Locked — this part is already invoiced or paid'.
+3. After locking, only cost remains editable.
+4. The field rules have parity with the Accept-Delivery receive screen; cost is editable when $0 or missing on either surface.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-7703, SV-7705 (S8-R7 / S10-R2)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has a Vendor Missing PO.</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Assign a vendor to the Vendor Missing PO.
 2. Confirm it moves into that vendor's group.
 3. Enter the missing part number and confirm receiving becomes enabled.</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. Assigning a vendor moves the PO into that vendor's group.
 2. Entering the missing part number unflags it.
 3. Receiving is then enabled.</t>
         </is>
       </c>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R8)</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Multiple POs/parts are selected with valid invoice numbers on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Reduce one part's received quantity below its ordered quantity.
 2. Click Receive all.
 3. Confirm the receipts.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. Everything selected is received at once.
 2. Partial receive (received qty below ordered) is supported.
 3. Remaining unreceived quantity stays waiting to receive.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R10)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You received POs on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. After receiving, check that a Delivery record was created.
 2. Check that a Vendor Bill was created.
 3. Check that the vendor bill synced to QuickBooks.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. A Delivery is created.
 2. A Vendor Bill is created.
 3. The vendor bill syncs to QuickBooks (same pipeline as single-PO receive).</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R11)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO on the Bulk Receive page holds a cored part.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Receive only the cored line (core-only partial receive).
 2. Confirm an Ok/Not OK resolution becomes available for the core.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. Core-only partial receive is supported.
 2. Once the cored part is received, its Ok/Not OK resolution becomes available (for Story 3/4 resolution).</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-C1 / S8-C2)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has a vendor group with multiple POs.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Locate the 'Apply invoice to selected POs' control under the vendor name.
 2. With no invoice # and no PO selected, confirm it is disabled.
 3. Enter an invoice # and select at least one PO under that vendor.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. The control appears under the vendor name.
 2. It is enabled only when an invoice number is entered and at least one PO under that vendor is selected.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R1)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor group has several POs; some are selected.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Enter one invoice number.
 2. Click Apply.
@@ -4699,1695 +4754,1652 @@
 4. Edit one PO's invoice number.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The invoice number is pre-filled into only the selected POs of that vendor.
 2. Unselected POs are not changed.
 3. Each PO's invoice number remains editable after Apply.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R2)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has multiple vendor groups plus a vendorless group.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Apply Invoice is available per vendor group.
 2. Confirm the vendorless group has no Apply Invoice control.
 3. Apply the same invoice number to POs where uniqueness is relaxed.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. Apply Invoice is scoped to each vendor group.
 2. The vendorless group has no Apply Invoice control.
 3. The same invoice number can be reused (uniqueness relaxed).</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R3)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part with no part number is on a PO or receive surface.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Locate the 'Missing part number' indicator on the part.
 2. Click Edit and enter a part number.
 3. Save and reload.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. The part shows 'Missing part number' with an Edit action.
 2. Entering and saving a part number persists it immediately.
 3. A part number is mandatory to receive.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10-R1)</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part with a newly-entered part number (not matching any existing item) is ready to receive with a vendor assigned.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Enter a brand-new part number and save.
 2. Receive the part.
 3. Check inventory and Part History for the new item.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. A new inventory/catalog part is created.
 2. Stock is added for the received quantity.
 3. A Part History entry is written.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10 AC (new number))</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. An inventory item with a known part number exists; a part on a PO can be given that number.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. Enter the existing part number on the part and save.
 2. Receive the part.
 3. Check the linked item's stock, received cost, Part History, description and category.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. The part links to the existing inventory item.
 2. Stock, received cost and Part History update.
 3. The item's existing description and category are NOT overwritten.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10 AC (existing number))</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid WO and a part on an open WO are available.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. On the open WO part, confirm qty/cost/sell are editable.
 2. On the invoiced/paid WO part, confirm sell is locked and cost is editable.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>1. Open WO: quantity, cost and sell editable.
-2. Invoiced/paid WO: sell locked (lock icon + tooltip), only cost editable.</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>1. Open work order: quantity, cost and sell are editable.
+2. Invoiced/paid work order: sell is locked (lock icon + tooltip), only cost editable.
+3. The inline part-number field rules apply with parity across BOTH the Bulk Receive page AND the single / Accept-Delivery receive screen.
+4. Cost is editable when $0 or missing on either receive surface.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>SV-7703, SV-7705 (S10-R2 / S8-R7)</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part without a part number is on a receive surface.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to receive the part with no part number.
 2. For a vendor-missing part, attempt to receive with no vendor.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a part number.
 2. For vendor-missing, receiving is also blocked without a vendor.
 3. On an invoiced/paid WO, sell stays locked and cost stays editable while the block applies.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10 Negative)</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A default part category exists and a vendor is assigned to the part.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Enter a part number inline and receive.
 2. Verify a CataloguePart and an inventory stock Part were created (not just a string on the request).
 3. Verify Part History exists.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. A catalog part is created/linked.
 2. An inventory stock Part exists (a CataloguePart alone is not stock).
 3. Part History is written; the flow does not rely on the complete-simple bypass to create inventory.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10 Technical guardrails)</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO-originated PO exists.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Open /parts/orders and find the WO-originated PO.
 2. Confirm a Receive action on the PO row.
 3. Open the PO detail card and confirm a Receive action there too.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. The PO list row shows a Receive action.
 2. The PO detail card also shows a Receive action (the detail card previously hid it).</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R1)</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO-originated PO with an unreceived part exists.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Click Receive on the PO.
 2. Observe the destination surface.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. The shared Accept Delivery surface opens for that PO.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R2)</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. An Office / read-only user credential (no Order Parts) exists.
 2. A fulfilled PO and an unfulfilled PO exist.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as an Office / read-only user and open the PO list.
 2. Confirm the Receive action is hidden for them.
 3. As an authorized user, confirm the Receive action is hidden on a fulfilled PO.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or detail.
 2. Fulfilled POs do not show the Receive action.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R3)</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A multi-vendor delivery exists at /parts/deliveries.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Open Accept Delivery / Vendor Invoices at /parts/deliveries.
 2. Confirm grouping by vendor.
 3. Confirm each vendor group has its own invoice #, date, tax, note and Receive.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. The screen groups items by vendor.
 2. Each vendor group has its own invoice number, date, tax, note and Receive action.
 3. Multiple vendors on one PO are supported (existing behavior).</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12 (existing multi-vendor))</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the bottom</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO has a vendorless/no-PN part and a WO-originated PO reached via the Receive button.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Open Accept Delivery for the WO.
 2. Confirm the vendorless/no-PN parts appear.
-3. Confirm the vendor-missing group is at the bottom.</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
+3. Confirm the vendor-missing group is at the top (leading).</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. New vendorless/no-PN WO parts appear and are receivable here.
 2. WO-originated POs reached via the Receive button appear.
-3. Vendor-missing parts sit in their own group at the bottom.</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
+3. Vendor-missing parts sit in their own group that LEADS (appears at the top), because they need action (assign a vendor) before receiving.</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R1)</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing / no-PN part is in an Accept Delivery group.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to receive without a vendor set.
 2. Attempt to receive without a part number.
 3. Attempt to receive without a vendor invoice number.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is gated until a vendor is set.
 2. Receiving is gated until the missing part number is entered.
-3. Receiving is gated until a vendor invoice number is captured.</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
+3. Receiving is gated until a vendor invoice number is captured.
+4. On Accept Delivery, cost is editable when $0 or missing (parity with Bulk Receive); the sell-price lock rule is unchanged.</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R2)</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A multi-vendor delivery with a vendor-missing group exists.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Open Accept Delivery.
 2. Confirm the '+N' vendor indicator.
 3. Confirm the ordering of the vendor-missing group.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. A '+N' indicator summarizes multiple vendors.
 2. The vendor-missing group leads (appears first).</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R3)</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A multi-vendor delivery is received.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Receive each vendor group with its own invoice number.
 2. Check QuickBooks / AP for the resulting bills.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. Each vendor group creates its own vendor bill.
 2. Each syncs to QuickBooks as a separate AP entry.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R4)</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A delivery item with a known ordered quantity is on Accept Delivery.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Set the received quantity above the ordered quantity.
 2. Observe the warning.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. A 'received more than ordered' warning is shown (existing behavior).</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12 (existing) received-more-than-ordered)</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Accept Delivery (Story 12)</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. An Accept Delivery group has a line whose cost is $0 or missing (cost is pulled from the WO/PO when available).</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>1. Open Accept Delivery for the delivery.
+2. Locate a line with a $0 or missing cost and edit the cost.
+3. Confirm the quantity remains editable and the sell-price lock rule is unchanged.</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>1. Cost is editable on Accept Delivery when $0 or missing (matching Bulk Receive / Story 8 / Story 10).
+2. Quantity stays editable.
+3. The sell-price lock rule is unchanged (sell locks only after the work order is invoiced/paid).</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>SV-7707 (S12-R5)</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing group is shown on the receive surface.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Open the vendor-missing group's vendor dropdown.
 2. Choose a vendor.
 3. Reload and confirm the assignment persists.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. The vendor dropdown assigns a vendor at PO level.
 2. The assignment is saved locally and to the backend.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R1)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO already has vendor X, and a vendor-missing group on the same PO is being assigned vendor X.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Assign the same vendor that is already on this PO.
 2. Observe the prompt.
 3. Try both 'Yes, Merge' and 'No, Keep Separate' in separate runs.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. A prompt 'Add to {vendor}?' appears.
 2. 'Yes, Merge' combines into one group; 'No, Keep Separate' keeps two invoice numbers for the same vendor on one PO (valid).</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R2)</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same WO exist; vendor Y is on the other PO.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Assign vendor Y to the vendor-missing group.
 2. Accept the merge prompt.
 3. Confirm items moved and the emptied source PO is removed.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. A prompt to merge the POs appears.
 2. Items move to the target PO; the emptied source PO is removed.
 3. The view redirects to the target PO.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R3)</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing group with a valid part number is being assigned a brand-new vendor (no collision).</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Assign a different vendor that is not already on any PO for this WO.
 2. Observe the QuickBooks flag and the group's Receive action.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. The vendor auto-assigns with no prompt.
 2. The QuickBooks 'vendor missing' flag clears.
 3. The group's Receive action becomes enabled.</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R4 / S13-R5)</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two vendors share the same name but different IDs; an invoiced/paid WO with a vendor-missing PO exists.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Assign a vendor and confirm matching is by ID (same-name different-ID vendors are not treated as the same).
 2. Attempt a merge across different work orders.
 3. Attempt to receive on the invoiced/paid WO.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. Vendors are matched by ID, not name.
 2. Merge only applies within the same work order.
 3. Receiving is blocked when the WO is invoiced/paid.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13 Technical guardrails)</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Work Orders list is open with WOs that have unreceived parts.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work Orders list column selector.
 2. Enable 'Waiting on Parts'.
 3. Read the column values across statuses.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>1. A 'Waiting on Parts' column is offered in the column selector (off by default).
 2. It shows the count of unreceived parts per work order across all statuses.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R1)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Waiting on Parts column is enabled and a WO shows a count.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Click the count on a work order row.
 2. Observe the destination.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. Accept Delivery opens for the work order's first unreceived PO.
 2. Receiving behaves as it does today from there.</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R2)</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO with nothing to receive (or POs off) is in the list with the column enabled.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Find a WO with nothing waiting to receive.
 2. Read its Waiting on Parts cell.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. The cell shows '—' with no clickable link.</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R3)</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Require Review Before Completion is ON and saved.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Open a work order with approved lines.
 2. Start completion.
 3. Observe that the review flow is used.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review ON, completing routes into the review flow rather than completing directly.</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R1)</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON.
 3. A work order with approved lines is ready to complete.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
 2. Read the wizard's primary CTA label.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. The primary CTA reads 'Complete &amp; Send to Review' (Send to Review).</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R2)</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON.
 3. A work order missing mileage/hours/VIN is ready to complete.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Start completion and reach the Details step.
 2. Note which vehicle fields are collected.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. The Details step collects mileage and engine hours only.
 2. VIN is NOT collected here; it is captured later by the reviewer in the Mark Reviewed dialog.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R3)</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON with a part-bearing work order.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. Start completion and click Receive Parts.
 2. Observe the destination.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>1. Receive Parts opens the shared receive page (not an inline modal).</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R4)</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order with approved lines is in the completion wizard.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete &amp; Send to Review.
 2. Observe the work order status and banner.
 3. Check the lines state and inventory pick state.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. The work order status becomes Review (amber).
 2. A 'Ready for Review' / 'Sent for review' indication is shown.
 3. Lines lock to Complete and inventory is auto-picked.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R5 / R6)</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Review state.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. Click Mark Reviewed.
 2. Observe the VIN field.
 3. Clear the VIN and check the Confirm Review button, then enter a VIN.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>1. The Mark Reviewed dialog exposes a VIN field (input_review_vin), required if missing.
 2. Confirm Review is disabled until a VIN is present.
 3. With a VIN, Confirm Review is enabled.</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 / R10)</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order with an inventory line just went to Review.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order in Review state.
 2. Check the line states.
 3. Check whether inventory was auto-picked.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>1. Lines are locked to Complete.
 2. Inventory has been auto-picked.</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R6)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Verify Confirm Review moves the WO to a distinct Reviewed state requiring a separate final Complete Work Order</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Review with the Mark Reviewed dialog filled (VIN present).</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. Click Confirm Review.
 2. Observe the resulting work order state.
 3. Look for a separate final 'Complete Work Order' action.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>1. The WO moves to Reviewed (green) with a 'sign-off complete' banner.
-2. A separate final Complete Work Order action is required to move to Complete.</t>
-        </is>
-      </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>1. After Confirm Review the sign-off completes and the work order moves directly Review -&gt; Complete.
+2. There is no distinct 'Reviewed' holding state and no separate final 'Complete Work Order' click.</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R5 / R8 (distinct Reviewed state))</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. A role with Review Work Orders and a role without it both exist.
 2. A work order is in Review state, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as a role without Review Work Orders and open the work order in Review.
 2. Confirm Mark Reviewed is disabled with 'Awaiting review'.
 3. Sign in as a role with Review Work Orders (system defaults grant it broadly; it can be limited to manager/foreman via custom roles) and confirm Mark Reviewed is available.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. A role without the Review Work Orders permission sees Mark Reviewed disabled with an 'Awaiting review' indicator.
 2. A role with the Review Work Orders permission can Mark Reviewed and sign off.
 3. The user who completed / sent the work order to review cannot Mark Reviewed even with the permission; a different qualified reviewer can.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 (role-gating))</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Mark Reviewed dialog includes an optional review note field (input_review_note)</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. The Mark Reviewed dialog is open.</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>1. Look for an optional note field in the dialog.
-2. Enter a note and Confirm.</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>1. An optional review note field (input_review_note) is present.
-2. A note can be entered and saved with the sign-off.</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>SV-7870 (R7 / R10 (optional note))</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>Verify after sign-off the final Complete Work Order (any role) completes the WO and invoicing is blocked until reviewed</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E123" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A work order is in Reviewed state (or a Review state before sign-off for the invoicing-block check).</t>
-        </is>
-      </c>
-      <c r="F123" s="2" t="inlineStr">
-        <is>
-          <t>1. Before sign-off, attempt to invoice the work order.
-2. After sign-off, click the final Complete Work Order (as any role).
-3. Confirm the WO becomes Complete (invoice-ready).</t>
-        </is>
-      </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>1. Invoicing is blocked until the WO is reviewed.
-2. After sign-off, the final Complete Work Order (any role) makes the WO Complete and invoice-ready.</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>SV-7870 (R8)</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -6396,842 +6408,940 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>Verify the Mark Reviewed dialog includes VIN (required) and an optional review note field (input_review_note)</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. The Mark Reviewed dialog is open.</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Mark Reviewed dialog.
+2. Confirm a required VIN / Serial # field (Confirm disabled until VIN entered).
+3. Confirm an optional review note field is present; enter a note and Confirm.</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>1. The Mark Reviewed dialog shows a VIN / Serial # field that is required (Confirm Reviewed is disabled until VIN is entered).
+2. An optional review note field (input_review_note) is present.
+3. A note can be entered and saved with the sign-off.</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (R7 / R10 (optional note))</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order is in Reviewed state (or a Review state before sign-off for the invoicing-block check).</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>1. Before sign-off, attempt to invoice the work order.
+2. Complete the review sign-off (Confirm Review).
+3. Confirm the work order becomes Complete (invoice-ready).</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>1. Invoicing is blocked until the work order is reviewed.
+2. After sign-off the work order moves directly Review -&gt; Complete (invoice-ready), with no separate final Complete Work Order click.</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (R8)</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
           <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. At least one work order is in Review state.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work Orders list.
 2. Look for a 'Ready for Review' filter or column.
 3. Confirm work orders in Review appear in it.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. A 'Ready for Review' filter/column lists work orders awaiting review.</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R9)</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order has one unapproved line.</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete &amp; Send to Review.
 2. Attempt to send with an unapproved line.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>1. Send to Review is blocked with the existing approve-line error while any line is unapproved.</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R11)</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order has inventory and special-order cores.</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Resolve inventory cores in the completion modal (after Pick) before Send to Review.
 2. For required-invoice, resolve special-order cores after the Receive round-trip before Send to Review; for optional-invoice, resolve at the Create Invoice gate after sign-off.
 3. Attempt to invoice before both Reviewed and cores are resolved.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>1. Inventory cores are resolved before Send to Review.
 2. Special-order cores follow the vendor-invoice rules.
 3. Invoicing is blocked until the WO is Reviewed AND all cores are resolved.</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R Core parts / invoicing block)</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Verify the Require Review default for new vs existing orgs matches the agreed cohort rule</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>1. A newly-created org and an existing org are available.
 2. Signed in as Admin for each.</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. Check the Require Review default on a brand-new org.
 2. Check that existing orgs keep today's behavior (backfilled).</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>1. A brand-new org shows the Require Review setting in its default state, and existing orgs keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R Open (default))</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You are on the Create Work Order form (/workorders → Create).</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Open the Create Work Order form.
 2. Read the primary button label.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. The primary button reads 'Create Work Order'.</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R1)</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order requiring mileage/VIN is being completed.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Observe where required fields are collected.
 3. Confirm the tech story is handled by its own flow, not inside this modal.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. Required fields (mileage / VIN when required) are collected in a centralized center modal.
 2. The tech story is NOT part of this modal (Story 17 handles it separately).</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R2)</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has just been completed.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. Read the success screen.
 2. Confirm WO number, total, Done and Go to Invoice.
 3. Confirm the invoice number is shown on the Finance step, not the success screen.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>1. The success screen shows the WO number and total with Done and Go to Invoice.
 2. The invoice number appears on the Finance step, not on the success screen.</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R3)</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completion modal is open.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. Trigger the close-confirmation modal.
 2. Click Close (prominent/red) and observe.
 3. Trigger it again and click Cancel (text link, far left) and observe.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
-        <is>
-          <t>1. Clicking Close closes the modal only, keeps any entered changes, and stays on the work order.
-2. Cancel closes the modal and returns to the previous screen.</t>
-        </is>
-      </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>1. Close (prominent/red button) closes the confirmation modal only, discards nothing (no discard warning), and stays on the work order.
+2. Cancel (text link, far left) closes the modal and returns to the previous screen.
+3. Other consumers of the shared confirmation dialog keep their existing action labels.</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R4)</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. A role with the App Settings permission (e.g. Admin) and a role without it (e.g. Service Advisor or Technician) both exist.
 2. You can sign in as each.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as a role with App Settings and open and modify /administration/settings → Work Orders.
 2. Sign in as a role without App Settings and attempt to open and modify the same page.
 3. As the role without App Settings, attempt to save a Work Order settings change directly (API), and note the response.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can view and modify the Work Order settings page.
 2. A role without App Settings cannot open or change the Work Order settings.
 3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>SV-7696 (S1 AC / §8 Permissions)</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for several roles exist.
 2. A work order ready to complete exists.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to complete a work order.
 2. Record which roles can and cannot.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. Roles with Work Orders: Create &amp; Edit plus WO Lines: Create &amp; Edit and Full View (needed to approve all lines) can complete a work order: Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
 2. Technician and Parts Tech cannot complete (Technician cannot approve lines in Tech View and/or lacks Work Orders: Create &amp; Edit; Parts Tech is a receiver, not a completer).
 3. Office, Sales Rep and Time Clock cannot complete a work order.</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>§8 Permissions</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for several roles exist.
 2. The Bulk Receive flow is available (Story 7/8 built).</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to reach and use Bulk Receive.
 2. Record the outcomes.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
 2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot receive.
 3. Sales Rep and Time Clock cannot reach Bulk Receive.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>§8 Permissions</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for roles with and without Review Work Orders exist.
 2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to Mark Reviewed.
 2. Record which roles can and cannot.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. Mark Reviewed (review sign-off) requires the Review Work Orders permission; system defaults grant it broadly, and it can be narrowed to manager/foreman via custom roles.
 2. A role without Review Work Orders sees Mark Reviewed disabled with an 'Awaiting review' indicator.
 3. The user who completed / sent the work order to review cannot Mark Reviewed it; a different user who holds Review Work Orders can sign off.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 / §8 role-gating review)</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. An Office / read-only credential (no Order Parts) exists.
 2. A WO-originated PO exists, plus a fulfilled PO.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as an Office / read-only user.
 2. Open the PO list and detail.
 3. Confirm the Receive action is not shown, and confirm it is also absent on a fulfilled PO.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or PO detail.
 2. Receive is also hidden for fulfilled (already-received) POs.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R3)</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Verify the backend enforces the Simple-Flow settings and permission atoms (not front-end only)</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. Signed in with API access.
 2. A relevant Simple-Flow setting (e.g. Require Vendor Invoice Number) is ON.</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Attempt a setting-violating action directly via the API (bypassing the UI), e.g. completing without the required invoice, and note the response.
 2. As a role that lacks the mapped atom, attempt the gated action via the API and note the response.
 3. As a role that has only Work Orders: Create &amp; Edit, attempt to receive onto a work order and note the response.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. The backend enforces the Simple-Flow settings and the permission atoms (it is not front-end only): a setting-violating or unauthorized request is rejected.
 2. Because several work-order atoms collapse to the same backend role pair, any role with Work Orders: Create &amp; Edit can receive onto a work order.
 3. The receive endpoint accepts the documented OR of ROLE_DELIVERY_CREATE_AND_EDIT, ROLE_WORK_ORDER_PART_CREATE and ROLE_WORK_ORDER_CREATE_AND_EDIT.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>§8 BE enforcement</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for roles with and without Review Work Orders exist.
 2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Confirm that only roles holding Review Work Orders can sign off, and roles without it cannot.
 2. Confirm the user who completed / sent the work order to review cannot sign it off.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. Review sign-off is governed by the Review Work Orders custom-role permission (it is NOT open to all users for v1).
 2. The permission gates the Mark Reviewed action, and the reviewer-not-completer rule is enforced (the completer cannot sign off).</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>§8 role-gating review</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. Two different users who both hold the Review Work Orders permission exist.
 2. User A has completed / sent a work order to review; it is in Review state.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as User A (who sent the work order to review) and open the work order in Review.
 2. Attempt to Mark Reviewed.
 3. Sign in as User B (a different user who holds Review Work Orders) and Mark Reviewed.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. User A cannot Mark Reviewed the work order they completed / sent to review; the action is blocked or disabled.
 2. User B, a different user who holds the Review Work Orders permission, can Mark Reviewed and sign off.
 3. The reviewer must be a different person from the completer.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 (reviewer != completer))</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. A Technician credential exists (WO Lines: Create &amp; Edit, no See Financial Data).
 2. An open work order with a line is available.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the Technician and open the work order line.
 2. Attempt to add a vendorless / no-part-number part (description + quantity + sell price).</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. The Technician cannot add a vendorless / no-part-number part.
 2. The mandatory sell price cannot be entered without See Financial Data, so the add is prevented.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5 / §9 (See Financial Data gate))</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for each system role exist (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Technician, Parts Manager, Parts Tech, Office, Sales Rep, Time Clock).
 2. A work order ready to complete is available.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. For each role, open the work order and check whether the Complete Work Order action is available and usable.
 2. Record the result per role against the checklist below.
@@ -7239,920 +7349,964 @@
 4. Roles expected NOT to be able to complete: Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. Complete Work Order is available for Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
 2. Complete Work Order is NOT available for Technician, Parts Tech, Office, Sales Rep or Time Clock.
 3. Technician and Parts Tech are blocked because they cannot approve lines and/or lack Work Orders: Create &amp; Edit; Office is view-only; Sales Rep and Time Clock have no work-order edit access.</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>§9 per-role completion matrix</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage is ON and the work order has no mileage.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave mileage empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until mileage is entered.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>SV-7697, SV-7698, SV-7699 (S2-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. VIN is required for this org's completion and the work order has no VIN.
 3. Require Review is OFF (VIN is collected at completion in the non-review flow).</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave VIN empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until the VIN is entered.</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7710 (S15-R2 / S3-R3)</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Engine Hours is ON and the work order has no engine hours.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave engine hours empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until engine hours are entered.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open on a line.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Leave the story textarea empty.
 2. Check the Next/Continue button.
 3. Type any text and check again.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. With the textarea empty, Next/Continue is disabled.
 2. After typing text, Next/Continue becomes enabled.</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R4)</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is ON and a part is being received.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. On the receive surface, leave the vendor invoice number empty.
 2. Attempt to receive.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor invoice number.
 2. Once an invoice number is entered, receiving is allowed.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R5 / §4)</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing part is on a receive surface.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to receive with no vendor.
 2. Attempt to receive with a vendor but no part number.
 3. Provide both and receive.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor.
 2. Receiving is blocked without a part number.
 3. Receiving succeeds only with both.</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>SV-7705, SV-7707, SV-7708 (S10 / S12-R2 / S13)</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open on a WO with no VIN on the asset.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Clear the VIN field.
 2. Check the Confirm Review button.
 3. Enter a VIN and check again.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Review is disabled while VIN is empty.
 2. Confirm Review enables after a VIN is entered.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7)</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part-bearing work order had completion started and cancelled once.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Cancel the first completion attempt.
 2. Start and complete again.
 3. Inspect the POs.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. No duplicate POs are created on the second attempt.</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>SV-7698 (S3-R9 (idempotency))</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid work order is on a receive surface.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the invoiced/paid WO part.
 2. Try to edit the sell field.
 3. Hover the lock icon.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. The sell field is locked (not editable).
 2. A lock icon and tooltip 'Locked — this part is already invoiced or paid' are shown.
 3. Only cost remains editable.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R7 / §4 field locking)</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same vendor are being received.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Enter the same invoice number on both POs.
 2. Receive both.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. The reused invoice number is accepted (uniqueness is relaxed).
 2. Both POs receive successfully.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R3 / §4 (uniqueness relaxed))</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Verify the approve-line error text appears when completing with an unapproved line</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has one unapproved line and all other gates satisfied.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
 2. Read the error shown at the final confirm.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. The existing 'you need to approve the line to complete the work order' error is shown.
 2. Completion does not proceed until the line is approved.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>Key Decision (line approval)</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has an in-stock inventory part; its on-hand quantity is noted.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order via the simple (skip) path.
 2. Check the part's on-hand quantity and Part History.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. The in-stock part's on-hand quantity decrements.
 2. A Part History entry is written.
 3. The skip path's status setter does not bypass inventory movement / Part History / catalog / delivery.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 1</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create Purchase Orders is OFF.
 3. A work order with a vendor/found part exists.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order with Create POs OFF.
 2. Check for any PO, vendor bill, AP sync.
 3. Check for any catalog/inventory sync of the vendor/found part.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. No PO, no vendor bill, no AP sync.
 2. No catalog/inventory sync (part is received at request time only).</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>§5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create POs is on and a work order has a receivable vendor part.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. Receive the part via Accept Delivery.
 2. Check that a Delivery, then a Vendor Bill, then a QuickBooks sync occur.
 3. Repeat via the Bulk Receive surface (once built) and confirm it also syncs.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. Receiving creates a Delivery, then a Vendor Bill, then syncs to QuickBooks.
 2. Both receive surfaces sync the vendor bill (only complete-simple bypasses this).</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 2</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless / no-PN part exists on a work order.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Before adding a vendor/PN, check inventory and Part History for the part.
 2. Add a vendor and PN, then re-check.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. Before a vendor/PN, there is zero inventory interaction (no item, no history).
 2. After a vendor and PN are added, normal inventory handling applies.</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Check QuickBooks sync for the Vendor Missing PO.
 2. Provide a vendor and part number and re-check.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. While vendor/PN are missing, the PO is excluded from QuickBooks.
 2. Once both are provided, it becomes eligible for QuickBooks.</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (§5 / S6-R3)</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a part with no cost recorded at completion.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order.
 2. Check the resulting cost/margin figures that flow to QuickBooks.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.
 2. For vendorless / no-part-number parts the mandatory sell price is captured at add time behind the See Financial Data gate, so a completing user has a sell figure and $0-cost margins are avoided.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>§8 (cost at completion)</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completed work order is ready to invoice.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Create the invoice.
 2. Check for the Journal Entry / Inventory sync to QuickBooks.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. The Journal Entry / Inventory sync to QuickBooks fires on invoice creation.
 2. This sync is not dependent on a PO existing.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part transitions to inventory-tracked (e.g. a part number is added and it is received).</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Add a part number to a previously untracked part and receive it.
 2. Open the item's Part History.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. Part History is preserved / created for the now inventory-tracked part.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 3</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Investigate: Part Sales unaffected by the shared order/status logic (requested -&gt; orderable/waiting-to-receive)</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>1. PLACEHOLDER for a new V2.4 §8 open question (needs BE investigation).</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>1. Investigation pending — steps to be defined once dev confirms whether the shared order/status logic touches Part Sales.</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>1. OPEN / NEEDS INVESTIGATION — expected result to be defined after dev confirmation. Keep Part Sales unchanged unless the shared logic forces a change (V2.4 §8).</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>§8 open question (Part Sales impact — BE investigation)</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -3212,8 +3212,8 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. EXPECTED PER STORY 17: a story can be entered inline on the line.
-2. A story can also be entered via the completion gate modal.
+          <t>1. A tech story can be entered inline on the line (Story 17 is the authoritative behavior).
+2. A story can also be entered via the completion gate modal, which lets stories be completed individually or several at once.
 3. Both paths persist the story.</t>
         </is>
       </c>
@@ -3228,7 +3228,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Verify a part can be requested with only description, quantity and sell price (part number, cost, vendor empty)</t>
+          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3255,18 +3255,17 @@
       <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Add a part to a line.
-2. Enter only a description, a quantity and a sell price.
-3. Leave part number, cost and vendor empty.
+2. Enter a description, a quantity and a category.
+3. Leave part number, cost, vendor and sell price empty.
 4. Save the part.</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. The part saves successfully with only description, quantity and sell price entered.
-2. Sell price is the only mandatory financial field and is validated at save (inline) — the part cannot be saved without it (not deferred to completion).
-3. The part appears on the line with its description, quantity and sell price and is treated as a vendorless part downstream.
-4. A sell-price-only part (missing vendor and/or cost) is orderable from the line — Order creates/joins the Vendor-Missing PO and moves it to waiting-to-receive.
-5. Adding a vendorless / no-part-number part requires WO Lines: Create &amp; Edit and See Financial Data, because the sell price is mandatory and has no catalog source.</t>
+          <t>1. The part saves successfully with description, quantity and category entered; part number, cost, vendor and sell price may be left empty.
+2. Category is a required field for v1 — the part cannot be saved without a category.
+3. Sell price is not enforced as required for v1 — the part can be saved without a sell price.
+4. The part appears on the line with its description and quantity and is treated as a vendorless part downstream; it is orderable from the line (Order creates or joins the Vendor-Missing purchase order and moves it to waiting-to-receive).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3280,7 +3279,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or sell price is missing</t>
+          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3307,17 +3306,17 @@
       <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Leave the description empty and try to save.
-2. Fill description, leave quantity empty and try to save.
-3. Fill quantity, leave sell price empty and try to save.
-4. As a role without See Financial Data (e.g. Technician), attempt to add a vendorless / no-part-number part.</t>
+2. Fill the description, leave the quantity empty and try to save.
+3. Fill the description and quantity, leave the category empty and try to save.
+4. Fill the description, quantity and category but leave the sell price empty and try to save.</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. Saving is blocked inline at save when the description is empty.
-2. Saving is blocked inline at save when the quantity is empty.
-3. Saving is blocked inline at save when the sell price is empty — sell price is validated at save, not deferred to completion.
-4. A user without See Financial Data (for example a Technician) cannot add a vendorless / no-part-number part, because they cannot enter the mandatory sell price.</t>
+          <t>1. Saving is blocked inline when the description is empty ('Description is a required field').
+2. Saving is blocked inline when the quantity is empty ('Quantity is a required field').
+3. Saving is blocked inline when the category is empty ('Category is a required field').
+4. Saving is allowed when only the sell price is empty — sell price is not enforced as a required field for v1.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6408,7 +6407,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN (required) and an optional review note field (input_review_note)</t>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6436,19 +6435,19 @@
         <is>
           <t>1. Open the Mark Reviewed dialog.
 2. Confirm a required VIN / Serial # field (Confirm disabled until VIN entered).
-3. Confirm an optional review note field is present; enter a note and Confirm.</t>
+3. Confirm there is no review note field, then complete the sign-off.</t>
         </is>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. The Mark Reviewed dialog shows a VIN / Serial # field that is required (Confirm Reviewed is disabled until VIN is entered).
-2. An optional review note field (input_review_note) is present.
-3. A note can be entered and saved with the sign-off.</t>
+2. There is no review note field on the dialog.
+3. The sign-off completes using the VIN / Serial # only.</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>SV-7870 (R7 / R10 (optional note))</t>
+          <t>SV-7870 (R7 (VIN required, no note))</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr"/>
@@ -7125,7 +7124,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Verify the backend enforces the Simple-Flow settings and permission atoms (not front-end only)</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -7151,16 +7150,18 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>1. Attempt a setting-violating action directly via the API (bypassing the UI), e.g. completing without the required invoice, and note the response.
-2. As a role that lacks the mapped atom, attempt the gated action via the API and note the response.
-3. As a role that has only Work Orders: Create &amp; Edit, attempt to receive onto a work order and note the response.</t>
+          <t>1. As a role that lacks the mapped permission, confirm the gated setting/action is hidden or unavailable in the UI.
+2. Attempt the same setting change directly via the API (bypassing the UI) as that role, and note the response.
+3. As a role that lacks the completion / review sign-off permission, attempt to complete a work order and to sign off a review directly via the API, and note the response.
+4. As a role that has only Work Orders: Create &amp; Edit, attempt to receive onto a work order and note the response.</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1. The backend enforces the Simple-Flow settings and the permission atoms (it is not front-end only): a setting-violating or unauthorized request is rejected.
-2. Because several work-order atoms collapse to the same backend role pair, any role with Work Orders: Create &amp; Edit can receive onto a work order.
-3. The receive endpoint accepts the documented OR of ROLE_DELIVERY_CREATE_AND_EDIT, ROLE_WORK_ORDER_PART_CREATE and ROLE_WORK_ORDER_CREATE_AND_EDIT.</t>
+          <t>1. UI gating is the pass criterion for v1: a role without the mapped permission does not see or cannot use the gated setting/action in the UI.
+2. The Simple-Flow settings atom is enforced at the backend too — the unauthorized settings request is rejected.
+3. The work-order completion and review sign-off atoms are NOT enforced at the backend — a direct API call from a role lacking the permission still succeeds. This passes for v1 on the UI restriction, but the API-level gap is a KNOWN ISSUE to fix; record the result as 'UI pass / API fail' so it stays on record.
+4. Because several work-order atoms collapse to the same backend role pair, any role with Work Orders: Create &amp; Edit can receive onto / act on a work order via the API (documented OR of ROLE_DELIVERY_CREATE_AND_EDIT, ROLE_WORK_ORDER_PART_CREATE and ROLE_WORK_ORDER_CREATE_AND_EDIT).</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -5915,8 +5915,8 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1. Accept Delivery opens for the work order's first unreceived PO.
-2. Receiving behaves as it does today from there.</t>
+          <t>1. EXPECTED (built): clicking the count opens the receiving surface for the work order's first unreceived PO. In the current build this is the consolidated Bulk Receive page (/bulk-receive), which supersedes the legacy Accept Delivery screen for work-order POs.
+2. Receiving behaves as it does from the Bulk Receive page from there.</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J163"/>
+  <dimension ref="A1:J164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1961,7 +1961,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
+          <t>Verify the optional-invoice completion modal collects the required vehicle fields (mileage and engine hours; VIN only when Require Review is off) when missing</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1983,7 +1983,8 @@
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage / Engine Hours are ON and the work order is missing those values.
-3. You are completing a part-bearing work order with invoice Optional.</t>
+3. You are completing a part-bearing work order with invoice Optional.
+4. Require Review Before Completion is off (so VIN is collected at completion, not by the reviewer).</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1995,9 +1996,10 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. The modal collects the required vehicle fields that are missing.
-2. Continuation is blocked until required fields are supplied.
-3. Tech story is handled separately (Story 17), not inside this step.</t>
+          <t>1. When Require Review is off, the modal collects the missing required vehicle fields: mileage, VIN and engine hours.
+2. When Require Review is on, VIN is not collected here — it is captured later by the reviewer in the Mark Reviewed dialog (Story 16) — and the modal collects only mileage and engine hours.
+3. Continuation is blocked until the required fields are supplied.
+4. Tech story is handled separately (Story 17), not inside this step.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2207,7 +2209,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
+          <t>Verify on a required-invoice work order an unapproved line disables the Complete Work Order button with a tooltip</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2228,27 +2230,30 @@
       <c r="E37" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Auto-approve Lines is OFF.
-3. A work order has one line still in Needs Approval and all other gates satisfied (tech story present, required fields present).</t>
+2. Require Vendor Invoice Number is ON (required-invoice / Story 4 flow).
+3. Auto-approve Lines is OFF.
+4. A work order has one line still in Needs Approval and all other gates satisfied (tech story present, required fields present).</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1. Click Complete Work Order.
-2. Proceed through any tech-story / details gates.
-3. Attempt the final Complete confirm.</t>
+          <t>1. Open the required-invoice work order and start completion.
+2. Observe the Complete Work Order button while a line is unapproved.
+3. Hover the disabled Complete Work Order button.
+4. Approve the line and observe the button again.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. The existing 'you need to approve the line to complete the work order' error appears.
-2. The work order does not complete while a line is unapproved.
-3. There is no new disabled state — the error surfaces on Complete.</t>
+          <t>1. In the required-invoice (Story 4) flow, an unapproved line leaves the Complete Work Order button disabled.
+2. A tooltip on the disabled button describes the reason, naming the line that needs approval.
+3. The button enables once all lines are approved.
+4. In the No-PO / Optional-invoice (Stories 2/3) and review-on (Story 16) flows the same unapproved line instead surfaces the existing 'you need to approve the line to complete the work order' error on Complete (the button stays active).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-7698, SV-7699 (Key Decision (all lines approved) / S3-R9 / S4-R8)</t>
+          <t>SV-7698, SV-7699 (S4-R8 / Key Decision (all lines approved) / S3-R9)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2257,7 +2262,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
+          <t>Verify a manually unapproved line disables the required-invoice Complete Work Order button with a tooltip even when Auto-approve is ON</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2278,26 +2283,29 @@
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Auto-approve Lines is ON.
-3. A work order has a line that was manually un-approved after being added.</t>
+2. Require Vendor Invoice Number is ON (required-invoice / Story 4 flow).
+3. Auto-approve Lines is ON.
+4. A work order has a line that was manually un-approved after being added.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
           <t>1. Confirm one line is unapproved.
-2. Click Complete Work Order and attempt to complete.
-3. Re-approve the line and retry.</t>
+2. Start completion and observe the Complete Work Order button.
+3. Hover the disabled Complete Work Order button.
+4. Re-approve the line and observe the button again.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. With the line unapproved, completion is blocked with the approve-line error.
-2. After re-approving all lines, completion proceeds.</t>
+          <t>1. In the required-invoice (Story 4) flow the manually unapproved line leaves the Complete Work Order button disabled with a tooltip naming the line that needs approval — this holds even though Auto-approve Lines is ON.
+2. After re-approving all lines, the Complete Work Order button enables and completion proceeds.
+3. In the No-PO / Optional-invoice (Stories 2/3) and review-on (Story 16) flows the same unapproved line instead surfaces the existing 'you need to approve the line to complete the work order' error on Complete.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Key Decision (holds regardless of Auto-approve)</t>
+          <t>SV-7699 (S4-R8 / Key Decision (holds regardless of Auto-approve))</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -5016,7 +5024,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -5043,19 +5051,21 @@
       <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to receive the part with no part number.
-2. For a vendor-missing part, attempt to receive with no vendor.</t>
+2. For a vendor-missing part, attempt to receive with no vendor.
+3. Attempt to receive with no cost / sell price entered.</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a part number.
 2. For vendor-missing, receiving is also blocked without a vendor.
-3. On an invoiced/paid WO, sell stays locked and cost stays editable while the block applies.</t>
+3. Receiving is blocked until a missing cost / sell price is entered.
+4. On an invoiced/paid WO, sell stays locked and cost stays editable while the block applies.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>SV-7705 (S10 Negative)</t>
+          <t>SV-7705, SV-7708 (S10 Negative / S13-R6 / S13-R7)</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -5353,7 +5363,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5381,20 +5391,22 @@
         <is>
           <t>1. Attempt to receive without a vendor set.
 2. Attempt to receive without a part number.
-3. Attempt to receive without a vendor invoice number.</t>
+3. Attempt to receive without a cost / sell price.
+4. Attempt to receive without a vendor invoice number.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is gated until a vendor is set.
 2. Receiving is gated until the missing part number is entered.
-3. Receiving is gated until a vendor invoice number is captured.
-4. On Accept Delivery, cost is editable when $0 or missing (parity with Bulk Receive); the sell-price lock rule is unchanged.</t>
+3. Receiving is gated until a missing cost / sell price is entered.
+4. Receiving is gated until a vendor invoice number is captured.
+5. On Accept Delivery, cost is editable when $0 or missing (parity with Bulk Receive); the sell-price lock rule is unchanged.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>SV-7707 (S12-R2)</t>
+          <t>SV-7707, SV-7708 (S12-R2 / S13-R6 / S13-R7)</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -5738,7 +5750,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5759,25 +5771,27 @@
       <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. A vendor-missing group with a valid part number is being assigned a brand-new vendor (no collision).</t>
+2. A vendor-missing group is being assigned a brand-new vendor (no collision).</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Assign a different vendor that is not already on any PO for this WO.
-2. Observe the QuickBooks flag and the group's Receive action.</t>
+2. Observe the QuickBooks flag.
+3. Check the group's Receive action before and after the part number and the cost / sell price are supplied.</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. The vendor auto-assigns with no prompt.
 2. The QuickBooks 'vendor missing' flag clears.
-3. The group's Receive action becomes enabled.</t>
+3. Assigning the vendor alone does not enable Receive — the part number and the cost / sell price are still required.
+4. Receiving becomes enabled only once the vendor, the part number, and the cost / sell price are all present (plus the vendor invoice number).</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>SV-7708 (S13-R4 / S13-R5)</t>
+          <t>SV-7708 (S13-R4 / S13-R5 / S13-R6 / S13-R7)</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5835,1320 +5849,1369 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Assign Vendor + Merge (Story 13)</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
+2. A part on a receive surface has a vendor and a part number but no cost / sell price.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the receive surface for the part.
+2. Leave the cost / sell price empty and check the Receive action.
+3. Enter a cost / sell price and check the Receive action again.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>1. While the cost / sell price is missing, the user gets an indication to enter one.
+2. Receiving is blocked while the cost / sell price is missing.
+3. Receiving becomes enabled once the cost / sell price is entered (with the vendor, part number and vendor invoice number also present).</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>SV-7708 (S13-R7)</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
           <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Work Orders list is open with WOs that have unreceived parts.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work Orders list column selector.
 2. Enable 'Waiting on Parts'.
 3. Read the column values across statuses.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. A 'Waiting on Parts' column is offered in the column selector (off by default).
 2. It shows the count of unreceived parts per work order across all statuses.</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R1)</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Waiting on Parts column is enabled and a WO shows a count.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Click the count on a work order row.
 2. Observe the destination.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. EXPECTED (built): clicking the count opens the receiving surface for the work order's first unreceived PO. In the current build this is the consolidated Bulk Receive page (/bulk-receive), which supersedes the legacy Accept Delivery screen for work-order POs.
 2. Receiving behaves as it does from the Bulk Receive page from there.</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R2)</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO with nothing to receive (or POs off) is in the list with the column enabled.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Find a WO with nothing waiting to receive.
 2. Read its Waiting on Parts cell.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. The cell shows '—' with no clickable link.</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R3)</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Require Review Before Completion is ON and saved.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Open a work order with approved lines.
 2. Start completion.
 3. Observe that the review flow is used.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review ON, completing routes into the review flow rather than completing directly.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R1)</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON.
 3. A work order with approved lines is ready to complete.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
 2. Read the wizard's primary CTA label.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. The primary CTA reads 'Complete &amp; Send to Review' (Send to Review).</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R2)</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON.
 3. A work order missing mileage/hours/VIN is ready to complete.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. Start completion and reach the Details step.
 2. Note which vehicle fields are collected.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>1. The Details step collects mileage and engine hours only.
 2. VIN is NOT collected here; it is captured later by the reviewer in the Mark Reviewed dialog.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R3)</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON with a part-bearing work order.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Start completion and click Receive Parts.
 2. Observe the destination.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. Receive Parts opens the shared receive page (not an inline modal).</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R4)</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order with approved lines is in the completion wizard.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete &amp; Send to Review.
 2. Observe the work order status and banner.
 3. Check the lines state and inventory pick state.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>1. The work order status becomes Review (amber).
 2. A 'Ready for Review' / 'Sent for review' indication is shown.
 3. Lines lock to Complete and inventory is auto-picked.</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R5 / R6)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Review state.</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Click Mark Reviewed.
 2. Observe the VIN field.
 3. Clear the VIN and check the Confirm Review button, then enter a VIN.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>1. The Mark Reviewed dialog exposes a VIN field (input_review_vin), required if missing.
 2. Confirm Review is disabled until a VIN is present.
 3. With a VIN, Confirm Review is enabled.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 / R10)</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order with an inventory line just went to Review.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order in Review state.
 2. Check the line states.
 3. Check whether inventory was auto-picked.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>1. Lines are locked to Complete.
 2. Inventory has been auto-picked.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R6)</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Review with the Mark Reviewed dialog filled (VIN present).</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. Click Confirm Review.
 2. Observe the resulting work order state.
 3. Look for a separate final 'Complete Work Order' action.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. After Confirm Review the sign-off completes and the work order moves directly Review -&gt; Complete.
 2. There is no distinct 'Reviewed' holding state and no separate final 'Complete Work Order' click.</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R5 / R8 (distinct Reviewed state))</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. A role with Review Work Orders and a role without it both exist.
 2. A work order is in Review state, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as a role without Review Work Orders and open the work order in Review.
 2. Confirm Mark Reviewed is disabled with 'Awaiting review'.
 3. Sign in as a role with Review Work Orders (system defaults grant it broadly; it can be limited to manager/foreman via custom roles) and confirm Mark Reviewed is available.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. A role without the Review Work Orders permission sees Mark Reviewed disabled with an 'Awaiting review' indicator.
 2. A role with the Review Work Orders permission can Mark Reviewed and sign off.
-3. The user who completed / sent the work order to review cannot Mark Reviewed even with the permission; a different qualified reviewer can.</t>
-        </is>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
+3. A user who holds the Review Work Orders permission may Mark Reviewed a work order they completed themselves — self-review is allowed in v1 with NO reviewer != completer identity restriction (the gate is purely the permission).</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 (role-gating))</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. Open the Mark Reviewed dialog.
 2. Confirm a required VIN / Serial # field (Confirm disabled until VIN entered).
 3. Confirm there is no review note field, then complete the sign-off.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>1. The Mark Reviewed dialog shows a VIN / Serial # field that is required (Confirm Reviewed is disabled until VIN is entered).
 2. There is no review note field on the dialog.
 3. The sign-off completes using the VIN / Serial # only.</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 (VIN required, no note))</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Reviewed state (or a Review state before sign-off for the invoicing-block check).</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Before sign-off, attempt to invoice the work order.
 2. Complete the review sign-off (Confirm Review).
 3. Confirm the work order becomes Complete (invoice-ready).</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. Invoicing is blocked until the work order is reviewed.
 2. After sign-off the work order moves directly Review -&gt; Complete (invoice-ready), with no separate final Complete Work Order click.</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R8)</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. At least one work order is in Review state.</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work Orders list.
 2. Look for a 'Ready for Review' filter or column.
 3. Confirm work orders in Review appear in it.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>1. A 'Ready for Review' filter/column lists work orders awaiting review.</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R9)</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order has one unapproved line.</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete &amp; Send to Review.
 2. Attempt to send with an unapproved line.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>1. Send to Review is blocked with the existing approve-line error while any line is unapproved.</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R11)</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order has inventory and special-order cores.</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. Resolve inventory cores in the completion modal (after Pick) before Send to Review.
 2. For required-invoice, resolve special-order cores after the Receive round-trip before Send to Review; for optional-invoice, resolve at the Create Invoice gate after sign-off.
 3. Attempt to invoice before both Reviewed and cores are resolved.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>1. Inventory cores are resolved before Send to Review.
 2. Special-order cores follow the vendor-invoice rules.
 3. Invoicing is blocked until the WO is Reviewed AND all cores are resolved.</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R Core parts / invoicing block)</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Verify the Require Review default for new vs existing orgs matches the agreed cohort rule</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. A newly-created org and an existing org are available.
 2. Signed in as Admin for each.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Check the Require Review default on a brand-new org.
 2. Check that existing orgs keep today's behavior (backfilled).</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. A brand-new org shows the Require Review setting in its default state, and existing orgs keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R Open (default))</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You are on the Create Work Order form (/workorders → Create).</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Open the Create Work Order form.
 2. Read the primary button label.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. The primary button reads 'Create Work Order'.</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R1)</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order requiring mileage/VIN is being completed.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Observe where required fields are collected.
 3. Confirm the tech story is handled by its own flow, not inside this modal.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr">
         <is>
           <t>1. Required fields (mileage / VIN when required) are collected in a centralized center modal.
 2. The tech story is NOT part of this modal (Story 17 handles it separately).</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R2)</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has just been completed.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. Read the success screen.
 2. Confirm WO number, total, Done and Go to Invoice.
 3. Confirm the invoice number is shown on the Finance step, not the success screen.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>1. The success screen shows the WO number and total with Done and Go to Invoice.
 2. The invoice number appears on the Finance step, not on the success screen.</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R3)</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completion modal is open.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. Trigger the close-confirmation modal.
 2. Click Close (prominent/red) and observe.
 3. Trigger it again and click Cancel (text link, far left) and observe.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. Close (prominent/red button) closes the confirmation modal only, discards nothing (no discard warning), and stays on the work order.
 2. Cancel (text link, far left) closes the modal and returns to the previous screen.
 3. Other consumers of the shared confirmation dialog keep their existing action labels.</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R4)</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. A role with the App Settings permission (e.g. Admin) and a role without it (e.g. Service Advisor or Technician) both exist.
 2. You can sign in as each.</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as a role with App Settings and open and modify /administration/settings → Work Orders.
 2. Sign in as a role without App Settings and attempt to open and modify the same page.
 3. As the role without App Settings, attempt to save a Work Order settings change directly (API), and note the response.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can view and modify the Work Order settings page.
 2. A role without App Settings cannot open or change the Work Order settings.
 3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>SV-7696 (S1 AC / §8 Permissions)</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for several roles exist.
 2. A work order ready to complete exists.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to complete a work order.
 2. Record which roles can and cannot.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. Roles with Work Orders: Create &amp; Edit plus WO Lines: Create &amp; Edit and Full View (needed to approve all lines) can complete a work order: Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
 2. Technician and Parts Tech cannot complete (Technician cannot approve lines in Tech View and/or lacks Work Orders: Create &amp; Edit; Parts Tech is a receiver, not a completer).
 3. Office, Sales Rep and Time Clock cannot complete a work order.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>§8 Permissions</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for several roles exist.
 2. The Bulk Receive flow is available (Story 7/8 built).</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to reach and use Bulk Receive.
 2. Record the outcomes.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
 2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot receive.
 3. Sales Rep and Time Clock cannot reach Bulk Receive.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>§8 Permissions</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for roles with and without Review Work Orders exist.
 2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to Mark Reviewed.
 2. Record which roles can and cannot.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. Mark Reviewed (review sign-off) requires the Review Work Orders permission; system defaults grant it broadly, and it can be narrowed to manager/foreman via custom roles.
 2. A role without Review Work Orders sees Mark Reviewed disabled with an 'Awaiting review' indicator.
-3. The user who completed / sent the work order to review cannot Mark Reviewed it; a different user who holds Review Work Orders can sign off.</t>
-        </is>
-      </c>
-      <c r="H137" s="2" t="inlineStr">
+3. A user who holds the Review Work Orders / Mark Reviewed permission may Mark Reviewed a work order they completed themselves — self-review is allowed in v1. There is NO reviewer != completer identity restriction; the gate is purely the permission.</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 / §8 role-gating review)</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. An Office / read-only credential (no Order Parts) exists.
 2. A WO-originated PO exists, plus a fulfilled PO.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as an Office / read-only user.
 2. Open the PO list and detail.
 3. Confirm the Receive action is not shown, and confirm it is also absent on a fulfilled PO.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or PO detail.
 2. Receive is also hidden for fulfilled (already-received) POs.</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R3)</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. Signed in with API access.
 2. A relevant Simple-Flow setting (e.g. Require Vendor Invoice Number) is ON.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. As a role that lacks the mapped permission, confirm the gated setting/action is hidden or unavailable in the UI.
 2. Attempt the same setting change directly via the API (bypassing the UI) as that role, and note the response.
@@ -7156,7 +7219,7 @@
 4. As a role that has only Work Orders: Create &amp; Edit, attempt to receive onto a work order and note the response.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. UI gating is the pass criterion for v1: a role without the mapped permission does not see or cannot use the gated setting/action in the UI.
 2. The Simple-Flow settings atom is enforced at the backend too — the unauthorized settings request is rejected.
@@ -7164,105 +7227,56 @@
 4. Because several work-order atoms collapse to the same backend role pair, any role with Work Orders: Create &amp; Edit can receive onto / act on a work order via the API (documented OR of ROLE_DELIVERY_CREATE_AND_EDIT, ROLE_WORK_ORDER_PART_CREATE and ROLE_WORK_ORDER_CREATE_AND_EDIT).</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>§8 BE enforcement</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for roles with and without Review Work Orders exist.
 2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>1. Confirm that only roles holding Review Work Orders can sign off, and roles without it cannot.
-2. Confirm the user who completed / sent the work order to review cannot sign it off.</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>1. Confirm that only roles holding Review Work Orders can sign off, and roles without it cannot.</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. Review sign-off is governed by the Review Work Orders custom-role permission (it is NOT open to all users for v1).
-2. The permission gates the Mark Reviewed action, and the reviewer-not-completer rule is enforced (the completer cannot sign off).</t>
-        </is>
-      </c>
-      <c r="H140" s="2" t="inlineStr">
+2. The permission gates the Mark Reviewed action (a role without Review Work Orders cannot sign off; a role with it can).
+3. A user who holds the Review Work Orders permission may sign off a work order they completed themselves — self-review is allowed in v1 with NO reviewer != completer identity restriction (the gate is purely the permission).</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>§8 role-gating review</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Permissions</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>1. Two different users who both hold the Review Work Orders permission exist.
-2. User A has completed / sent a work order to review; it is in Review state.</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>1. Sign in as User A (who sent the work order to review) and open the work order in Review.
-2. Attempt to Mark Reviewed.
-3. Sign in as User B (a different user who holds Review Work Orders) and Mark Reviewed.</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>1. User A cannot Mark Reviewed the work order they completed / sent to review; the action is blocked or disabled.
-2. User B, a different user who holds the Review Work Orders permission, can Mark Reviewed and sign off.
-3. The reviewer must be a different person from the completer.</t>
-        </is>
-      </c>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>SV-7870 (R7 (reviewer != completer))</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -7271,78 +7285,127 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>1. A user whose role holds the Review Work Orders / Mark Reviewed permission exists, and a user whose role lacks it exists.
+2. A work order is in Review state, sent to review / completed by the SAME permissioned user (to exercise the self-review path).</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>1. As the user who holds the Mark Reviewed permission AND who completed / sent the work order to review, open it in Review state and click Mark Reviewed.
+2. Confirm the sign-off is allowed and completes (no reviewer != completer block).
+3. As a user whose role does NOT hold the Mark Reviewed permission, open a work order in Review and check the Mark Reviewed control.</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>1. A user who holds the Review Work Orders / Mark Reviewed permission CAN Mark Reviewed a work order they completed themselves — self-review is allowed in v1 (there is NO reviewer != completer identity restriction).
+2. A user whose role does NOT hold the Mark Reviewed permission cannot sign off — the Mark Reviewed control is disabled with an 'Awaiting review' indicator.
+3. The only gate on Mark Reviewed is the Review Work Orders permission; who completed the work order is irrelevant.</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (R7 (review sign-off) — self-review permission-gated (identity rule NOT in v1))</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
           <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. A Technician credential exists (WO Lines: Create &amp; Edit, no See Financial Data).
 2. An open work order with a line is available.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the Technician and open the work order line.
 2. Attempt to add a vendorless / no-part-number part (description + quantity + sell price).</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. The Technician cannot add a vendorless / no-part-number part.
 2. The mandatory sell price cannot be entered without See Financial Data, so the add is prevented.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5 / §9 (See Financial Data gate))</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for each system role exist (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Technician, Parts Manager, Parts Tech, Office, Sales Rep, Time Clock).
 2. A work order ready to complete is available.</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. For each role, open the work order and check whether the Complete Work Order action is available and usable.
 2. Record the result per role against the checklist below.
@@ -7350,537 +7413,494 @@
 4. Roles expected NOT to be able to complete: Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. Complete Work Order is available for Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
 2. Complete Work Order is NOT available for Technician, Parts Tech, Office, Sales Rep or Time Clock.
 3. Technician and Parts Tech are blocked because they cannot approve lines and/or lack Work Orders: Create &amp; Edit; Office is view-only; Sales Rep and Time Clock have no work-order edit access.</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>§9 per-role completion matrix</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage is ON and the work order has no mileage.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave mileage empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until mileage is entered.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>SV-7697, SV-7698, SV-7699 (S2-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. VIN is required for this org's completion and the work order has no VIN.
-3. Require Review is OFF (VIN is collected at completion in the non-review flow).</t>
-        </is>
-      </c>
-      <c r="F145" s="2" t="inlineStr">
+3. Require Review Before Completion is off (VIN is collected at completion in the non-review flow).
+4. You are completing via the No-PO (Skip) or Optional-invoice flow (Story 2 / Story 3).</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave VIN empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>1. Completion is blocked until the VIN is entered.</t>
-        </is>
-      </c>
-      <c r="H145" s="2" t="inlineStr">
-        <is>
-          <t>SV-7698, SV-7710 (S15-R2 / S3-R3)</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>1. In the No-PO or Optional-invoice completion flow (Require Review off), completion is blocked until the required VIN is entered.
+2. VIN is no longer collected in the required-invoice (Story 4) completion modal, and when Require Review is on it is captured by the reviewer in the Mark Reviewed dialog (Story 16) — so this at-completion VIN gate applies only to the non-review No-PO / Optional-invoice flow.</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>SV-7698, SV-7699, SV-7710 (S15-R2 / S3-R3 / S4-R3)</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Engine Hours is ON and the work order has no engine hours.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave engine hours empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until engine hours are entered.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open on a line.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Leave the story textarea empty.
 2. Check the Next/Continue button.
 3. Type any text and check again.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. With the textarea empty, Next/Continue is disabled.
 2. After typing text, Next/Continue becomes enabled.</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R4)</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is ON and a part is being received.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. On the receive surface, leave the vendor invoice number empty.
 2. Attempt to receive.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor invoice number.
 2. Once an invoice number is entered, receiving is allowed.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R5 / §4)</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing part is on a receive surface.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to receive with no vendor.
 2. Attempt to receive with a vendor but no part number.
-3. Provide both and receive.</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr">
+3. Attempt to receive with a vendor and part number but no cost / sell price.
+4. Provide all three and receive.</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor.
 2. Receiving is blocked without a part number.
-3. Receiving succeeds only with both.</t>
-        </is>
-      </c>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>SV-7705, SV-7707, SV-7708 (S10 / S12-R2 / S13)</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+3. Receiving is blocked without a cost / sell price.
+4. Receiving succeeds only once the vendor, part number, and cost / sell price are all present.</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>SV-7705, SV-7707, SV-7708 (S10 / S12-R2 / S13-R6 / S13-R7)</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open on a WO with no VIN on the asset.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Clear the VIN field.
 2. Check the Confirm Review button.
 3. Enter a VIN and check again.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Review is disabled while VIN is empty.
 2. Confirm Review enables after a VIN is entered.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7)</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part-bearing work order had completion started and cancelled once.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Cancel the first completion attempt.
 2. Start and complete again.
 3. Inspect the POs.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. No duplicate POs are created on the second attempt.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>SV-7698 (S3-R9 (idempotency))</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid work order is on a receive surface.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the invoiced/paid WO part.
 2. Try to edit the sell field.
 3. Hover the lock icon.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. The sell field is locked (not editable).
 2. A lock icon and tooltip 'Locked — this part is already invoiced or paid' are shown.
 3. Only cost remains editable.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R7 / §4 field locking)</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same vendor are being received.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. Enter the same invoice number on both POs.
 2. Receive both.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. The reused invoice number is accepted (uniqueness is relaxed).
 2. Both POs receive successfully.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R3 / §4 (uniqueness relaxed))</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>Verify the approve-line error text appears when completing with an unapproved line</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A work order has one unapproved line and all other gates satisfied.</t>
-        </is>
-      </c>
-      <c r="F154" s="2" t="inlineStr">
-        <is>
-          <t>1. Click Complete Work Order.
-2. Read the error shown at the final confirm.</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>1. The existing 'you need to approve the line to complete the work order' error is shown.
-2. Completion does not proceed until the line is approved.</t>
-        </is>
-      </c>
-      <c r="H154" s="2" t="inlineStr">
-        <is>
-          <t>Key Decision (line approval)</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
@@ -7889,425 +7909,473 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>Verify an unapproved line blocks completion — required-invoice shows a disabled Complete button with a tooltip; other flows show the approve-line error</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order has one unapproved line and all other gates satisfied.</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>1. In the required-invoice (Story 4) flow, start completion and observe the Complete Work Order button, then hover it.
+2. In the No-PO / Optional-invoice (Stories 2/3) flow, click Complete Work Order and read the message shown.</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>1. In the required-invoice (Story 4) flow, the Complete Work Order button is disabled with a tooltip describing the reason and naming the line that needs approval.
+2. In the No-PO / Optional-invoice (Stories 2/3) and review-on (Story 16) flows, the existing 'you need to approve the line to complete the work order' error is shown and the button stays active.
+3. In every flow, completion does not proceed until the line is approved.</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>SV-7698, SV-7699 (S4-R8 / S3-R9 / Key Decision (line approval))</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has an in-stock inventory part; its on-hand quantity is noted.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order via the simple (skip) path.
 2. Check the part's on-hand quantity and Part History.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. The in-stock part's on-hand quantity decrements.
 2. A Part History entry is written.
 3. The skip path's status setter does not bypass inventory movement / Part History / catalog / delivery.</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 1</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create Purchase Orders is OFF.
 3. A work order with a vendor/found part exists.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order with Create POs OFF.
 2. Check for any PO, vendor bill, AP sync.
 3. Check for any catalog/inventory sync of the vendor/found part.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. No PO, no vendor bill, no AP sync.
 2. No catalog/inventory sync (part is received at request time only).</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>§5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create POs is on and a work order has a receivable vendor part.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Receive the part via Accept Delivery.
 2. Check that a Delivery, then a Vendor Bill, then a QuickBooks sync occur.
 3. Repeat via the Bulk Receive surface (once built) and confirm it also syncs.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. Receiving creates a Delivery, then a Vendor Bill, then syncs to QuickBooks.
 2. Both receive surfaces sync the vendor bill (only complete-simple bypasses this).</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 2</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless / no-PN part exists on a work order.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Before adding a vendor/PN, check inventory and Part History for the part.
 2. Add a vendor and PN, then re-check.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. Before a vendor/PN, there is zero inventory interaction (no item, no history).
 2. After a vendor and PN are added, normal inventory handling applies.</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Check QuickBooks sync for the Vendor Missing PO.
 2. Provide a vendor and part number and re-check.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. While vendor/PN are missing, the PO is excluded from QuickBooks.
 2. Once both are provided, it becomes eligible for QuickBooks.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (§5 / S6-R3)</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a part with no cost recorded at completion.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order.
 2. Check the resulting cost/margin figures that flow to QuickBooks.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.
 2. For vendorless / no-part-number parts the mandatory sell price is captured at add time behind the See Financial Data gate, so a completing user has a sell figure and $0-cost margins are avoided.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>§8 (cost at completion)</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completed work order is ready to invoice.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Create the invoice.
 2. Check for the Journal Entry / Inventory sync to QuickBooks.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. The Journal Entry / Inventory sync to QuickBooks fires on invoice creation.
 2. This sync is not dependent on a PO existing.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part transitions to inventory-tracked (e.g. a part number is added and it is received).</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. Add a part number to a previously untracked part and receive it.
 2. Open the item's Part History.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. Part History is preserved / created for the now inventory-tracked part.</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 3</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>Investigate: Part Sales unaffected by the shared order/status logic (requested -&gt; orderable/waiting-to-receive)</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>1. PLACEHOLDER for a new V2.4 §8 open question (needs BE investigation).</t>
-        </is>
-      </c>
-      <c r="F163" s="2" t="inlineStr">
-        <is>
-          <t>1. Investigation pending — steps to be defined once dev confirms whether the shared order/status logic touches Part Sales.</t>
-        </is>
-      </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>1. OPEN / NEEDS INVESTIGATION — expected result to be defined after dev confirmation. Keep Part Sales unchanged unless the shared logic forces a change (V2.4 §8).</t>
-        </is>
-      </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>§8 open question (Part Sales impact — BE investigation)</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr"/>
       <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Investigate: Part Sales unaffected by the shared order/status logic (requested -&gt; orderable/waiting-to-receive)</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>1. PLACEHOLDER for a new V2.4 §8 open question (needs BE investigation).</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>1. Investigation pending — steps to be defined once dev confirms whether the shared order/status logic touches Part Sales.</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>1. OPEN / NEEDS INVESTIGATION — expected result to be defined after dev confirmation. Keep Part Sales unchanged unless the shared logic forces a change (V2.4 §8).</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>§8 open question (Part Sales impact — BE investigation)</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Verify the Work Order settings page shows all Simple-Flow toggles in order with new vs existing visually distinct</t>
+          <t>Verify the Work Orders settings tab lists all Work Order setting toggles in order</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -523,9 +523,10 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. The page lists these toggles: Auto-approve Lines, Require Vendor Invoice Number, Require Review Before Completion, Require Tech Story, Require Mileage, Require Engine Hours, Automatically Pick Inventory Parts.
-2. Each toggle shows an On/Off control and its current state.
-3. No 'operating mode' (Full/Simple) selector appears anywhere on the page.</t>
+          <t>1. The Work Orders tab lists these toggles top to bottom: Auto-approve Lines, Require Vendor Invoice Number, Require Review Before Completion, Require Tech Story, Require Mileage, Require Engine Hours, Automatically Pick Inventory Parts.
+2. Each toggle shows an On/Off switch and its current state, with a short description underneath.
+3. There is no 'operating mode' (Full vs Simple) selector anywhere on the page.
+4. The toggles appear as one plain list (there is no special 'new' styling separating them from older settings).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -565,16 +566,16 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1. Scan the whole Work Orders settings tab.
-2. Look specifically for a 'Mode' / 'Full vs Simple' selector.
-3. Look specifically for a 'Require VIN' / 'VIN required' toggle.</t>
+          <t>1. Read the whole Work Orders settings tab top to bottom.
+2. Look for a 'Mode' or 'Full vs Simple' selector.
+3. Look for a 'Require VIN' or 'VIN required' toggle.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. There is no operating-mode (Full/Simple) selector.
-2. There is no 'Require VIN' toggle in the Work Order settings.
-3. Behavior is driven only by the individual setting toggles.</t>
+          <t>1. There is no operating-mode (Full vs Simple) selector.
+2. There is no 'Require VIN' toggle among the Work Orders settings.
+3. Behavior is driven only by the individual toggles listed on the tab.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -588,7 +589,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Verify a 'Create Purchase Orders' toggle exists and, when off, hides the Vendor Invoice sub-setting</t>
+          <t>Verify a 'Create Purchase Orders' toggle exists on the Work Orders tab and controls the Vendor Invoice setting</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -614,16 +615,16 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Locate a 'Create purchase orders' toggle.
-2. Turn it Off and observe the Vendor Invoice Number setting.
-3. Turn it On and observe the Vendor Invoice Number setting.</t>
+          <t>1. Look on the Work Orders settings tab for a 'Create Purchase Orders' toggle.
+2. If it exists, turn it Off and watch the Require Vendor Invoice Number setting.
+3. Turn it back On and watch the Require Vendor Invoice Number setting.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. EXPECTED PER SPEC (currently NOT met): a 'Create purchase orders' toggle exists, default On, with helper text.
-2. With Create POs Off, the Vendor Invoice (Optional/Required) sub-setting is hidden and no vendor-invoice capture happens in completion.
-3. With Create POs On, the Vendor Invoice (Optional/Required) sub-setting appears with helper text.</t>
+          <t>1. A 'Create Purchase Orders' toggle is present on the Work Orders tab (default On).
+2. With 'Create Purchase Orders' Off, the Require Vendor Invoice Number setting is hidden.
+3. With 'Create Purchase Orders' On, the Require Vendor Invoice Number setting is shown.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -670,9 +671,9 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. The 'Require Vendor Invoice Number' toggle is present.
-2. Helper text reads (approximately): 'When on, parts and a vendor invoice number are required to complete a work order. When off, complete now and receive parts later.'
-3. Its state maps to requireVendorInvoiceNumber in GET /api/organizations/settings.</t>
+          <t>1. The 'Require Vendor Invoice Number' toggle is present on the Work Orders tab.
+2. Its helper text reads exactly: 'When on, parts and a vendor invoice number are required to complete a work order. When off, complete now and receive parts later.'
+3. Its On/Off state matches requireVendorInvoiceNumber in GET /api/organizations/settings.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -813,15 +814,15 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1. Read the Require Tech Story, Require Mileage, Require Engine Hours and Automatically Pick Inventory Parts toggles.
-2. Compare each shown state against the API settings object.</t>
+          <t>1. Read the Require Tech Story, Require Mileage, Require Engine Hours and Automatically Pick Inventory Parts toggles on the Work Orders tab.
+2. Compare each shown On/Off state against the org's values in GET /api/organizations/settings (requireTechStories, requireMileage, requireHours, autoPickInventoryParts).</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. Each existing toggle is shown.
-2. Each toggle's On/Off state matches the org's current API value.
-3. States display without altering the values.</t>
+          <t>1. Each of these four toggles is shown on the Work Orders tab.
+2. Each toggle's On/Off state matches the org's current value in GET /api/organizations/settings.
+3. Simply viewing the tab does not change any value.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -867,9 +868,9 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. Auto-approve Lines = OFF (spec default — authoritative).
-2. Create Purchase Orders = ON.
-3. Vendor Invoice = REQUIRED.</t>
+          <t>1. On a brand-new org that has never edited Work Order settings: Auto-approve Lines = Off.
+2. Create Purchase Orders = On.
+3. Require Vendor Invoice Number = On (required).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1009,16 +1010,16 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1. Sign in as the user without App Settings.
-2. Attempt to open /administration/settings → Work Orders tab.
-3. Attempt to change and save a Work Order setting, including a direct API save.</t>
+          <t>1. Sign in as a role without the App Settings permission (e.g. Technician).
+2. Try to open /administration/settings and reach the Work Orders tab.
+3. Try to save a Work Order setting change (including a direct API save via POST /api/organizations/settings/change).</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. A role without the App Settings permission cannot reach the Work Order settings, or sees them read-only.
-2. That role cannot save changes to Work Order settings.
-3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
+          <t>1. The role without App Settings cannot reach the Work Orders settings (redirected away by the app).
+2. That role cannot save Work Order settings.
+3. The backend rejects a Work Order settings save from that role with HTTP 403.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1112,8 +1113,8 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. Saving persists the settings changes.
-2. Dirty-state gating (disabling Save until a change is made) is NOT required in v1 — Save being always enabled is acceptable (low-priority polish, not a blocker).</t>
+          <t>1. Saving changes with the 'Save Settings' button persists the settings.
+2. It is acceptable in v1 for 'Save Settings' to stay enabled even with no unsaved change (there is no dirty-state gating; this is a low-priority polish, not a blocker).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1160,9 +1161,9 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. The 'Require Review Before Completion' toggle is present on the page (not prototype-only).
-2. With it On, completing a work order routes into the review flow (Story 16).
-3. The completion CTA relabels to 'Complete &amp; Send to Review'.</t>
+          <t>1. The 'Require Review Before Completion' toggle is present on the Work Orders tab.
+2. With it On, completing a ready work order uses the review flow: the primary action becomes 'Send To Review' and the work order goes to 'Review' with a 'Ready for Review' indicator instead of completing immediately.
+3. (For a work order that still has parts to order or receive, the button stays 'Complete Work Order' and opens the completion wizard first.)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1208,8 +1209,8 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. Every toggle has a short helper description.
-2. Each description explains the On and Off behavior in plain language.</t>
+          <t>1. Every Work Orders toggle has a short description under it.
+2. Each description explains what turning the toggle On or Off does, in plain language.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1503,9 +1504,9 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. No PO is created.
-2. No vendor bill and no AP sync occur.
-3. No catalog/inventory sync for the vendor/found part; it is received at request time only.</t>
+          <t>1. No purchase order is created for the vendor part.
+2. No vendor bill and no accounts-payable sync happen.
+3. The vendor/found part is received at request time only (no catalog or inventory sync).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1961,7 +1962,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice completion modal collects the required vehicle fields (mileage and engine hours; VIN only when Require Review is off) when missing</t>
+          <t>Verify the completion modal collects the missing required vehicle fields (Mileage and Engine Hours; no VIN field in the modal)</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1996,10 +1997,10 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. When Require Review is off, the modal collects the missing required vehicle fields: mileage, VIN and engine hours.
-2. When Require Review is on, VIN is not collected here — it is captured later by the reviewer in the Mark Reviewed dialog (Story 16) — and the modal collects only mileage and engine hours.
-3. Continuation is blocked until the required fields are supplied.
-4. Tech story is handled separately (Story 17), not inside this step.</t>
+          <t>1. When required vehicle fields are missing, the completion Details modal collects Mileage and Engine Hours.
+2. There is no VIN field in the completion modal (VIN validity is shown by the 'Valid VIN Required' chip on the work order header; for a review-on work order the VIN is captured later by the reviewer in the Mark Reviewed dialog).
+3. You cannot continue until the required fields are supplied (an empty required field shows a 'required field' error).
+4. Tech story is handled separately as a line requirement, not inside this step.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2245,10 +2246,10 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. In the required-invoice (Story 4) flow, an unapproved line leaves the Complete Work Order button disabled.
-2. A tooltip on the disabled button describes the reason, naming the line that needs approval.
-3. The button enables once all lines are approved.
-4. In the No-PO / Optional-invoice (Stories 2/3) and review-on (Story 16) flows the same unapproved line instead surfaces the existing 'you need to approve the line to complete the work order' error on Complete (the button stays active).</t>
+          <t>1. In the required-invoice flow (Require Vendor Invoice Number ON), a line still in Needs Approval leaves the Complete Work Order button disabled.
+2. Hovering the disabled Complete Work Order button shows a tooltip explaining why, naming the line that needs approval.
+3. The button becomes enabled once every line is approved.
+4. In the optional-invoice flow (Require Vendor Invoice Number off) and when Require Review is on, the same unapproved line instead shows the existing message 'you need to approve the line to complete the work order' when you click Complete (the button stays active).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2298,9 +2299,9 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. In the required-invoice (Story 4) flow the manually unapproved line leaves the Complete Work Order button disabled with a tooltip naming the line that needs approval — this holds even though Auto-approve Lines is ON.
-2. After re-approving all lines, the Complete Work Order button enables and completion proceeds.
-3. In the No-PO / Optional-invoice (Stories 2/3) and review-on (Story 16) flows the same unapproved line instead surfaces the existing 'you need to approve the line to complete the work order' error on Complete.</t>
+          <t>1. In the required-invoice flow (Require Vendor Invoice Number ON), a manually un-approved line leaves the Complete Work Order button disabled with a tooltip naming the line that needs approval — even though Auto-approve Lines is ON.
+2. After re-approving every line, the Complete Work Order button enables and completion proceeds.
+3. In the optional-invoice flow (Require Vendor Invoice Number off) and when Require Review is on, the same unapproved line instead shows the existing message 'you need to approve the line to complete the work order' when you click Complete.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3141,7 +3142,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify the tech-story modal has a text box for typing the story</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3167,13 +3168,15 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>1. Inspect the textarea element.
-2. Confirm its test id / data attribute.</t>
+          <t>1. Open the tech-story modal on a line.
+2. Locate the text box where the story is typed.
+3. Type a story into the text box.</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. The textarea carries the test id input_tech_story.</t>
+          <t>1. The tech-story modal has a text box (textarea) for the story.
+2. The story text you type is accepted in the box.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3755,8 +3758,8 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. The PO detail offers a vendor selection option (Story 13).
-2. It offers a way to enter/edit the part number (Story 10).</t>
+          <t>1. The Vendor Missing PO detail offers a way to select a vendor.
+2. It offers a way to enter or edit the part number.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4195,7 +4198,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify the Bulk Receive page has a 'Back To Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4221,13 +4224,13 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>1. Locate the top-left 'Back to Purchase Orders' link.
+          <t>1. Locate the top-left 'Back To Purchase Orders' link.
 2. Click it.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1. A 'Back to Purchase Orders' link is present top-left.
+          <t>1. A 'Back To Purchase Orders' link is present top-left.
 2. Clicking it returns to the PO list.</t>
         </is>
       </c>
@@ -4536,7 +4539,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify Receive All receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4563,7 +4566,7 @@
       <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Reduce one part's received quantity below its ordered quantity.
-2. Click Receive all.
+2. Click Receive All.
 3. Confirm the receipts.</t>
         </is>
       </c>
@@ -4681,7 +4684,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify each vendor group has an 'Apply to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4707,7 +4710,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>1. Locate the 'Apply invoice to selected POs' control under the vendor name.
+          <t>1. Locate the 'Apply to selected POs' control under the vendor name.
 2. With no invoice # and no PO selected, confirm it is disabled.
 3. Enter an invoice # and select at least one PO under that vendor.</t>
         </is>
@@ -5057,10 +5060,10 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1. Receiving is blocked without a part number.
-2. For vendor-missing, receiving is also blocked without a vendor.
-3. Receiving is blocked until a missing cost / sell price is entered.
-4. On an invoiced/paid WO, sell stays locked and cost stays editable while the block applies.</t>
+          <t>1. A part cannot be received without a part number.
+2. A vendor-missing part cannot be received without a vendor.
+3. A part cannot be received without a cost / sell price.
+4. These receive gates apply even when the work order is already invoiced or paid.</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5389,19 +5392,18 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>1. Attempt to receive without a vendor set.
-2. Attempt to receive without a part number.
-3. Attempt to receive without a cost / sell price.
-4. Attempt to receive without a vendor invoice number.</t>
+          <t>1. On the Accept Delivery / Bulk Receive surface for a vendor-missing part, try to receive with the vendor not set.
+2. Set the vendor but leave the part number empty and try to receive.
+3. Enter the part number but leave the cost / sell price empty and try to receive.
+4. Enter the vendor invoice number and all of the above, then receive.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>1. Receiving is gated until a vendor is set.
-2. Receiving is gated until the missing part number is entered.
-3. Receiving is gated until a missing cost / sell price is entered.
-4. Receiving is gated until a vendor invoice number is captured.
-5. On Accept Delivery, cost is editable when $0 or missing (parity with Bulk Receive); the sell-price lock rule is unchanged.</t>
+          <t>1. Receiving is blocked until a vendor is set.
+2. Receiving is blocked until a part number is entered.
+3. Receiving is blocked until a cost / sell price is entered.
+4. Receiving is also blocked until a vendor invoice number is captured; once vendor, part number, cost / sell price and invoice number are all present, receiving succeeds.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5783,10 +5785,8 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1. The vendor auto-assigns with no prompt.
-2. The QuickBooks 'vendor missing' flag clears.
-3. Assigning the vendor alone does not enable Receive — the part number and the cost / sell price are still required.
-4. Receiving becomes enabled only once the vendor, the part number, and the cost / sell price are all present (plus the vendor invoice number).</t>
+          <t>1. Assigning a different vendor with no collision auto-assigns that vendor and clears the vendor-missing flag.
+2. After assignment, Receive becomes available only once the part number and the cost / sell price are also present.</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -5882,9 +5882,8 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1. While the cost / sell price is missing, the user gets an indication to enter one.
-2. Receiving is blocked while the cost / sell price is missing.
-3. Receiving becomes enabled once the cost / sell price is entered (with the vendor, part number and vendor invoice number also present).</t>
+          <t>1. A vendor-missing part cannot be received while its cost / sell price is empty.
+2. Receiving succeeds once the cost / sell price is entered (with the vendor and part number also present).</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -5931,8 +5930,8 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1. A 'Waiting on Parts' column is offered in the column selector (off by default).
-2. It shows the count of unreceived parts per work order across all statuses.</t>
+          <t>1. The Work Orders list column selector offers a 'Waiting on Parts' column (off by default).
+2. When enabled, it shows the count of unreceived parts per work order across all statuses.</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -5978,8 +5977,8 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>1. EXPECTED (built): clicking the count opens the receiving surface for the work order's first unreceived PO. In the current build this is the consolidated Bulk Receive page (/bulk-receive), which supersedes the legacy Accept Delivery screen for work-order POs.
-2. Receiving behaves as it does from the Bulk Receive page from there.</t>
+          <t>1. Clicking the count opens the receiving surface for the work order's first unreceived purchase order. In the current build this is the consolidated Bulk Receive page (/bulk-receive), which supersedes the legacy Accept Delivery screen for work-order POs.
+2. Receiving from there behaves as it does on the Bulk Receive page.</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6025,7 +6024,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>1. The cell shows '—' with no clickable link.</t>
+          <t>1. A work order with nothing to receive shows an em dash ('—') in the Waiting on Parts column, with no clickable link.</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6119,7 +6118,8 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1. The primary CTA reads 'Complete &amp; Send to Review' (Send to Review).</t>
+          <t>1. With Require Review Before Completion ON, a ready work order's primary action button reads 'Send To Review' (it replaces 'Complete Work Order').
+2. For a work order that still has parts to order or receive, the button reads 'Complete Work Order' and opens the completion wizard first.</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6166,8 +6166,8 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>1. The Details step collects mileage and engine hours only.
-2. VIN is NOT collected here; it is captured later by the reviewer in the Mark Reviewed dialog.</t>
+          <t>1. When Require Review is on, the completion Details step collects Mileage and Engine Hours only.
+2. There is no VIN field in the completion modal; VIN is captured later by the reviewer in the Mark Reviewed dialog.</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6309,9 +6309,9 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1. The Mark Reviewed dialog exposes a VIN field (input_review_vin), required if missing.
+          <t>1. The Mark Reviewed dialog shows a VIN / Serial # field, required if the work order is missing a valid VIN.
 2. Confirm Review is disabled until a VIN is present.
-3. With a VIN, Confirm Review is enabled.</t>
+3. Once a VIN is entered, Confirm Review is enabled.</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6741,7 +6741,8 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>1. A brand-new org shows the Require Review setting in its default state, and existing orgs keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
+          <t>1. On a brand-new org the Require Review Before Completion setting shows its default state.
+2. Existing orgs keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -6834,8 +6835,8 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>1. Required fields (mileage / VIN when required) are collected in a centralized center modal.
-2. The tech story is NOT part of this modal (Story 17 handles it separately).</t>
+          <t>1. The required vehicle fields (Mileage and Engine Hours) are collected in a centralized center modal titled 'Complete Work Order'.
+2. The tech story is NOT part of this modal (it is handled by its own line-level flow).</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7213,18 +7214,18 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>1. As a role that lacks the mapped permission, confirm the gated setting/action is hidden or unavailable in the UI.
-2. Attempt the same setting change directly via the API (bypassing the UI) as that role, and note the response.
-3. As a role that lacks the completion / review sign-off permission, attempt to complete a work order and to sign off a review directly via the API, and note the response.
-4. As a role that has only Work Orders: Create &amp; Edit, attempt to receive onto a work order and note the response.</t>
+          <t>1. As a role that lacks the mapped permission, confirm the gated setting or action is hidden or unavailable in the app.
+2. As that same role, try the same setting change directly through the API (bypassing the app) and note the response.
+3. As a role that lacks the completion or review sign-off permission, try to complete a work order and to sign off a review directly through the API and note the responses.
+4. As a role that only has Work Orders: Create &amp; Edit, try to receive parts onto a work order through the API and note the response.</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>1. UI gating is the pass criterion for v1: a role without the mapped permission does not see or cannot use the gated setting/action in the UI.
-2. The Simple-Flow settings atom is enforced at the backend too — the unauthorized settings request is rejected.
-3. The work-order completion and review sign-off atoms are NOT enforced at the backend — a direct API call from a role lacking the permission still succeeds. This passes for v1 on the UI restriction, but the API-level gap is a KNOWN ISSUE to fix; record the result as 'UI pass / API fail' so it stays on record.
-4. Because several work-order atoms collapse to the same backend role pair, any role with Work Orders: Create &amp; Edit can receive onto / act on a work order via the API (documented OR of ROLE_DELIVERY_CREATE_AND_EDIT, ROLE_WORK_ORDER_PART_CREATE and ROLE_WORK_ORDER_CREATE_AND_EDIT).</t>
+          <t>1. In the app, a role without the mapped permission does not see or cannot use the gated setting or action (this is the v1 pass criterion).
+2. The Work Order settings save is also blocked at the backend: the unauthorized API request is rejected with HTTP 403.
+3. Work order completion and review sign-off are NOT blocked at the backend today: a direct API call from a role lacking the permission still succeeds (HTTP 200). This still passes v1 on the app-level restriction, but the backend gap is a known issue to fix later — note it as 'app blocks / backend allows'.
+4. Because several work-order permissions share the same backend check, any role with Work Orders: Create &amp; Edit can receive parts onto a work order through the API.</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7505,14 +7506,15 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>1. Start completion.
-2. Leave VIN empty and try to proceed.</t>
+          <t>1. Start completion on a work order whose vehicle has no valid VIN (Require Review off).
+2. Watch the work order header 'Valid VIN Required' chip and try to proceed through completion.</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>1. In the No-PO or Optional-invoice completion flow (Require Review off), completion is blocked until the required VIN is entered.
-2. VIN is no longer collected in the required-invoice (Story 4) completion modal, and when Require Review is on it is captured by the reviewer in the Mark Reviewed dialog (Story 16) — so this at-completion VIN gate applies only to the non-review No-PO / Optional-invoice flow.</t>
+          <t>1. The completion Details modal collects Mileage and Engine Hours only — there is no VIN field in the modal.
+2. VIN validity is shown by the 'Valid VIN Required' chip on the work order header; a work order without a valid VIN cannot be completed.
+3. For a review-on work order the VIN is captured later by the reviewer in the Mark Reviewed dialog, not at completion.</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7693,18 +7695,18 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>1. Attempt to receive with no vendor.
-2. Attempt to receive with a vendor but no part number.
-3. Attempt to receive with a vendor and part number but no cost / sell price.
-4. Provide all three and receive.</t>
+          <t>1. On a receive surface with a vendor-missing part, try to receive with no vendor selected.
+2. Select a vendor but leave the part number empty and try to receive.
+3. Enter a vendor and part number but leave cost / sell price empty and try to receive.
+4. Provide vendor, part number and cost / sell price, then receive.</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>1. Receiving is blocked without a vendor.
-2. Receiving is blocked without a part number.
-3. Receiving is blocked without a cost / sell price.
-4. Receiving succeeds only once the vendor, part number, and cost / sell price are all present.</t>
+          <t>1. Receiving is blocked while no vendor is selected.
+2. Receiving is blocked while the part number is empty.
+3. Receiving is blocked while the cost / sell price is empty.
+4. Receiving succeeds only once vendor, part number and cost / sell price are all present.</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -7935,15 +7937,15 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>1. In the required-invoice (Story 4) flow, start completion and observe the Complete Work Order button, then hover it.
-2. In the No-PO / Optional-invoice (Stories 2/3) flow, click Complete Work Order and read the message shown.</t>
+          <t>1. With Require Vendor Invoice Number ON, open a work order that has one line still needing approval and start completion; look at the Complete Work Order button, then hover it.
+2. With Require Vendor Invoice Number off (or Require Review on), open a similar work order and click Complete Work Order; read the message shown.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>1. In the required-invoice (Story 4) flow, the Complete Work Order button is disabled with a tooltip describing the reason and naming the line that needs approval.
-2. In the No-PO / Optional-invoice (Stories 2/3) and review-on (Story 16) flows, the existing 'you need to approve the line to complete the work order' error is shown and the button stays active.
-3. In every flow, completion does not proceed until the line is approved.</t>
+          <t>1. With Require Vendor Invoice Number ON, the Complete Work Order button is disabled and hovering it shows a tooltip that explains why and names the line that needs approval.
+2. With Require Vendor Invoice Number off, or with Require Review on, the existing message 'you need to approve the line to complete the work order' is shown and the button stays active.
+3. In every case, completion does not proceed until the line is approved.</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8039,8 +8041,8 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>1. No PO, no vendor bill, no AP sync.
-2. No catalog/inventory sync (part is received at request time only).</t>
+          <t>1. No purchase order, vendor bill or accounts-payable sync is produced.
+2. No catalog or inventory sync happens (the part is received at request time only).</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -6085,7 +6085,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+          <t>Verify the completion action reads 'Send To Review' when Require Review is on</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -6112,14 +6112,14 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>1. Click Complete Work Order.
-2. Read the wizard's primary CTA label.</t>
+          <t>1. Open a work order that is ready to complete, with Require Review Before Completion turned on.
+2. Read the primary action button on the work order (and, for a work order that still has parts to receive, the heading of the dialog that opens).</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review Before Completion ON, a ready work order's primary action button reads 'Send To Review' (it replaces 'Complete Work Order').
-2. For a work order that still has parts to order or receive, the button reads 'Complete Work Order' and opens the completion wizard first.</t>
+2. For a work order that still has parts waiting to receive, clicking 'Send To Review' opens a dialog headed 'Complete &amp; Send to Review' that shows how many parts are waiting to receive and offers 'Receive Parts' and 'Send To Review'.</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Require Review is ON and a work order with approved lines is in the completion wizard.</t>
+2. Require Review is ON and a work order with approved lines is ready to send to review (for a work order with parts still to receive, the 'Complete &amp; Send to Review' dialog is open).</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>1. Click Complete &amp; Send to Review.
+          <t>1. Click Send To Review (the primary action button, or the 'Send To Review' button in the 'Complete &amp; Send to Review' dialog for a part-bearing work order).
 2. Observe the work order status and banner.
 3. Check the lines state and inventory pick state.</t>
         </is>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>SV-7870 (R5 / R8 (distinct Reviewed state))</t>
+          <t>SV-7870 (R5 / R8 (direct sign-off, no separate Complete))</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify all lines must be approved before Send To Review (the 'Send To Review' action is disabled until every line is approved)</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6640,13 +6640,13 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>1. Click Complete &amp; Send to Review.
-2. Attempt to send with an unapproved line.</t>
+          <t>1. Open the work order and locate the 'Send To Review' action while a line is still unapproved.
+2. Attempt to use Send To Review with the unapproved line.</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>1. Send to Review is blocked with the existing approve-line error while any line is unapproved.</t>
+          <t>1. The 'Send To Review' action cannot be used while any line is unapproved - the 'Send To Review' button is disabled until every line has been approved.</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -588,7 +588,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Verify a 'Create Purchase Orders' toggle exists and, when off, hides the Vendor Invoice sub-setting</t>
+          <t>Verify there is no 'Create Purchase Orders' toggle and the Vendor Invoice sub-setting always shows (POs always on)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -614,21 +614,19 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1. Locate a 'Create purchase orders' toggle.
-2. Turn it Off and observe the Vendor Invoice Number setting.
-3. Turn it On and observe the Vendor Invoice Number setting.</t>
+          <t>1. Look for a 'Create purchase orders' toggle in the Work Orders settings.
+2. Locate the Vendor Invoice (Optional/Required) setting.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. EXPECTED PER SPEC (currently NOT met): a 'Create purchase orders' toggle exists, default On, with helper text.
-2. With Create POs Off, the Vendor Invoice (Optional/Required) sub-setting is hidden and no vendor-invoice capture happens in completion.
-3. With Create POs On, the Vendor Invoice (Optional/Required) sub-setting appears with helper text.</t>
+          <t>1. There is no 'Create purchase orders' toggle — purchase orders are always created for vendor parts (the Create-POs setting and the No-PO/Skip flow were retired).
+2. The Vendor Invoice (Optional/Required) sub-setting always shows with its helper text.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>SV-7696 (S1-R2 (Create purchase orders))</t>
+          <t>SV-7696 (Story 1 / §4 (Create-POs setting retired — POs always on))</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -835,7 +833,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Verify first-use defaults on a brand-new org (auto-approve OFF, create POs ON, vendor invoice REQUIRED)</t>
+          <t>Verify first-use defaults on a brand-new org (auto-approve OFF, vendor invoice REQUIRED; no Create-POs setting)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -862,13 +860,13 @@
       <c r="F9" s="2" t="inlineStr">
         <is>
           <t>1. Open /administration/settings → Work Orders tab for the new org.
-2. Read the default state of Auto-approve Lines, Create Purchase Orders, and Vendor Invoice.</t>
+2. Read the default state of Auto-approve Lines and Vendor Invoice.</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>1. Auto-approve Lines = OFF (spec default — authoritative).
-2. Create Purchase Orders = ON.
+2. There is no Create Purchase Orders setting — purchase orders are always on.
 3. Vendor Invoice = REQUIRED.</t>
         </is>
       </c>
@@ -1228,7 +1226,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — Simple (Stories 3/4)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1262,7 +1260,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-7697 (S2-R1)</t>
+          <t>SV-7698, SV-7699 (Story 3/4 (streamlined completion — Complete button placement))</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1276,7 +1274,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — Simple (Stories 3/4)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1313,7 +1311,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-7697 (S2-R2 / S2-R3 / S2-R4)</t>
+          <t>SV-7698, SV-7699 (Story 3/4 (streamlined completion — no-parts WO one-confirm))</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1327,7 +1325,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — Simple (Stories 3/4)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1362,7 +1360,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-7697, SV-7710 (S2-R4 / S2-R5 / S15-R3)</t>
+          <t>SV-7698, SV-7699, SV-7710 (Story 3/4 (streamlined completion — Success screen) / S15-R3)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1376,7 +1374,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — Simple (Stories 3/4)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1410,7 +1408,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-7697, SV-7710 (S2-R5 / S15-R3)</t>
+          <t>SV-7698, SV-7699, SV-7710 (Story 3/4 (streamlined completion — Go to Invoice) / S15-R3)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1424,7 +1422,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — Simple (Stories 3/4)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1460,7 +1458,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-7697 (S2-R2 / S2 AC (missing required fields blocked))</t>
+          <t>SV-7698, SV-7699 (Story 3/4 (streamlined completion — missing required fields blocked))</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1469,12 +1467,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Verify with Create POs OFF a work order with vendor parts completes with no PO, no vendor bill and no AP sync</t>
+          <t>Verify a work order with a vendor part creates a PO on completion and routes through the receive step (POs always on)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — Simple (Stories 3/4)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1490,27 +1488,27 @@
       <c r="E22" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Create Purchase Orders is set to OFF.
-3. An open work order with an approved vendor-part line exists.</t>
+2. An open work order with an approved vendor-part line exists.
+3. POs are always on — there is no Create-POs setting to turn off.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1. Complete the work order in one confirm.
-2. Check whether any PO was created.
-3. Check for any vendor bill / AP sync.</t>
+          <t>1. Start completion of the work order.
+2. Observe whether a PO / background order is created for the vendor part and whether receiving is required.
+3. Complete after receiving and check the vendor bill / AP sync.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. No PO is created.
-2. No vendor bill and no AP sync occur.
-3. No catalog/inventory sync for the vendor/found part; it is received at request time only.</t>
+          <t>1. A PO (background order) is created for the vendor part; Complete Work Order stays disabled until the part is received (S4-R1/R4).
+2. After receiving, completion proceeds and the vendor bill / AP sync occur per the normal pipeline.
+3. There is no skip/no-PO path — the former Create-POs-OFF flow was retired.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SV-7697 (S2-R6 / S2 AC (Create POs off ⇒ no PO))</t>
+          <t>SV-7698, SV-7699 (Story 3/4 (POs always on — former Create-POs-OFF flow retired))</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1524,7 +1522,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — Simple (Stories 3/4)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1560,7 +1558,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SV-7697 (S2-R6 / §5 invariant 1)</t>
+          <t>SV-7698, SV-7699 (Story 3/4 (streamlined completion — inventory movement) / §5 invariant 1)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1574,7 +1572,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — Simple (Stories 3/4)</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1610,7 +1608,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>SV-7697 (S2-R2 / S2 AC (auto-pick off ⇒ pick in modal))</t>
+          <t>SV-7698, SV-7699 (Story 3/4 (streamlined completion — auto-pick off ⇒ pick in modal))</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1624,7 +1622,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — Simple (Stories 3/4)</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1658,7 +1656,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-7697 (S2-R6 / S2 AC (re-open returns to Approved))</t>
+          <t>SV-7698, SV-7699 (Story 3/4 (streamlined completion — re-open returns to Approved))</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1672,7 +1670,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — Simple (Stories 3/4)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1707,7 +1705,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>SV-7697 (S2 AC (individual-line Complete + per-part receive kept))</t>
+          <t>SV-7698, SV-7699 (Story 3/4 (streamlined completion — individual-line Complete + per-part receive))</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -2234,16 +2232,16 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1. Click Complete Work Order.
-2. Proceed through any tech-story / details gates.
-3. Attempt the final Complete confirm.</t>
+          <t>1. Open the work order with one line in Needs Approval and all other gates satisfied.
+2. Look at the Complete Work Order button and hover it for any tooltip.
+3. Approve the remaining line and re-check the button.</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. The existing 'you need to approve the line to complete the work order' error appears.
-2. The work order does not complete while a line is unapproved.
-3. There is no new disabled state — the error surfaces on Complete.</t>
+          <t>1. The Complete Work Order button is disabled while any line is unapproved.
+2. A tooltip on the disabled button describes the reason (which line needs approval).
+3. The button enables and completion proceeds once all lines are approved (S4-R8).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2284,15 +2282,15 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Confirm one line is unapproved.
-2. Click Complete Work Order and attempt to complete.
+          <t>1. Confirm one line is unapproved (manually un-approved after being added, Auto-approve ON).
+2. Look at the Complete Work Order button (disabled) and its tooltip.
 3. Re-approve the line and retry.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. With the line unapproved, completion is blocked with the approve-line error.
-2. After re-approving all lines, completion proceeds.</t>
+          <t>1. With the line unapproved, the Complete Work Order button is disabled with a tooltip describing the reason.
+2. After re-approving all lines, the button enables and completion proceeds (holds regardless of Auto-approve).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3590,7 +3588,7 @@
       <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. A work order has a vendor part with no vendor assigned and Create POs is on.
+2. A work order has a vendor part with no vendor assigned (purchase orders are always on).
 3. The work order has been completed so POs are generated.</t>
         </is>
       </c>
@@ -5381,20 +5379,22 @@
         <is>
           <t>1. Attempt to receive without a vendor set.
 2. Attempt to receive without a part number.
-3. Attempt to receive without a vendor invoice number.</t>
+3. Attempt to receive with the cost / sell price missing.
+4. Attempt to receive without a vendor invoice number.</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is gated until a vendor is set.
-2. Receiving is gated until the missing part number is entered.
-3. Receiving is gated until a vendor invoice number is captured.
-4. On Accept Delivery, cost is editable when $0 or missing (parity with Bulk Receive); the sell-price lock rule is unchanged.</t>
+2. Receiving is gated until the missing part number is entered (S13-R6).
+3. Receiving is gated until a missing cost / sell price is entered (S13-R7).
+4. Receiving is gated until a vendor invoice number is captured.
+5. On Accept Delivery, cost is editable when $0 or missing (parity with Bulk Receive); the sell-price lock rule is unchanged.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>SV-7707 (S12-R2)</t>
+          <t>SV-7707, SV-7708 (S12-R2 / S13-R6 / S13-R7)</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr"/>
@@ -5951,7 +5951,7 @@
       <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. A WO with nothing to receive (or POs off) is in the list with the column enabled.</t>
+2. A WO with nothing to receive is in the list with the column enabled.</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify VIN is NOT required at completion in the non-review flow (only mileage and engine hours, when missing)</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -7435,24 +7435,26 @@
       <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. VIN is required for this org's completion and the work order has no VIN.
-3. Require Review is OFF (VIN is collected at completion in the non-review flow).</t>
+2. Require Review is OFF.
+3. A work order is missing VIN but has mileage and engine hours present.</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>1. Start completion.
-2. Leave VIN empty and try to proceed.</t>
+          <t>1. Start completion and reach the Details step.
+2. Note which vehicle fields are required, then complete with VIN still empty.</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>1. Completion is blocked until the VIN is entered.</t>
+          <t>1. The completion Details step collects only mileage and engine hours (when missing) — VIN is NOT a required completion field (S4-R3).
+2. Completion is NOT blocked by a missing VIN; the work order completes.
+3. VIN is captured later only if Require Review is on, in the Mark Reviewed dialog (Story 16).</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>SV-7698, SV-7710 (S15-R2 / S3-R3)</t>
+          <t>SV-7699 (S4-R3 (VIN removed from completion; captured at Mark Reviewed))</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr"/>
@@ -7868,14 +7870,14 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>1. Click Complete Work Order.
-2. Read the error shown at the final confirm.</t>
+          <t>1. Open a work order with one unapproved line and all other gates satisfied.
+2. Look at the Complete Work Order button and its tooltip.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>1. The existing 'you need to approve the line to complete the work order' error is shown.
-2. Completion does not proceed until the line is approved.</t>
+          <t>1. The Complete Work Order button is disabled with a tooltip describing which line needs approval.
+2. Completion does not proceed until the line is approved; the button enables once all lines are approved.</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -7937,7 +7939,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
+          <t>Verify there is no Create-POs-OFF bypass — a vendor part always generates a PO and QuickBooks sync on completion</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -7958,26 +7960,27 @@
       <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Create Purchase Orders is OFF.
-3. A work order with a vendor/found part exists.</t>
+2. A work order with a vendor/found part exists.
+3. There is no Create Purchase Orders setting to turn off — POs are always on.</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>1. Complete the work order with Create POs OFF.
-2. Check for any PO, vendor bill, AP sync.
-3. Check for any catalog/inventory sync of the vendor/found part.</t>
+          <t>1. Complete the work order that has a vendor/found part (receiving as required).
+2. Check that a PO was created for the vendor part.
+3. Check the vendor bill / AP sync and the catalog/inventory sync.</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>1. No PO, no vendor bill, no AP sync.
-2. No catalog/inventory sync (part is received at request time only).</t>
+          <t>1. A PO is created for the vendor part — no setting suppresses PO creation.
+2. The vendor bill / AP sync occurs per the normal pipeline once received.
+3. Catalog/inventory sync happens per the normal receive pipeline.</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>§5 / §4 (Create POs OFF)</t>
+          <t>§4/§5 (POs always on — no Create-POs-OFF bypass)</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr"/>
@@ -8007,7 +8010,7 @@
       <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Create POs is on and a work order has a receivable vendor part.</t>
+2. A work order has a receivable vendor part (purchase orders are always on).</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:J171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -935,7 +935,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Verify a settings change applies to future completions only and not to already-completed work orders</t>
+          <t>Verify a settings change applies to future completions and to a completed work order when it is reopened, but not retroactively to work orders left completed</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -962,20 +962,23 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1. Complete a work order under the current settings.
-2. Change a relevant Work Order setting (e.g. Require Vendor Invoice Number) and Save.
-3. Reopen the already-completed work order and inspect it.</t>
+          <t>1. Complete a work order under the current Work Order settings so it reaches Complete.
+2. Go to the Work Orders settings tab, change a relevant setting (for example turn Require Review Before Completion ON) and Save.
+3. First, without touching the completed work order, check its status.
+4. Then reopen the completed work order (for example add a New Line, which returns it to Approved) and complete it again.
+5. Observe whether the new setting now applies to the reopened work order.</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. The already-completed work order is not retroactively changed by the new setting.
-2. Only work orders completed after the change follow the new setting.</t>
+          <t>1. While it is left completed, the already-completed work order still shows Complete and is not changed by the new settings (the change is not applied retroactively to work orders that stay completed).
+2. Only work orders completed after the change follow the new settings for their first completion.
+3. When the completed work order is reopened, the new settings now apply to it: re-completing it must satisfy the new gate (for example it now routes through the review step / Ready for Review instead of completing directly).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-7696 (S1-R9 (future completions only, never retroactive))</t>
+          <t>SV-7696 (S1-R9 (future completions + apply on reopen; never retroactive to WOs left completed))</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1654,12 +1657,13 @@
       <c r="G25" s="2" t="inlineStr">
         <is>
           <t>1. The work order status returns to Approved.
-2. On the next completion, the modal summarizes already-received vs newly-added parts.</t>
+2. On the next completion, the modal summarizes already-received vs newly-added parts.
+3. When you resolve the last open line again, the work order follows the current settings: with Require Review off it moves to Complete on its own; with Require Review on it moves to Ready for Review.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-7697 (S2-R6 / S2 AC (re-open returns to Approved))</t>
+          <t>SV-7697, SV-7870 (S2-R6 / S2 AC (re-open returns to Approved); S16-R12 (auto-complete on re-resolve))</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1751,7 +1755,8 @@
       <c r="G27" s="2" t="inlineStr">
         <is>
           <t>1. The wizard shows a Receive step (e.g. 'N parts waiting to receive').
-2. The actions are Cancel, Complete Without Receiving, and Receive Parts.</t>
+2. The actions are Cancel, Complete Without Receiving, and Receive Parts.
+3. If one of the waiting parts is a special-order core, Complete Without Receiving is disabled (with a tooltip) until that core is received; for non-core parts it stays available.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1900,7 +1905,8 @@
         <is>
           <t>1. The work order completes and the Success screen appears.
 2. Unreceived parts remain in a waiting-to-receive state (would show in the Waiting on Parts column).
-3. The line still shows a Receive button.</t>
+3. The line still shows a Receive button.
+4. Note: Complete Without Receiving is only available when no special-order core is waiting; if a core is waiting it is disabled and the core must be received first.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2247,8 +2253,8 @@
       <c r="G37" s="2" t="inlineStr">
         <is>
           <t>1. In the required-invoice flow (Require Vendor Invoice Number ON), a line still in Needs Approval leaves the Complete Work Order button disabled.
-2. Hovering the disabled Complete Work Order button shows a tooltip explaining why, naming the line that needs approval.
-3. The button becomes enabled once every line is approved.
+2. Hovering the disabled Complete Work Order button shows the tooltip 'Every line must be approved or declined in order to complete the work order.'
+3. The button becomes enabled once every line is approved or declined.
 4. In the optional-invoice flow (Require Vendor Invoice Number off) and when Require Review is on, the same unapproved line instead shows the existing message 'you need to approve the line to complete the work order' when you click Complete (the button stays active).</t>
         </is>
       </c>
@@ -2299,7 +2305,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. In the required-invoice flow (Require Vendor Invoice Number ON), a manually un-approved line leaves the Complete Work Order button disabled with a tooltip naming the line that needs approval — even though Auto-approve Lines is ON.
+          <t>1. In the required-invoice flow (Require Vendor Invoice Number ON), a manually un-approved line leaves the Complete Work Order button disabled with the tooltip 'Every line must be approved or declined in order to complete the work order.' — even though Auto-approve Lines is ON.
 2. After re-approving every line, the Complete Work Order button enables and completion proceeds.
 3. In the optional-invoice flow (Require Vendor Invoice Number off) and when Require Review is on, the same unapproved line instead shows the existing message 'you need to approve the line to complete the work order' when you click Complete.</t>
         </is>
@@ -2462,7 +2468,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify a waiting special-order core disables Complete Without Receiving (with a tooltip) and offers Receive Parts</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2484,25 +2490,27 @@
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is OFF (Optional).
-3. A work order has a special-order (vendor) cored part not yet received.</t>
+3. A work order has a special-order (vendor) cored part that has not been received yet.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
-2. Observe whether a core-resolution step appears.
-3. Confirm Complete Without Receiving is still available.</t>
+2. In the completion wizard receive step, look at the actions while the core part is still not received.
+3. Hover the Complete Without Receiving action and try to use it.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. There is nothing to resolve yet for special-order cores in the completion modal.
-2. Complete Without Receiving remains available.</t>
+          <t>1. The receive step shows the parts still to receive and indicates that a core charge is among them.
+2. Complete Without Receiving is disabled (greyed out); hovering it shows a tooltip saying the core part must be received first before you can complete.
+3. A Receive Parts button is offered so the core can be received.
+4. Complete Without Receiving only becomes available once the waiting core has been received.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-7698 (S3-C2)</t>
+          <t>SV-7698 (S3-C2 (updated per design #4 core-block))</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2593,7 +2601,8 @@
         <is>
           <t>1. The Create Invoice gate opens a resolve module for the unresolved cores.
 2. It routes to receive the cored line(s) (core-only partial receive supported).
-3. After resolving Ok/Not OK the invoice proceeds.</t>
+3. After resolving Ok/Not OK the invoice proceeds.
+4. Because a waiting core cannot be skipped, the core line must be received before completion; receiving it settles the core so invoicing can proceed.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2641,7 +2650,8 @@
         <is>
           <t>1. The work order remains Completed.
 2. It remains un-invoiced.
-3. Cores remain pending.</t>
+3. Cores remain pending.
+4. Note: because the core cannot be skipped at completion, this cancel path applies after completion at the Create Invoice gate; the core stays pending and the work order stays un-invoiced until it is received and resolved.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2691,7 +2701,8 @@
         <is>
           <t>1. After the receive round-trip a gated Resolve-cores modal appears.
 2. Cores can be resolved (part is always received, so always resolvable).
-3. After resolving, Complete succeeds to the Success screen.</t>
+3. After resolving, Complete succeeds to the Success screen.
+4. Consistent with the un-skippable-core rule: the required-invoice flow already forces the Receive round-trip, so the core is always received before Complete.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -4670,7 +4681,8 @@
       <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. Core-only partial receive is supported.
-2. Once the cored part is received, its Ok/Not OK resolution becomes available (for Story 3/4 resolution).</t>
+2. Once the cored part is received, its Ok/Not OK resolution becomes available (for Story 3/4 resolution).
+3. Consistent with the completion rule that a waiting core cannot be skipped: the core must be received (core-only partial receive supported) before its Ok / Not OK can be resolved.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4880,7 +4892,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify a NEW part number can be entered and saved so the part can be received</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4913,14 +4925,14 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1. A new inventory/catalog part is created.
-2. Stock is added for the received quantity.
-3. A Part History entry is written.</t>
+          <t>1. The new part number saves and stays on the part.
+2. Once the part has a part number (plus the required cost / sell price and a vendor invoice number), it can be received.
+3. The part-number entry does not have to create a new inventory or catalog item with stock for this to pass.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>SV-7705 (S10 AC (new number))</t>
+          <t>SV-7705 (S10-R1 (PN mandatory to receive); S10-R2 struck (first-class part not required in v1))</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4929,7 +4941,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify an EXISTING part number can be entered so the part can be received, without overwriting the item's description or category</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4962,14 +4974,15 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1. The part links to the existing inventory item.
-2. Stock, received cost and Part History update.
-3. The item's existing description and category are NOT overwritten.</t>
+          <t>1. The existing part number saves on the part.
+2. The part can be received once it has the number (plus the required cost / sell price and a vendor invoice number).
+3. If a catalog item with that number already exists, its description and category are not overwritten.
+4. Linking the part into a first-class inventory item (updating its stock / cost / history) is not required for this to pass.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>SV-7705 (S10 AC (existing number))</t>
+          <t>SV-7705 (S10-R1 (PN mandatory to receive); S10-R2 struck (linking to first-class item not required in v1))</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -5077,7 +5090,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify the inline part-number save persists and enables receiving</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -5110,14 +5123,14 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1. A catalog part is created/linked.
-2. An inventory stock Part exists (a CataloguePart alone is not stock).
-3. Part History is written; the flow does not rely on the complete-simple bypass to create inventory.</t>
+          <t>1. The part number entered inline is saved and persists (it is not lost).
+2. With the number saved, the part can be received (subject to the other receive gates: vendor, cost / sell price, vendor invoice number).
+3. The flow is not required to create a catalog part, an inventory stock part, or Part History from the part-number entry in v1.</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>SV-7705 (S10 Technical guardrails)</t>
+          <t>SV-7705 (S10-R1 + S10 technical guardrails; S10-R2 struck (catalog/inventory creation not required in v1))</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr"/>
@@ -6071,12 +6084,13 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>1. With Require Review ON, completing routes into the review flow rather than completing directly.</t>
+          <t>1. With Require Review ON, completing routes into the review flow rather than completing directly.
+2. When the last open line is resolved (by any path) while Require Review is on, the work order routes to Ready for Review — it never auto-completes.</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>SV-7870 (R1)</t>
+          <t>SV-7870 (R1 + S16-R12)</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -6262,12 +6276,13 @@
         <is>
           <t>1. The work order status becomes Review (amber).
 2. A 'Ready for Review' / 'Sent for review' indication is shown.
-3. Lines lock to Complete and inventory is auto-picked.</t>
+3. Lines lock to Complete and inventory is auto-picked.
+4. The same Review / Ready-for-Review end state is reached when the last open line auto-resolves under Require Review on, not only when Send To Review is clicked explicitly.</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>SV-7870 (R5 / R6)</t>
+          <t>SV-7870 (R5 / R6 + S16-R12)</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr"/>
@@ -6407,12 +6422,13 @@
       <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. After Confirm Review the sign-off completes and the work order moves directly Review -&gt; Complete.
-2. There is no distinct 'Reviewed' holding state and no separate final 'Complete Work Order' click.</t>
+2. There is no distinct 'Reviewed' holding state and no separate final 'Complete Work Order' click.
+3. Note: with Require Review on, resolving the last open line first routes the work order to Ready for Review; sign-off (Confirm Review) then moves it to Complete.</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>SV-7870 (R5 / R8 (direct sign-off, no separate Complete))</t>
+          <t>SV-7870 (R5 / R8 (direct sign-off, no separate Complete) + S16-R12)</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -6553,12 +6569,13 @@
       <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. Invoicing is blocked until the work order is reviewed.
-2. After sign-off the work order moves directly Review -&gt; Complete (invoice-ready), with no separate final Complete Work Order click.</t>
+2. After sign-off the work order moves directly Review -&gt; Complete (invoice-ready), with no separate final Complete Work Order click.
+3. With Require Review on the work order never auto-completes on last-line-resolve; it routes to Ready for Review and invoicing stays blocked until it is reviewed.</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>SV-7870 (R8)</t>
+          <t>SV-7870 (R8 + S16-R12)</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -6695,7 +6712,8 @@
         <is>
           <t>1. Inventory cores are resolved before Send to Review.
 2. Special-order cores follow the vendor-invoice rules.
-3. Invoicing is blocked until the WO is Reviewed AND all cores are resolved.</t>
+3. Invoicing is blocked until the WO is Reviewed AND all cores are resolved.
+4. In the review flow too, a waiting special-order core cannot be skipped: Send to Review / completion is blocked until the core is received and resolved, and invoicing stays blocked until both Reviewed and all cores resolved.</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7911,7 +7929,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Verify an unapproved line blocks completion — required-invoice shows a disabled Complete button with a tooltip; other flows show the approve-line error</t>
+          <t>Verify an unapproved line disables the Complete Work Order button with a tooltip (regardless of the Require Vendor Invoice Number setting)</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -7931,21 +7949,23 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>1. Signed in as Admin.
-2. A work order has one unapproved line and all other gates satisfied.</t>
+          <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
+2. Auto-approve Lines is OFF so a newly added line lands in Needs Approval.
+3. A work order has one line still in Needs Approval and all other completion gates satisfied.</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>1. With Require Vendor Invoice Number ON, open a work order that has one line still needing approval and start completion; look at the Complete Work Order button, then hover it.
-2. With Require Vendor Invoice Number off (or Require Review on), open a similar work order and click Complete Work Order; read the message shown.</t>
+          <t>1. With Require Vendor Invoice Number ON, open a work order that has one line still in Needs Approval; look at the Complete Work Order button, then hover it.
+2. Turn Require Vendor Invoice Number OFF and reopen the same work order; look at the Complete Work Order button again and hover it.
+3. Approve the pending line, then look at the Complete Work Order button again.</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>1. With Require Vendor Invoice Number ON, the Complete Work Order button is disabled and hovering it shows a tooltip that explains why and names the line that needs approval.
-2. With Require Vendor Invoice Number off, or with Require Review on, the existing message 'you need to approve the line to complete the work order' is shown and the button stays active.
-3. In every case, completion does not proceed until the line is approved.</t>
+          <t>1. With Require Vendor Invoice Number ON, the Complete Work Order button is disabled; hovering it shows the tooltip 'Every line must be approved or declined in order to complete the work order.' (the tooltip is generic and does not name the specific line).
+2. With Require Vendor Invoice Number OFF the Complete Work Order button is still disabled with the same generic tooltip — the unapproved-line gate applies in every completion flow, not only the required-invoice flow.
+3. Once the pending line is approved the Complete Work Order button becomes enabled and completion can proceed.</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8292,7 +8312,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
+          <t>Verify Part History is preserved for a part that is genuinely inventory-tracked</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -8313,23 +8333,24 @@
       <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. A part transitions to inventory-tracked (e.g. a part number is added and it is received).</t>
+2. A genuinely inventory-tracked part exists (an inventory item with stock).</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>1. Add a part number to a previously untracked part and receive it.
-2. Open the item's Part History.</t>
+          <t>1. Use / receive a genuinely inventory-tracked part on a work order and complete it.
+2. Open that part's Part History (Parts &gt; Inventory, the clock icon on the part row).</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>1. Part History is preserved / created for the now inventory-tracked part.</t>
+          <t>1. For a part that is genuinely inventory-tracked, its Part History is preserved / written.
+2. Simply entering a part number on a previously untracked part is not required to turn it into an inventory-tracked part in v1, so no Part History needs to be created from that entry alone.</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>§5 invariant 3</t>
+          <t>SV-7705 (§5 invariant 3 (rescoped after S10-R2 strike))</t>
         </is>
       </c>
       <c r="I163" s="2" t="inlineStr"/>
@@ -8378,6 +8399,351 @@
       </c>
       <c r="I164" s="2" t="inlineStr"/>
       <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Verify resolving the last open line by completing a single line auto-completes the work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
+2. Require Review Before Completion is OFF (in the Work Orders settings tab).
+3. A work order is in Approved status with two or more open (not-yet-completed) lines.</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and complete one line at a time using the per-line Complete action.
+2. After completing the first line (while at least one other line is still open), check the work order status.
+3. Complete the last remaining open line.
+4. Check the work order status again.</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>1. While at least one line is still open, the work order stays in Approved.
+2. The moment the last open line is completed, the work order moves to Complete on its own (invoice-ready).
+3. You do not have to click Complete Work Order separately for the work order to reach Complete.</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (S16-R12 (a) single line)</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Verify resolving the last open lines in bulk (several at once) auto-completes the work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review Before Completion is OFF.
+3. A work order is in Approved status with several open lines and nothing left to receive on those lines.</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and select all the open lines.
+2. From the bulk actions menu choose Set line status and set the selected lines to Complete (resolving them all at once).
+3. Check the work order status.</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>1. All selected lines become Complete in one action.
+2. Because that resolves the last open lines, the work order moves to Complete on its own (invoice-ready).
+3. No separate Complete Work Order step is needed.</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (S16-R12 (b) bulk)</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Verify a split that leaves a work order fully resolved auto-completes that work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review Before Completion is OFF.
+3. A work order has several lines; some are already completed and at least one line is still open.</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and complete all but one line, leaving one line still open (the work order stays Approved).
+2. Select the remaining open line and use the bulk actions menu Split work order to move it to a new work order.
+3. Check the status of the original work order after the split.</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>1. The open line moves to a new work order.
+2. The original work order is now fully resolved (all its remaining lines are complete), so it moves to Complete on its own.
+3. No separate Complete Work Order step is needed on the original work order.</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (S16-R12 (c) split)</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Verify deleting a line so the remaining lines are all resolved auto-completes the work order when Require Review is off</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review Before Completion is OFF.
+3. A work order has some completed lines and one remaining open line.</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order (its other lines are already complete; one line is still open).
+2. Select the open line and use the bulk actions menu Delete lines to remove it.
+3. Check the work order status.</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>1. The open line is removed.
+2. Because the remaining lines are all complete, the work order moves to Complete on its own.
+3. No separate Complete Work Order step is needed.</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (S16-R12 (d) delete line)</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Verify that with Require Review on, resolving the last open line routes the work order to Ready for Review instead of auto-completing</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review Before Completion is ON and saved.
+3. A work order is in Approved status with two or more open lines.</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order and complete the lines one at a time (or in bulk).
+2. After the last open line is resolved, check the work order status.
+3. Confirm whether the work order went straight to Complete or to review.</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>1. When the last open line is resolved, the work order moves to Ready for Review (Review) — it does NOT auto-complete.
+2. The work order must be signed off in the review step before it can reach Complete.</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (S16-R12 review ON)</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Verify a clock-out that finishes the last line routes the work order to Ready for Review even when Require Review is off</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as a Technician who is clocked into the work on the work order.
+2. Require Review Before Completion is OFF.
+3. The work order has one remaining open line that the technician is working on.</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>1. As the technician, finish the last open line by clocking out of it.
+2. Check the work order status.</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>1. Even though Require Review is off, the work order routes to Ready for Review (not straight to Complete).
+2. This is the one path that does not auto-complete when review is off (a technician may not be allowed to complete a work order).</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (S16-R13 clock-out exception)</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Verify the work order status transitions on the backend when the last open line is resolved (auto-Complete when review off, Ready for Review when review on)</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>API — Auto-Complete Trigger (Story 16 R12/R13)</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order is in Approved status with two or more open lines.</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>1. With Require Review off, resolve the last open line and read the work order record.
+2. Turn Require Review on, and on another work order resolve the last open line and read the work order record.</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>1. With Require Review off, after the last open line resolves the work order record status becomes Complete (the resolve action returns success).
+2. With Require Review on, after the last open line resolves the work order record status becomes Ready for Review (Review), not Complete.</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (S16-R12 backend status transition)</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J171"/>
+  <dimension ref="A1:J188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1756,7 +1756,7 @@
         <is>
           <t>1. The wizard shows a Receive step (e.g. 'N parts waiting to receive').
 2. The actions are Cancel, Complete Without Receiving, and Receive Parts.
-3. If one of the waiting parts is a special-order core, Complete Without Receiving is disabled (with a tooltip) until that core is received; for non-core parts it stays available.</t>
+3. If one of the waiting parts is a special-order core, a Resolve cores screen appears before this choice; once every core is decided (OK / Not OK), Complete Without Receiving stays available — only an undecided core blocks completing.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
           <t>1. The work order completes and the Success screen appears.
 2. Unreceived parts remain in a waiting-to-receive state (would show in the Waiting on Parts column).
 3. The line still shows a Receive button.
-4. Note: Complete Without Receiving is only available when no special-order core is waiting; if a core is waiting it is disabled and the core must be received first.</t>
+4. Note: a special-order core no longer has to be received first — it is decided (OK / Not OK) on the Resolve cores screen before this choice; only an undecided core blocks Complete Without Receiving.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Verify a waiting special-order core disables Complete Without Receiving (with a tooltip) and offers Receive Parts</t>
+          <t>Verify a Resolve cores screen appears before the Receive parts / Complete without receiving choice and only an undecided core blocks completing</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2496,21 +2496,21 @@
       <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
-2. In the completion wizard receive step, look at the actions while the core part is still not received.
-3. Hover the Complete Without Receiving action and try to use it.</t>
+2. Observe the screen shown right before the Receive parts / Complete without receiving choice.
+3. Leave the core undecided and try Complete Without Receiving.
+4. Mark the core OK or Not OK on the resolve screen and try again.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. The receive step shows the parts still to receive and indicates that a core charge is among them.
-2. Complete Without Receiving is disabled (greyed out); hovering it shows a tooltip saying the core part must be received first before you can complete.
-3. A Receive Parts button is offered so the core can be received.
-4. Complete Without Receiving only becomes available once the waiting core has been received.</t>
+          <t>1. A separate Resolve cores screen lists the un-received vendor core with its part info, core charge and an OK / Not OK choice, and explains that resolving now keeps the invoice accurate.
+2. While the core is still undecided, completing is blocked.
+3. Once every core is decided (OK or Not OK), Complete Without Receiving works — a decided core no longer blocks completing without receiving (no receive needed first).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-7698 (S3-C2 (updated per design #4 core-block))</t>
+          <t>SV-8353 (S18 C-R1/C-R4)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2519,7 +2519,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify the 'Cores pending' indication reflects only undecided special-order cores (a decided core clears it)</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2540,23 +2540,24 @@
       <c r="E43" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. A completed (optional-invoice) work order has an unresolved special-order core.</t>
+2. A completed (optional-invoice) work order has an un-received special-order core.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>1. Open the work order's invoice / Finance view.
-2. Look for a cores indicator.</t>
+          <t>1. With the core still undecided (no OK / Not OK yet), open the work order's invoice / Finance view and look for a cores indication.
+2. Decide the core (OK or Not OK) and check again.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. The invoice shows a 'Cores pending' flag while special-order cores are unresolved.</t>
+          <t>1. While the core is undecided, a 'Cores pending' indication shows and invoice creation is blocked.
+2. Once every core is decided (OK or Not OK), the 'Cores pending' indication clears and invoicing is no longer blocked — even though the core part has not been received yet.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-7698 (S3-C3)</t>
+          <t>SV-8353 (S18 C-R4)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2665,7 +2666,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify the required-invoice flow asks to resolve special-order cores FIRST and then to receive them</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2692,22 +2693,21 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1. Complete Work Order → Receive Parts and receive the cored part.
-2. On return, observe the Resolve-cores modal.
-3. Resolve each core Ok / Not OK, then Complete.</t>
+          <t>1. Click Complete Work Order.
+2. Observe the order of the core steps in the wizard.
+3. Decide the core OK / Not OK on the resolve screen, then Receive Parts and receive it, then Complete.</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. After the receive round-trip a gated Resolve-cores modal appears.
-2. Cores can be resolved (part is always received, so always resolvable).
-3. After resolving, Complete succeeds to the Success screen.
-4. Consistent with the un-skippable-core rule: the required-invoice flow already forces the Receive round-trip, so the core is always received before Complete.</t>
+          <t>1. The wizard asks to resolve the core FIRST (same resolve screen as the optional flow) and then to receive — not resolve-after-receive.
+2. At receive the saved decision is applied automatically; the user is not asked OK / Not OK again.
+3. After all parts are received, Complete succeeds to the Success screen.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SV-7699 (S4-C2)</t>
+          <t>SV-7699, SV-8353 (S18 C-R6)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2716,7 +2716,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify the completion and invoice gates detect an undecided special-order core that exists only as a requested part</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2737,24 +2737,24 @@
       <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. A completed work order has a special-order cored part that exists only as a PartRequest (no WorkOrderPart yet).</t>
+2. A work order has a special-order cored part that exists only as a part request (not received, no work-order part yet) and is still undecided.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1. Click Create Invoice.
-2. Observe whether the unresolved core is detected.</t>
+          <t>1. Try to complete the work order and to create the invoice.
+2. Decide the core OK / Not OK and try again.</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. The invoice gate detects the unresolved core even though it is only a PartRequest.
-2. The user is required to resolve it before invoicing.</t>
+          <t>1. The undecided core is detected even though it exists only as a requested (un-received) part — completing and invoicing are blocked.
+2. Once the core is decided, the gates clear (no receive needed first).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SV-7698 (S3 Guardrail (PartRequest-only core))</t>
+          <t>SV-8353 (S18 C-R2/C-R4 (guardrail))</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2859,128 +2859,559 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>Verify the Resolve cores screen lists every un-received vendor core with part info, core charge and OK / Not OK, plus an invoice-accuracy message</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Core parts — Pre-Resolve (Story 18)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Vendor Invoice Number is OFF (Optional).
+3. A work order has two special-order (vendor) cored parts that have not been received yet.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Complete Work Order.
+2. Observe the screen shown right before the Receive parts / Complete without receiving choice.
+3. Read the message on the screen.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>1. A separate, consolidated Resolve cores screen appears, listing EVERY un-received vendor core (both parts).
+2. Each core shows its part info, its core charge and an OK / Not OK choice.
+3. A message explains that resolving now is for invoice accuracy.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 C-R1)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Verify marking a core Not OK immediately adds the core charge to the work order total and customer invoice, while OK adds no charge</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Core parts — Pre-Resolve (Story 18)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order has two un-received vendor cores shown on the Resolve cores screen.</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Mark one core Not OK and note the work order total.
+2. Mark the other core OK and note the total again.
+3. Create the customer invoice and check its amounts.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>1. Not OK: the core charge is priced into the work order total right away and flows to the customer invoice.
+2. OK: no charge is added (the vendor core return is created automatically later, at receive).
+3. The invoice matches the decisions even though no core part has been received.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 C-R3)</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Verify completion and invoice creation are blocked only while a core is undecided — a decided core does not block</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Core parts — Pre-Resolve (Story 18)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order has two un-received vendor cores.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. Decide one core (OK or Not OK), leave the other undecided; try to complete the work order and to create the invoice.
+2. Decide the remaining core and try again.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1. With any core still undecided, completing and invoice creation are blocked and a cores-pending indication shows.
+2. Once every core is decided, completion and invoice creation proceed — no receive is required first.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 C-R4)</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Verify receiving a pre-resolved core auto-applies the saved decision: OK creates exactly one vendor return, Not OK creates none, the invoice never changes, retries create no duplicates</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Core parts — Pre-Resolve (Story 18)</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order has one core pre-resolved OK and another pre-resolved Not OK, both not yet received; the customer invoice is created.</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive the OK core; check vendor returns and the customer invoice.
+2. Receive the Not OK core; check again.
+3. Retry / re-submit the receive and re-check for duplicates.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>1. The OK core is received already resolved, with exactly ONE vendor core return created automatically.
+2. The Not OK core is received already resolved, with NO return created.
+3. The user is never asked OK / Not OK again, the customer invoice does not change at receive, and retries create no duplicate cores or returns.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 C-R5)</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Verify the receive dialog locks quantity to the full remaining amount once the work order is invoiced/paid, with the core auto-selected and an explanatory tooltip</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Core parts — Pre-Resolve (Story 18)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. An invoiced/paid work order has an un-received cored part; another (not yet invoiced) work order also has one.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the receive dialog for the invoiced/paid work order's part, try to change the quantity, and hover the field.
+2. Open the receive dialog for the not-yet-invoiced work order's part and change the quantity.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>1. On the invoiced/paid work order the quantity is locked to the full remaining amount, the core is auto-selected, and the tooltip reads 'This part is on a customer invoice and should be received in full'.
+2. Before invoicing, the quantity stays editable (partial receive allowed).
+3. The lock is on the screen only — the customer invoice itself never changes at receive.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 C-R8)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Lines tab shows the core decision state before and after receive: 'Core decision pending', 'Core OK — return to vendor, no charge', 'Core Not OK — customer charged'</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Core parts — Pre-Resolve (Story 18)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order has three vendor cores: one undecided, one decided OK, one decided Not OK.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order's Lines tab before receiving and read each core's state.
+2. Receive the two decided cores and re-check the Lines tab.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1. Before receive: the undecided core shows 'Core decision pending'; the OK core shows 'Core OK — return to vendor, no charge'; the Not OK core shows 'Core Not OK — customer charged'.
+2. After receive, a pre-resolved core shows its resolved state with NO OK / Not OK buttons.
+3. No duplicate core prompts appear anywhere.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 C-R9)</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Verify a core decision cannot be changed once the work order has an active invoice</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Core parts — Pre-Resolve (Story 18)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order has a decided core and an active customer invoice.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to change the core's OK / Not OK decision (on the resolve screen or the Lines tab).</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1. The decision cannot be changed while the work order has an active invoice.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 AC (resolution immutable with an active invoice))</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>API: Verify POST /api/work-orders/{id}/pre-resolve-cores persists the core decision on the part request with no side-effect records</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>API — Core Pre-Resolve (Story 18)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1. A valid Admin session (API).
+2. A work order with an un-received special-order cored part request exists.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. POST /api/work-orders/{id}/pre-resolve-cores with the core decision (ok / not_ok).
+2. Re-read the work order's lines / receive-view read models.
+3. Inspect for side-effect records (work-order part, statement item, vendor return).</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1. The request succeeds (2xx) and core_resolution is persisted on the core work_order_part_request (ok | not_ok; NULL = undecided).
+2. NO WorkOrderPart, statement item, or vendor return is created at this point.
+3. cores_pending reflects only undecided (NULL) cores after the call.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 C-R2 / technical plan)</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>API: Verify resolving a received core via the existing handle-core endpoints also writes the decision back to the linked core part request</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>API — Core Pre-Resolve (Story 18)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>1. A valid Admin session (API).
+2. A received cored part exists that can be resolved via the existing handle-core(s) endpoints.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>1. Resolve the received core Ok / Not OK via the existing handle-core(s) endpoint.
+2. Read the linked core part request and its core_resolution value.</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>1. The call succeeds and the decision is ALSO written to the linked core PartRequest (core_resolution matches the handle-core decision), keeping core_resolution the single source of history.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 C-R10)</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
           <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Tech Story is ON.
 3. A work order has a line with no tech story yet.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order Lines tab.
 2. Look under the line for a Story sub-row.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The line has a Story sub-row.
 2. When empty, it shows an 'Add tech story for this line' link.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R1)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Tech Story is ON.
 3. A work order has at least one line missing a story.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
 2. Observe whether completion proceeds without stories.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. Completion cannot proceed while any line is missing a tech story.
 2. The user is routed to enter the missing stories first.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R2)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Tech Story is ON.
 3. A work order has a line missing a story.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
 2. Observe the first modal that appears.
@@ -2988,49 +3419,49 @@
 4. Observe the next step.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. The tech-story modal opens FIRST (before the completion wizard).
 2. After Continue, the flow chains into the completion wizard (parts/pick → complete).
 3. Gate order is tech story → parts → complete/send-to-review.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R3)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open during completion.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Read the modal header.
 2. Read the per-line card (line #, name, technician).
@@ -3038,49 +3469,49 @@
 4. Leave the textarea empty and check the Next/Continue button.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. The header reads 'Tech story' with 'WO# · Customer'.
 2. A per-line card shows the line number, name and technician; a 'Line X of N' indicator is shown.
 3. The Next/Continue button is disabled until the textarea is non-empty.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R4)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has two or more lines all missing stories, and Require Tech Story is ON.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Start completion so the tech-story modal opens on Line 1 of N.
 2. Enter a story and click Next.
@@ -3088,193 +3519,193 @@
 4. On the last line, check the final button.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. On line 1 there is no Back button; after line 1, a Back button appears.
 2. Each line requires a non-empty story to advance.
 3. The last line shows Continue (chained into completion) or Save.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R4 (multi-line navigation))</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A line has a saved tech story.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. View the line's Story sub-row.
 2. Confirm the story text and controls.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The saved story renders inline with a green check and the story text.
 2. An Edit link is available to change it.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R5)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story modal has a text box for typing the story</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Open the tech-story modal on a line.
 2. Locate the text box where the story is typed.
 3. Type a story into the text box.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. The tech-story modal has a text box (textarea) for the story.
 2. The story text you type is accepted in the box.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R6 (test id))</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a line missing a story.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Add a tech story inline via the line's 'Add tech story' link.
 2. On a separate line missing a story, trigger the gate modal by clicking Complete.
 3. Confirm both entry points save a story.</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. A tech story can be entered inline on the line (Story 17 is the authoritative behavior).
 2. A story can also be entered via the completion gate modal, which lets stories be completed individually or several at once.
 3. Both paths persist the story.</t>
         </is>
       </c>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-7710, SV-7876 (TS Decision vs S15-R2)</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr"/>
-      <c r="J57" s="2" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. An open work order with a line is on its Lines tab.</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Add a part to a line.
 2. Enter a description, a quantity and a category.
@@ -3282,7 +3713,7 @@
 4. Save the part.</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The part saves successfully with description, quantity and category entered; part number, cost, vendor and sell price may be left empty.
 2. Category is a required field for v1 — the part cannot be saved without a category.
@@ -3290,42 +3721,42 @@
 4. The part appears on the line with its description and quantity and is treated as a vendorless part downstream; it is orderable from the line (Order creates or joins the Vendor-Missing purchase order and moves it to waiting-to-receive).</t>
         </is>
       </c>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R1)</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The add-part dialog is open on a work order line.</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Leave the description empty and try to save.
 2. Fill the description, leave the quantity empty and try to save.
@@ -3333,7 +3764,7 @@
 4. Fill the description, quantity and category but leave the sell price empty and try to save.</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. Saving is blocked inline when the description is empty ('Description is a required field').
 2. Saving is blocked inline when the quantity is empty ('Quantity is a required field').
@@ -3341,1042 +3772,1092 @@
 4. Saving is allowed when only the sell price is empty — sell price is not enforced as a required field for v1.</t>
         </is>
       </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R1 / S5 AC (validation))</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless part has been added to a work order line.</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Open the vendorless part's detail.
 2. Read its source / type field.</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The source is 'vendor' or 'found'.
 2. It is never set to 'inventory'.
 3. It is treated as vendorless downstream.</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R2)</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless part exists on a work order line.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Open the vendorless part.
 2. Change its description or quantity and save.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. The part can be edited after creation.
 2. The changes persist.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R3)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part with description + qty + sell but no part number exists on a work order.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Search inventory for a new item matching the description.
 2. Check for any Part History entry for it.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. No inventory item is created for the no-PN part.
 2. No Part History is written until a part number is added.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R4 / S5 AC (no inventory interaction))</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless part (no PN, no vendor) exists on a work order.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Edit the part and add a part number.
 2. Assign a vendor to it.
 3. Observe the part's vendorless status.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. Once both a part number and a vendor are present, the part is no longer treated as vendorless.
 2. It becomes eligible for downstream inventory / QuickBooks handling.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5 AC (transitions out of vendorless))</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless / no-PN part is on a work order PO.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Open a receive surface (Accept Delivery / Bulk Receive) for that PO.
 2. Attempt to receive the part without a part number.
 3. Attempt to receive it without a vendor.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked while the part number is missing.
 2. Receiving is blocked while the vendor is missing.
 3. Receiving is enabled only after both a part number and a vendor are provided.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R4 / S5 AC (receive gate))</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a vendor part with no vendor assigned and Create POs is on.
 3. The work order has been completed so POs are generated.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Open the PO list at /parts/orders.
 2. Find the PO for this work order.
 3. Confirm the vendorless part is on that PO.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The vendorless part is placed on the work order's normal PO.
 2. No separate 'dummy PO' is created for it.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R1)</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO exists that holds a part with no vendor.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Open /parts/orders.
 2. Look for the Vendor Missing indication on the PO row.
 3. Open the PO detail and confirm the indication there.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. The PO list shows a 'Vendor Missing' indication (with '+N' when multiple vendors are involved).
 2. The PO detail also shows the Vendor Missing flag.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R2)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists.
 3. QuickBooks integration is available for inspection.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Trigger / inspect QuickBooks sync for the PO.
 2. Confirm the Vendor Missing PO is excluded.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. The Vendor Missing PO is flagged.
 2. It is excluded from QuickBooks sync while the vendor is missing.</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R3)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO detail is open.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. Open the PO detail.
 2. Look for a way to select a vendor.
 3. Look for a way to enter/edit the missing part number.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. The Vendor Missing PO detail offers a way to select a vendor.
 2. It offers a way to enter or edit the part number.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R4)</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists with a part lacking vendor and part number.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Assign a vendor to the PO.
 2. Enter the missing part number.
 3. Observe the Vendor Missing flag.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. Once both a vendor and a part number are provided the Vendor Missing flag is removed.
 2. The part becomes eligible for QuickBooks.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R5)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Verify a Vendor Missing PO's spend is excluded from the QuickBooks Vendor Bill export and the Vendors Expenses report until a vendor is assigned</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A Vendor Missing PO exists.
-3. A relevant PO report is available.</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the PO report that lists POs.
-2. Find the Vendor Missing PO.</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>1. The report marks the Vendor Missing PO as 'needs vendor'.</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A Vendor Missing PO with a non-zero cost exists.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Vendors Expenses report and look for the vendor-missing PO's spend.
+2. Inspect the QuickBooks Vendor Bill export for that PO.
+3. Assign a vendor to the PO and check both again.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1. While the PO has no vendor, its spend is NOT counted in the Vendors Expenses report.
+2. Its spend is excluded from the QuickBooks Vendor Bill export.
+3. There is no dedicated purchase-order report and no 'needs vendor' marker — nothing 'marks' these POs.
+4. Once a vendor is assigned, the spend flows into both normally.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R6)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. An open work order has a sell-price-only line part (sell price set; vendor and/or cost missing; part number empty).</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>1. On the line, use the Order action for the sell-price-only part.
 2. Open the PO list at /parts/orders and find the work order's PO.
 3. Confirm the part's status.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>1. Ordering from the line creates or joins the work order's Vendor-Missing PO (no separate dummy PO).
 2. The part moves from 'requested' to 'waiting-to-receive' without completing the work order.
 3. At receive, a vendor and part number are still required (cost editable — Story 10).</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R7)</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The PO list at /parts/orders has multiple POs.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>1. Open /parts/orders.
 2. Look for a select-all checkbox in the header.
 3. Look for a checkbox on each PO row.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>1. A select-all checkbox is present.
 2. Each PO row has its own checkbox.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7-R1)</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The PO list has selectable POs.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>1. Select one or more POs.
 2. Observe the action bar.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>1. A bar appears reading 'N purchase orders selected'.
 2. The bar has Clear and Receive Selected actions.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7-R2)</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two or more POs are selected on the PO list.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>1. Click Receive Selected.
 2. Observe the destination page and the POs shown.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. The PO Bulk Receive page opens (Story 8).
 2. It contains the POs that were selected.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7-R3)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The PO list contains at least one fulfilled PO.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to select a fulfilled PO's checkbox.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The fulfilled PO cannot be selected (checkbox disabled).</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7-R4)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The PO list contains a Vendor Missing PO.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Select a Vendor Missing PO.
 2. Confirm its Vendor Missing indication is shown while selected.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. The Vendor Missing PO is selectable.
 2. Its Vendor Missing status remains clearly indicated.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7-R5)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The PO list has more POs than fit on one page (or a filter is applied).</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter or page the list.
 2. Click select-all.
 3. Check which POs are selected.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. Select-all only selects POs in the current page/filter, not the whole dataset.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7 (select-all scope))</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Verify part-sale-originated POs appear in the PO list and are selectable like work-order POs</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>PO Multi-Select (Story 7)</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A Part Sale with a vendor part exists, so a part-sale purchase order was created.</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Purchase Orders list and find the part-sale PO.
+2. Select it (checkbox) together with work-order POs and use Receive Selected.</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>1. The part-sale-originated PO appears in the PO list.
+2. It is selectable and joins the Receive Selected flow like a work-order PO.</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>SV-7702 (S7 AC (part-sale POs) + §8 Part Sales — confirmed)</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Verify the Bulk Receive page has a 'Back To Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You reached the Bulk Receive page via Receive Selected.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Locate the top-left 'Back To Purchase Orders' link.
 2. Click it.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. A 'Back To Purchase Orders' link is present top-left.
 2. Clicking it returns to the PO list.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R1)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Multiple POs across multiple vendors were sent to the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Read the vendor group headers and counts.
 2. Use one vendor's Expand/Collapse all control.
 3. Confirm each vendor has its own control (not one global).</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. POs are grouped by vendor with a count per vendor.
 2. Each vendor group has its own Expand/Collapse all control.
 3. POs within a group are collapsible.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R2 / S8-R3)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page is open with several POs.</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Read a PO row's details.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. The row shows the PO number.
 2. It shows the related work order, or an inventory / no-WO indicator.
 3. It shows the parts count.</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R4)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page is open with POs and parts.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Confirm nothing is selected on load.
 2. Select a PO and confirm all its parts get selected.
@@ -4384,595 +4865,647 @@
 4. Confirm the receive action is locked when nothing is checked.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. Nothing is selected by default.
 2. Selecting a PO selects all its parts; individual parts can be toggled.
 3. Actions are locked until at least one item is checked.</t>
         </is>
       </c>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R5)</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr"/>
-      <c r="J81" s="2" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO's parts are selected on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the 'Receive parts (N)' button state with no invoice number.
 2. Enter a vendor invoice number.
 3. Confirm the button state again.</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. The Receive button is disabled without a vendor invoice number.
 2. For a vendor-missing PO it also requires a vendor assigned and the missing part number entered.
 3. Once satisfied, the Receive button enables.</t>
         </is>
       </c>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R6)</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr"/>
-      <c r="J82" s="2" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Verify Bulk Receive field editability: quantity editable (partial receive), cost editable ONLY when it is $0, sell locks after the WO is invoiced/paid</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. The Bulk Receive page has a PO whose WO is NOT yet invoiced/paid, and another whose WO IS invoiced/paid.</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>1. On the not-yet-invoiced PO, edit quantity, cost and sell.
-2. On the invoiced/paid PO, try to edit sell.
-3. Hover the locked sell field.</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>1. Quantity and cost are editable; sell is editable while the work order is not invoiced/paid.
-2. After the work order is invoiced/paid, sell is locked with a lock icon and tooltip 'Locked — this part is already invoiced or paid'.
-3. After locking, only cost remains editable.
-4. The field rules have parity with the Accept-Delivery receive screen; cost is editable when $0 or missing on either surface.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>SV-7703, SV-7705 (S8-R7 / S10-R2)</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. The Bulk Receive page has a part whose cost is $0, a part whose cost is not $0, and a PO whose work order IS invoiced/paid.</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>1. Edit the quantity on a part (partial receive).
+2. Try to edit the cost on the part whose cost is $0.
+3. Try to edit the cost on the part whose cost is not $0.
+4. On the invoiced/paid PO, try to edit the sell price and hover the locked field.</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>1. Quantity is editable (partial receive supported).
+2. Cost is editable when it is $0 (pulled from the work order / PO when available).
+3. Cost is NOT editable when it is not $0.
+4. Sell price is editable until the work order is invoiced/paid, then locked with a lock icon and tooltip 'Locked — this part is already invoiced or paid'.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>SV-7703, SV-7705 (S8-R7 / S10-R3)</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has a Vendor Missing PO.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Assign a vendor to the Vendor Missing PO.
 2. Confirm it moves into that vendor's group.
 3. Enter the missing part number and confirm receiving becomes enabled.</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. Assigning a vendor moves the PO into that vendor's group.
 2. Entering the missing part number unflags it.
 3. Receiving is then enabled.</t>
         </is>
       </c>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R8)</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Verify Receive All receives everything selected at once and supports partial receive</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Multiple POs/parts are selected with valid invoice numbers on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Reduce one part's received quantity below its ordered quantity.
 2. Click Receive All.
 3. Confirm the receipts.</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. Everything selected is received at once.
 2. Partial receive (received qty below ordered) is supported.
 3. Remaining unreceived quantity stays waiting to receive.</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R10)</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You received POs on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. After receiving, check that a Delivery record was created.
 2. Check that a Vendor Bill was created.
 3. Check that the vendor bill synced to QuickBooks.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. A Delivery is created.
 2. A Vendor Bill is created.
 3. The vendor bill syncs to QuickBooks (same pipeline as single-PO receive).</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R11)</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Verify a pre-resolved core's decision is applied automatically at receive with no re-prompt, and core-only partial receive is supported</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A PO on the Bulk Receive page holds a cored part.</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A PO on the Bulk Receive page holds a cored part whose core was already decided (OK or Not OK) on the work order.</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Receive only the cored line (core-only partial receive).
-2. Confirm an Ok/Not OK resolution becomes available for the core.</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
+2. Watch for any core prompt during the receive.
+3. Check the core's state on the work order lines and the customer invoice afterwards.</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. Core-only partial receive is supported.
-2. Once the cored part is received, its Ok/Not OK resolution becomes available (for Story 3/4 resolution).
-3. Consistent with the completion rule that a waiting core cannot be skipped: the core must be received (core-only partial receive supported) before its Ok / Not OK can be resolved.</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>SV-7703 (S8-C1 / S8-C2)</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Verify each vendor group has an 'Apply to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
+2. The saved OK / Not OK decision is applied automatically at receive — the user is NOT asked again (no duplicate prompt).
+3. The received core shows its resolved state with no OK / Not OK buttons, and the customer invoice does not change at receive.</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>SV-7703, SV-8353 (S18 C-R5)</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Verify a part-sale-originated PO can be received on the Bulk Receive page like a work-order PO</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>PO Bulk Receive Page (Story 8)</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A part-sale purchase order is waiting to receive and is on the Bulk Receive page.</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>1. Find the part-sale PO under its vendor group on the Bulk Receive page.
+2. Select it, enter the vendor invoice number and receive it.
+3. Check the part sale afterwards.</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>1. The part-sale PO appears under its vendor group like a work-order PO.
+2. It can be received on this page via the same receive pipeline.
+3. The part sale progresses normally after receiving (no errors).</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>SV-7703 (S8 AC (part-sale POs) + §8 Part Sales — confirmed)</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Verify each vendor group has an invoice number field under the vendor name, available only when at least one PO of that vendor is selected (no Apply button)</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has a vendor group with multiple POs.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>1. Locate the 'Apply to selected POs' control under the vendor name.
-2. With no invoice # and no PO selected, confirm it is disabled.
-3. Enter an invoice # and select at least one PO under that vendor.</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>1. The control appears under the vendor name.
-2. It is enabled only when an invoice number is entered and at least one PO under that vendor is selected.</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>1. Look under the vendor name for the field to enter one invoice number.
+2. With no PO of that vendor selected, confirm the field is not available.
+3. Select at least one PO under that vendor and type an invoice number.</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>1. A field to enter one invoice number for that vendor's POs sits under the vendor name.
+2. It is available only when at least one PO under that vendor is selected.
+3. There is no 'Apply' button — the number is remembered as typed.</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R1)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Verify a typed invoice number fills only the selected POs of that vendor with no Apply click, still editable per PO</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor group has several POs; some are selected.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>1. Enter one invoice number.
-2. Click Apply.
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1. Select some POs under a vendor (leave others unselected).
+2. Type one invoice number in that vendor's invoice number field.
 3. Inspect the selected and unselected POs' invoice fields.
 4. Edit one PO's invoice number.</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>1. The invoice number is pre-filled into only the selected POs of that vendor.
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>1. The typed number is filled into only the selected POs of that vendor — no Apply click needed (the number is remembered as typed).
 2. Unselected POs are not changed.
-3. Each PO's invoice number remains editable after Apply.</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
+3. Each PO's invoice number remains editable afterwards; then Receive all works for that vendor.</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R2)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Verify the vendor invoice number field is scoped per vendor, absent for the vendorless group, and allows a reused invoice number</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has multiple vendor groups plus a vendorless group.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>1. Confirm Apply Invoice is available per vendor group.
-2. Confirm the vendorless group has no Apply Invoice control.
-3. Apply the same invoice number to POs where uniqueness is relaxed.</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>1. Apply Invoice is scoped to each vendor group.
-2. The vendorless group has no Apply Invoice control.
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>1. Confirm each vendor group has its own invoice number field.
+2. Confirm the vendorless group shows no invoice number field.
+3. Type the same invoice number for POs of another vendor.</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>1. The invoice number field is scoped to each vendor group — other vendors' POs and unselected POs are unaffected.
+2. The vendorless group shows no invoice-number field (assign a vendor first).
 3. The same invoice number can be reused (uniqueness relaxed).</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R3)</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part with no part number is on a PO or receive surface.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. Locate the 'Missing part number' indicator on the part.
 2. Click Edit and enter a part number.
 3. Save and reload.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. The part shows 'Missing part number' with an Edit action.
 2. Entering and saving a part number persists it immediately.
 3. A part number is mandatory to receive.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10-R1)</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Verify a NEW part number can be entered and saved so the part can be received</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part with a newly-entered part number (not matching any existing item) is ready to receive with a vendor assigned.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Enter a brand-new part number and save.
 2. Receive the part.
 3. Check inventory and Part History for the new item.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. The new part number saves and stays on the part.
 2. Once the part has a part number (plus the required cost / sell price and a vendor invoice number), it can be received.
 3. The part-number entry does not have to create a new inventory or catalog item with stock for this to pass.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10-R1 (PN mandatory to receive); S10-R2 struck (first-class part not required in v1))</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Verify an EXISTING part number can be entered so the part can be received, without overwriting the item's description or category</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. An inventory item with a known part number exists; a part on a PO can be given that number.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Enter the existing part number on the part and save.
 2. Receive the part.
 3. Check the linked item's stock, received cost, Part History, description and category.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The existing part number saves on the part.
 2. The part can be received once it has the number (plus the required cost / sell price and a vendor invoice number).
@@ -4980,48 +5513,48 @@
 4. Linking the part into a first-class inventory item (updating its stock / cost / history) is not required for this to pass.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10-R1 (PN mandatory to receive); S10-R2 struck (linking to first-class item not required in v1))</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid WO and a part on an open WO are available.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. On the open WO part, confirm qty/cost/sell are editable.
 2. On the invoiced/paid WO part, confirm sell is locked and cost is editable.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. Open work order: quantity, cost and sell are editable.
 2. Invoiced/paid work order: sell is locked (lock icon + tooltip), only cost editable.
@@ -5029,49 +5562,49 @@
 4. Cost is editable when $0 or missing on either receive surface.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>SV-7703, SV-7705 (S10-R2 / S8-R7)</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part without a part number is on a receive surface.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to receive the part with no part number.
 2. For a vendor-missing part, attempt to receive with no vendor.
 3. Attempt to receive with no cost / sell price entered.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. A part cannot be received without a part number.
 2. A vendor-missing part cannot be received without a vendor.
@@ -5079,331 +5612,332 @@
 4. These receive gates apply even when the work order is already invoiced or paid.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>SV-7705, SV-7708 (S10 Negative / S13-R6 / S13-R7)</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Verify the inline part-number save persists and enables receiving</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A default part category exists and a vendor is assigned to the part.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Enter a part number inline and receive.
 2. Verify a CataloguePart and an inventory stock Part were created (not just a string on the request).
 3. Verify Part History exists.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. The part number entered inline is saved and persists (it is not lost).
 2. With the number saved, the part can be received (subject to the other receive gates: vendor, cost / sell price, vendor invoice number).
 3. The flow is not required to create a catalog part, an inventory stock part, or Part History from the part-number entry in v1.</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10-R1 + S10 technical guardrails; S10-R2 struck (catalog/inventory creation not required in v1))</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO-originated PO exists.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Open /parts/orders and find the WO-originated PO.
 2. Confirm a Receive action on the PO row.
 3. Open the PO detail card and confirm a Receive action there too.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. The PO list row shows a Receive action.
 2. The PO detail card also shows a Receive action (the detail card previously hid it).</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R1)</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO-originated PO with an unreceived part exists.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. Click Receive on the PO.
 2. Observe the destination surface.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. The shared Accept Delivery surface opens for that PO.</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R2)</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. An Office / read-only user credential (no Order Parts) exists.
 2. A fulfilled PO and an unfulfilled PO exist.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as an Office / read-only user and open the PO list.
 2. Confirm the Receive action is hidden for them.
 3. As an authorized user, confirm the Receive action is hidden on a fulfilled PO.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or detail.
 2. Fulfilled POs do not show the Receive action.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R3)</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A multi-vendor delivery exists at /parts/deliveries.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Open Accept Delivery / Vendor Invoices at /parts/deliveries.
 2. Confirm grouping by vendor.
 3. Confirm each vendor group has its own invoice #, date, tax, note and Receive.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. The screen groups items by vendor.
 2. Each vendor group has its own invoice number, date, tax, note and Receive action.
 3. Multiple vendors on one PO are supported (existing behavior).</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12 (existing multi-vendor))</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Verify vendorless / no-part-number Work Order parts appear and can be received on the Receive (Accept Delivery) screen, and the Vendor Missing group sits per the agreed rule (top on Bulk Receive, bottom on the Receive screen)</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A WO has a vendorless/no-PN part and a WO-originated PO reached via the Receive button.</t>
-        </is>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Accept Delivery for the WO.
-2. Confirm the vendorless/no-PN parts appear.
-3. Confirm the vendor-missing group is at the top (leading).</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>1. New vendorless/no-PN WO parts appear and are receivable here.
-2. WO-originated POs reached via the Receive button appear.
-3. Vendor-missing parts sit in their own group that LEADS (appears at the top), because they need action (assign a vendor) before receiving.</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>SV-7707 (S12-R1)</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin (or a role with receiving access).
+2. A Work Order has a part with no vendor and no part number, plus a WO-created Purchase Order that is opened using the Receive button on the Work Order.</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>1. On the Work Order, click the Receive button to open the Receive (Accept Delivery) screen (headed Purchase Order Details).
+2. Confirm the vendorless / no-part-number parts are listed and can be received here.
+3. Note where the Vendor Missing group sits on this Receive (Accept Delivery) screen.
+4. Open the Bulk Receive page (headed Receive Vendor Parts) for the same Purchase Orders and note where the Vendor Missing group sits there.</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>1. The vendorless / no-part-number Work Order parts appear in the Vendor Missing group and can be received once a vendor is chosen (Select Vendor) and a Part Number is entered.
+2. WO-created Purchase Orders opened with the Receive button appear on the Receive (Accept Delivery) screen and are receivable.
+3. The Vendor Missing group is positioned per the agreed rule (Milos, 2026-07-16): on the Bulk Receive page (Receive Vendor Parts) it leads at the TOP; on the Receive (Accept Delivery) screen it sits at the BOTTOM.</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>SV-7707 (S12-R1 (+ Milos Round-3 2026-07-16))</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing / no-PN part is in an Accept Delivery group.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. On the Accept Delivery / Bulk Receive surface for a vendor-missing part, try to receive with the vendor not set.
 2. Set the vendor but leave the part number empty and try to receive.
@@ -5411,7 +5945,7 @@
 4. Enter the vendor invoice number and all of the above, then receive.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked until a vendor is set.
 2. Receiving is blocked until a part number is entered.
@@ -5419,860 +5953,1145 @@
 4. Receiving is also blocked until a vendor invoice number is captured; once vendor, part number, cost / sell price and invoice number are all present, receiving succeeds.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>SV-7707, SV-7708 (S12-R2 / S13-R6 / S13-R7)</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Verify the multi-vendor '+N' indicator and the Vendor Missing group position on the receiving screens</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A multi-vendor delivery with a vendor-missing group exists.</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>1. Open Accept Delivery.
-2. Confirm the '+N' vendor indicator.
-3. Confirm the ordering of the vendor-missing group.</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>1. A '+N' indicator summarizes multiple vendors.
-2. The vendor-missing group leads (appears first).</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>SV-7707 (S12-R3)</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin (or a role with receiving access).
+2. A multi-vendor Purchase Order that also includes parts with no vendor (a Vendor Missing group) exists.</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the Purchase Orders list (Parts &gt; Purchase Orders) and look at the vendor indicator on a multi-vendor Purchase Order.
+2. Open the Receive (Accept Delivery) screen from the Work Order Receive button and note where the Vendor Missing group sits.
+3. Open the Bulk Receive page (Receive Vendor Parts) and note where the Vendor Missing group sits.</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>1. A multi-vendor Purchase Order shows a '+N' indicator (for example '+1' or '+4') on the Purchase Orders list summarizing the extra vendors. (On the Receive / Accept Delivery screen the vendor names are listed in full instead of a '+N' badge.)
+2. The Vendor Missing group is positioned per the agreed rule (Milos, 2026-07-16): on the Bulk Receive page (Receive Vendor Parts) it leads at the TOP; on the Receive (Accept Delivery) screen it sits at the BOTTOM.</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>SV-7707 (S12-R3 (+ Milos Round-3 2026-07-16))</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A multi-vendor delivery is received.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. Receive each vendor group with its own invoice number.
 2. Check QuickBooks / AP for the resulting bills.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. Each vendor group creates its own vendor bill.
 2. Each syncs to QuickBooks as a separate AP entry.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R4)</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A delivery item with a known ordered quantity is on Accept Delivery.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Set the received quantity above the ordered quantity.
 2. Observe the warning.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. A 'received more than ordered' warning is shown (existing behavior).</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12 (existing) received-more-than-ordered)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. An Accept Delivery group has a line whose cost is $0 or missing (cost is pulled from the WO/PO when available).</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Open Accept Delivery for the delivery.
 2. Locate a line with a $0 or missing cost and edit the cost.
 3. Confirm the quantity remains editable and the sell-price lock rule is unchanged.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. Cost is editable on Accept Delivery when $0 or missing (matching Bulk Receive / Story 8 / Story 10).
 2. Quantity stays editable.
 3. The sell-price lock rule is unchanged (sell locks only after the work order is invoiced/paid).</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R5)</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Verify returning from receiving lands on the exact work order line the receive started from, not the top of the work order</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Receive Button on WO POs (Story 11)</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order has several lines and a line far down the page has an un-received part.</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>1. From that line, click Receive (Receive opens Accept Delivery).
+2. Receive the part and go back to the work order.
+3. Observe where the page lands.</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>1. The user is returned to the exact work order line they received from — the page scrolls/focuses to the originating line, not the top of the work order — giving instant visual confirmation of the received part.</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>SV-7698, SV-7706 (S11-R4 (+ S3-R5 amendment))</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Verify clicking Receive on a single work order part opens Accept Delivery showing all of that vendor's to-receive parts plus the vendorless group</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>Accept Delivery (Story 12)</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order part has a vendor that also has other parts waiting to receive, and a vendorless part is waiting to receive too.</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Receive on the single work order part.
+2. Observe which parts the Accept Delivery screen shows.</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>1. Accept Delivery shows all to-receive parts for that part's vendor (other vendors' parts are not shown).
+2. The vendorless group is also shown alongside them.</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>SV-7707 (S12-R6)</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Verify a vendorless part can be assigned a vendor / merged into the single-part receive on the spot, reusing the same invoice number</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Accept Delivery (Story 12)</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. You are on the Accept Delivery screen opened from a single work order part, and the vendorless group is showing a part.</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>1. Assign a vendor to the vendorless part (or merge it into this receive).
+2. Receive both parts using the same invoice number.</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>1. The vendorless part can be assigned a vendor / merged into this receive right there — no need to go back.
+2. The same invoice number is reused for the merged part.
+3. Both parts are received successfully.</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>SV-7707 (S12-R6)</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing group is shown on the receive surface.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Open the vendor-missing group's vendor dropdown.
 2. Choose a vendor.
 3. Reload and confirm the assignment persists.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>1. The vendor dropdown assigns a vendor at PO level.
 2. The assignment is saved locally and to the backend.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R1)</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO already has vendor X, and a vendor-missing group on the same PO is being assigned vendor X.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. Assign the same vendor that is already on this PO.
 2. Observe the prompt.
 3. Try both 'Yes, Merge' and 'No, Keep Separate' in separate runs.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>1. A prompt 'Add to {vendor}?' appears.
 2. 'Yes, Merge' combines into one group; 'No, Keep Separate' keeps two invoice numbers for the same vendor on one PO (valid).</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R2)</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same WO exist; vendor Y is on the other PO.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. Assign vendor Y to the vendor-missing group.
 2. Accept the merge prompt.
 3. Confirm items moved and the emptied source PO is removed.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. A prompt to merge the POs appears.
 2. Items move to the target PO; the emptied source PO is removed.
 3. The view redirects to the target PO.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R3)</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing group is being assigned a brand-new vendor (no collision).</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. Assign a different vendor that is not already on any PO for this WO.
 2. Observe the QuickBooks flag.
 3. Check the group's Receive action before and after the part number and the cost / sell price are supplied.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. Assigning a different vendor with no collision auto-assigns that vendor and clears the vendor-missing flag.
 2. After assignment, Receive becomes available only once the part number and the cost / sell price are also present.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R4 / S13-R5 / S13-R6 / S13-R7)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two vendors share the same name but different IDs; an invoiced/paid WO with a vendor-missing PO exists.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. Assign a vendor and confirm matching is by ID (same-name different-ID vendors are not treated as the same).
 2. Attempt a merge across different work orders.
 3. Attempt to receive on the invoiced/paid WO.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>1. Vendors are matched by ID, not name.
 2. Merge only applies within the same work order.
 3. Receiving is blocked when the WO is invoiced/paid.</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13 Technical guardrails)</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. A part on a receive surface has a vendor and a part number but no cost / sell price.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the part.
 2. Leave the cost / sell price empty and check the Receive action.
 3. Enter a cost / sell price and check the Receive action again.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. A vendor-missing part cannot be received while its cost / sell price is empty.
 2. Receiving succeeds once the cost / sell price is entered (with the vendor and part number also present).</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R7)</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Verify an assigned vendor stays changeable via the same dropdown until the part is received or the work order is invoiced/paid</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Assign Vendor + Merge (Story 13)</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A PO part has a vendor assigned but is not yet received; another part is already received (or its work order is invoiced/paid).</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>1. On the un-received part, open the vendor dropdown and pick a different vendor.
+2. On the received (or invoiced/paid) part, try to change the vendor.</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>1. The vendor is NOT locked on selection — it can be changed via the same dropdown, so a wrong pick can be corrected before receiving.
+2. Once the part is received or the work order is invoiced/paid, the vendor can no longer be changed.</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>SV-7708 (S13-R8 (SV-8343))</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Verify the part number stays editable via the edit icon after entry until the part is received or the work order is invoiced/paid</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Assign Vendor + Merge (Story 13)</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A PO part has a part number entered but is not yet received; another part is already received (or its work order is invoiced/paid).</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>1. On the un-received part, use the edit icon to change the part number.
+2. On the received (or invoiced/paid) part, try to edit the part number.</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>1. The part number remains editable (edit icon) after entry, under the same condition as the vendor — until the part is received or the work order is invoiced/paid.
+2. Once the part is received or the work order is invoiced/paid, the part number can no longer be edited.</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>SV-7708 (S13-R8 (SV-8343))</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Work Orders list is open with WOs that have unreceived parts.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work Orders list column selector.
 2. Enable 'Waiting on Parts'.
 3. Read the column values across statuses.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>1. The Work Orders list column selector offers a 'Waiting on Parts' column (off by default).
 2. When enabled, it shows the count of unreceived parts per work order across all statuses.</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R1)</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Waiting on Parts column is enabled and a WO shows a count.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Click the count on a work order row.
 2. Observe the destination.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. Clicking the count opens the receiving surface for the work order's first unreceived purchase order. In the current build this is the consolidated Bulk Receive page (/bulk-receive), which supersedes the legacy Accept Delivery screen for work-order POs.
 2. Receiving from there behaves as it does on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R2)</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO with nothing to receive (or POs off) is in the list with the column enabled.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>1. Find a WO with nothing waiting to receive.
 2. Read its Waiting on Parts cell.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr">
         <is>
           <t>1. A work order with nothing to receive shows an em dash ('—') in the Waiting on Parts column, with no clickable link.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R3)</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Verify part-sale orders behave with the Waiting on Parts column — unreceived count and receive shortcut work without errors</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Waiting on Parts Column (Story 14)</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. The Waiting on Parts column is enabled and a Part Sale has an unreceived vendor part.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>1. Locate the part-sale order on the list where the Waiting on Parts column shows.
+2. Check its unreceived-parts count and click it.
+3. Receive via the shortcut and re-check the count.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>1. The part-sale order's unreceived parts are counted consistently in the Waiting on Parts column (or the order is cleanly excluded — no error, no broken link).
+2. The receive shortcut behaves like it does for work orders.
+3. After receiving, the count updates correctly.</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>SV-7709 (§8 Part Sales — confirmed (remaining check))</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Require Review Before Completion is ON and saved.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>1. Open a work order with approved lines.
 2. Start completion.
 3. Observe that the review flow is used.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review ON, completing routes into the review flow rather than completing directly.
 2. When the last open line is resolved (by any path) while Require Review is on, the work order routes to Ready for Review — it never auto-completes.</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R1 + S16-R12)</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I133" s="2" t="inlineStr"/>
+      <c r="J133" s="2" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>Verify the completion action reads 'Send To Review' when Require Review is on</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON.
 3. A work order with approved lines is ready to complete.</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>1. Open a work order that is ready to complete, with Require Review Before Completion turned on.
 2. Read the primary action button on the work order (and, for a work order that still has parts to receive, the heading of the dialog that opens).</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review Before Completion ON, a ready work order's primary action button reads 'Send To Review' (it replaces 'Complete Work Order').
 2. For a work order that still has parts waiting to receive, clicking 'Send To Review' opens a dialog headed 'Complete &amp; Send to Review' that shows how many parts are waiting to receive and offers 'Receive Parts' and 'Send To Review'.</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R2)</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON.
 3. A work order missing mileage/hours/VIN is ready to complete.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Start completion and reach the Details step.
 2. Note which vehicle fields are collected.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. When Require Review is on, the completion Details step collects Mileage and Engine Hours only.
 2. There is no VIN field in the completion modal; VIN is captured later by the reviewer in the Mark Reviewed dialog.</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R3)</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON with a part-bearing work order.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Start completion and click Receive Parts.
 2. Observe the destination.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. Receive Parts opens the shared receive page (not an inline modal).</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R4)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order with approved lines is ready to send to review (for a work order with parts still to receive, the 'Complete &amp; Send to Review' dialog is open).</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Click Send To Review (the primary action button, or the 'Send To Review' button in the 'Complete &amp; Send to Review' dialog for a part-bearing work order).
 2. Observe the work order status and banner.
 3. Check the lines state and inventory pick state.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. The work order status becomes Review (amber).
 2. A 'Ready for Review' / 'Sent for review' indication is shown.
@@ -6280,957 +7099,956 @@
 4. The same Review / Ready-for-Review end state is reached when the last open line auto-resolves under Require Review on, not only when Send To Review is clicked explicitly.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R5 / R6 + S16-R12)</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Review state.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Click Mark Reviewed.
 2. Observe the VIN field.
 3. Clear the VIN and check the Confirm Review button, then enter a VIN.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. The Mark Reviewed dialog shows a VIN / Serial # field, required if the work order is missing a valid VIN.
 2. Confirm Review is disabled until a VIN is present.
 3. Once a VIN is entered, Confirm Review is enabled.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 / R10)</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order with an inventory line just went to Review.</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order in Review state.
 2. Check the line states.
 3. Check whether inventory was auto-picked.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. Lines are locked to Complete.
 2. Inventory has been auto-picked.</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R6)</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Review with the Mark Reviewed dialog filled (VIN present).</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Click Confirm Review.
 2. Observe the resulting work order state.
 3. Look for a separate final 'Complete Work Order' action.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. After Confirm Review the sign-off completes and the work order moves directly Review -&gt; Complete.
 2. There is no distinct 'Reviewed' holding state and no separate final 'Complete Work Order' click.
 3. Note: with Require Review on, resolving the last open line first routes the work order to Ready for Review; sign-off (Confirm Review) then moves it to Complete.</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R5 / R8 (direct sign-off, no separate Complete) + S16-R12)</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. A role with Review Work Orders and a role without it both exist.
 2. A work order is in Review state, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as a role without Review Work Orders and open the work order in Review.
 2. Confirm Mark Reviewed is disabled with 'Awaiting review'.
 3. Sign in as a role with Review Work Orders (system defaults grant it broadly; it can be limited to manager/foreman via custom roles) and confirm Mark Reviewed is available.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. A role without the Review Work Orders permission sees Mark Reviewed disabled with an 'Awaiting review' indicator.
 2. A role with the Review Work Orders permission can Mark Reviewed and sign off.
 3. A user who holds the Review Work Orders permission may Mark Reviewed a work order they completed themselves — self-review is allowed in v1 with NO reviewer != completer identity restriction (the gate is purely the permission).</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 (role-gating))</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open.</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Open the Mark Reviewed dialog.
 2. Confirm a required VIN / Serial # field (Confirm disabled until VIN entered).
 3. Confirm there is no review note field, then complete the sign-off.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. The Mark Reviewed dialog shows a VIN / Serial # field that is required (Confirm Reviewed is disabled until VIN is entered).
 2. There is no review note field on the dialog.
 3. The sign-off completes using the VIN / Serial # only.</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 (VIN required, no note))</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Reviewed state (or a Review state before sign-off for the invoicing-block check).</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Before sign-off, attempt to invoice the work order.
 2. Complete the review sign-off (Confirm Review).
 3. Confirm the work order becomes Complete (invoice-ready).</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. Invoicing is blocked until the work order is reviewed.
 2. After sign-off the work order moves directly Review -&gt; Complete (invoice-ready), with no separate final Complete Work Order click.
 3. With Require Review on the work order never auto-completes on last-line-resolve; it routes to Ready for Review and invoicing stays blocked until it is reviewed.</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R8 + S16-R12)</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. At least one work order is in Review state.</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work Orders list.
 2. Look for a 'Ready for Review' filter or column.
 3. Confirm work orders in Review appear in it.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. A 'Ready for Review' filter/column lists work orders awaiting review.</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R9)</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Verify all lines must be approved before Send To Review (the 'Send To Review' action is disabled until every line is approved)</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order has one unapproved line.</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and locate the 'Send To Review' action while a line is still unapproved.
 2. Attempt to use Send To Review with the unapproved line.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. The 'Send To Review' action cannot be used while any line is unapproved - the 'Send To Review' button is disabled until every line has been approved.</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R11)</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Verify cores are decided before receiving ahead of Send to Review, and invoicing stays blocked until Reviewed and every core is decided</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order has inventory and special-order cores.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Resolve inventory cores in the completion modal (after Pick) before Send to Review.
-2. For required-invoice, resolve special-order cores after the Receive round-trip before Send to Review; for optional-invoice, resolve at the Create Invoice gate after sign-off.
-3. Attempt to invoice before both Reviewed and cores are resolved.</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
+2. Decide the special-order cores OK / Not OK on the resolve screen BEFORE receiving, before Send to Review (same in required- and optional-invoice flows).
+3. Attempt to invoice before the work order is Reviewed and before every core is decided.</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. Inventory cores are resolved before Send to Review.
-2. Special-order cores follow the vendor-invoice rules.
-3. Invoicing is blocked until the WO is Reviewed AND all cores are resolved.
-4. In the review flow too, a waiting special-order core cannot be skipped: Send to Review / completion is blocked until the core is received and resolved, and invoicing stays blocked until both Reviewed and all cores resolved.</t>
-        </is>
-      </c>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>SV-7870 (R Core parts / invoicing block)</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Require Review default for new vs existing orgs matches the agreed cohort rule</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
+2. Special-order cores are pre-resolved before receiving on the resolve screen before Send to Review — no longer deferred to the Create Invoice gate.
+3. Invoicing is blocked until the work order is Reviewed AND every core is decided; only an undecided core blocks — a decided (un-received) core does not.</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870, SV-8353 (S18 / Story 16 core paragraph)</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Verify Require Review Before Completion starts ON for a brand-new organization, and existing organizations keep today's behavior</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>1. A newly-created org and an existing org are available.
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>1. A brand-new organization / account (no settings changed yet) and an existing organization are available.
 2. Signed in as Admin for each.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>1. Check the Require Review default on a brand-new org.
-2. Check that existing orgs keep today's behavior (backfilled).</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr">
-        <is>
-          <t>1. On a brand-new org the Require Review Before Completion setting shows its default state.
-2. Existing orgs keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
-        </is>
-      </c>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>SV-7870 (R Open (default))</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>1. On a brand-new organization, open Settings &gt; Work Orders and check the Require Review Before Completion setting.
+2. On an existing organization, confirm its completion behavior is unchanged (the setting is backfilled).</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>1. On a brand-new organization / account, Require Review Before Completion defaults to ON (Milos decision, 2026-07-16: it stays ON for every new organization).
+2. Existing organizations keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (R Open (default) - Milos Round-3 2026-07-16: ON for new orgs)</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You are on the Create Work Order form (/workorders → Create).</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Open the Create Work Order form.
 2. Read the primary button label.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. The primary button reads 'Create Work Order'.</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R1)</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order requiring mileage/VIN is being completed.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Observe where required fields are collected.
 3. Confirm the tech story is handled by its own flow, not inside this modal.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. The required vehicle fields (Mileage and Engine Hours) are collected in a centralized center modal titled 'Complete Work Order'.
 2. The tech story is NOT part of this modal (it is handled by its own line-level flow).</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R2)</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has just been completed.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. Read the success screen.
 2. Confirm WO number, total, Done and Go to Invoice.
 3. Confirm the invoice number is shown on the Finance step, not the success screen.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. The success screen shows the WO number and total with Done and Go to Invoice.
 2. The invoice number appears on the Finance step, not on the success screen.</t>
         </is>
       </c>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R3)</t>
         </is>
       </c>
-      <c r="I133" s="2" t="inlineStr"/>
-      <c r="J133" s="2" t="inlineStr"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completion modal is open.</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. Trigger the close-confirmation modal.
 2. Click Close (prominent/red) and observe.
 3. Trigger it again and click Cancel (text link, far left) and observe.</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. Close (prominent/red button) closes the confirmation modal only, discards nothing (no discard warning), and stays on the work order.
 2. Cancel (text link, far left) closes the modal and returns to the previous screen.
 3. Other consumers of the shared confirmation dialog keep their existing action labels.</t>
         </is>
       </c>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R4)</t>
         </is>
       </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. A role with the App Settings permission (e.g. Admin) and a role without it (e.g. Service Advisor or Technician) both exist.
 2. You can sign in as each.</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as a role with App Settings and open and modify /administration/settings → Work Orders.
 2. Sign in as a role without App Settings and attempt to open and modify the same page.
 3. As the role without App Settings, attempt to save a Work Order settings change directly (API), and note the response.</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can view and modify the Work Order settings page.
 2. A role without App Settings cannot open or change the Work Order settings.
 3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
         </is>
       </c>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>SV-7696 (S1 AC / §8 Permissions)</t>
         </is>
       </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for several roles exist.
 2. A work order ready to complete exists.</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to complete a work order.
 2. Record which roles can and cannot.</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. Roles with Work Orders: Create &amp; Edit plus WO Lines: Create &amp; Edit and Full View (needed to approve all lines) can complete a work order: Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
 2. Technician and Parts Tech cannot complete (Technician cannot approve lines in Tech View and/or lacks Work Orders: Create &amp; Edit; Parts Tech is a receiver, not a completer).
 3. Office, Sales Rep and Time Clock cannot complete a work order.</t>
         </is>
       </c>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>§8 Permissions</t>
         </is>
       </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for several roles exist.
 2. The Bulk Receive flow is available (Story 7/8 built).</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to reach and use Bulk Receive.
 2. Record the outcomes.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
 2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot receive.
 3. Sales Rep and Time Clock cannot reach Bulk Receive.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>§8 Permissions</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for roles with and without Review Work Orders exist.
 2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to Mark Reviewed.
 2. Record which roles can and cannot.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. Mark Reviewed (review sign-off) requires the Review Work Orders permission; system defaults grant it broadly, and it can be narrowed to manager/foreman via custom roles.
 2. A role without Review Work Orders sees Mark Reviewed disabled with an 'Awaiting review' indicator.
 3. A user who holds the Review Work Orders / Mark Reviewed permission may Mark Reviewed a work order they completed themselves — self-review is allowed in v1. There is NO reviewer != completer identity restriction; the gate is purely the permission.</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 / §8 role-gating review)</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. An Office / read-only credential (no Order Parts) exists.
 2. A WO-originated PO exists, plus a fulfilled PO.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as an Office / read-only user.
 2. Open the PO list and detail.
 3. Confirm the Receive action is not shown, and confirm it is also absent on a fulfilled PO.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or PO detail.
 2. Receive is also hidden for fulfilled (already-received) POs.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R3)</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. Signed in with API access.
 2. A relevant Simple-Flow setting (e.g. Require Vendor Invoice Number) is ON.</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. As a role that lacks the mapped permission, confirm the gated setting or action is hidden or unavailable in the app.
 2. As that same role, try the same setting change directly through the API (bypassing the app) and note the response.
@@ -7238,7 +8056,7 @@
 4. As a role that only has Work Orders: Create &amp; Edit, try to receive parts onto a work order through the API and note the response.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. In the app, a role without the mapped permission does not see or cannot use the gated setting or action (this is the v1 pass criterion).
 2. The Work Order settings save is also blocked at the backend: the unauthorized API request is rejected with HTTP 403.
@@ -7246,185 +8064,185 @@
 4. Because several work-order permissions share the same backend check, any role with Work Orders: Create &amp; Edit can receive parts onto a work order through the API.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>§8 BE enforcement</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for roles with and without Review Work Orders exist.
 2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. Confirm that only roles holding Review Work Orders can sign off, and roles without it cannot.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. Review sign-off is governed by the Review Work Orders custom-role permission (it is NOT open to all users for v1).
 2. The permission gates the Mark Reviewed action (a role without Review Work Orders cannot sign off; a role with it can).
 3. A user who holds the Review Work Orders permission may sign off a work order they completed themselves — self-review is allowed in v1 with NO reviewer != completer identity restriction (the gate is purely the permission).</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>§8 role-gating review</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. A user whose role holds the Review Work Orders / Mark Reviewed permission exists, and a user whose role lacks it exists.
 2. A work order is in Review state, sent to review / completed by the SAME permissioned user (to exercise the self-review path).</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. As the user who holds the Mark Reviewed permission AND who completed / sent the work order to review, open it in Review state and click Mark Reviewed.
 2. Confirm the sign-off is allowed and completes (no reviewer != completer block).
 3. As a user whose role does NOT hold the Mark Reviewed permission, open a work order in Review and check the Mark Reviewed control.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. A user who holds the Review Work Orders / Mark Reviewed permission CAN Mark Reviewed a work order they completed themselves — self-review is allowed in v1 (there is NO reviewer != completer identity restriction).
 2. A user whose role does NOT hold the Mark Reviewed permission cannot sign off — the Mark Reviewed control is disabled with an 'Awaiting review' indicator.
 3. The only gate on Mark Reviewed is the Review Work Orders permission; who completed the work order is irrelevant.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 (review sign-off) — self-review permission-gated (identity rule NOT in v1))</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. A Technician credential exists (WO Lines: Create &amp; Edit, no See Financial Data).
 2. An open work order with a line is available.</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the Technician and open the work order line.
 2. Attempt to add a vendorless / no-part-number part (description + quantity + sell price).</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The Technician cannot add a vendorless / no-part-number part.
 2. The mandatory sell price cannot be entered without See Financial Data, so the add is prevented.</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5 / §9 (See Financial Data gate))</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for each system role exist (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Technician, Parts Manager, Parts Tech, Office, Sales Rep, Time Clock).
 2. A work order ready to complete is available.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. For each role, open the work order and check whether the Complete Work Order action is available and usable.
 2. Record the result per role against the checklist below.
@@ -7432,89 +8250,89 @@
 4. Roles expected NOT to be able to complete: Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. Complete Work Order is available for Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
 2. Complete Work Order is NOT available for Technician, Parts Tech, Office, Sales Rep or Time Clock.
 3. Technician and Parts Tech are blocked because they cannot approve lines and/or lack Work Orders: Create &amp; Edit; Office is view-only; Sales Rep and Time Clock have no work-order edit access.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>§9 per-role completion matrix</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage is ON and the work order has no mileage.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave mileage empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until mileage is entered.</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>SV-7697, SV-7698, SV-7699 (S2-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. VIN is required for this org's completion and the work order has no VIN.
@@ -7522,196 +8340,196 @@
 4. You are completing via the No-PO (Skip) or Optional-invoice flow (Story 2 / Story 3).</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. Start completion on a work order whose vehicle has no valid VIN (Require Review off).
 2. Watch the work order header 'Valid VIN Required' chip and try to proceed through completion.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. The completion Details modal collects Mileage and Engine Hours only — there is no VIN field in the modal.
 2. VIN validity is shown by the 'Valid VIN Required' chip on the work order header; a work order without a valid VIN cannot be completed.
 3. For a review-on work order the VIN is captured later by the reviewer in the Mark Reviewed dialog, not at completion.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699, SV-7710 (S15-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Engine Hours is ON and the work order has no engine hours.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave engine hours empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until engine hours are entered.</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open on a line.</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. Leave the story textarea empty.
 2. Check the Next/Continue button.
 3. Type any text and check again.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. With the textarea empty, Next/Continue is disabled.
 2. After typing text, Next/Continue becomes enabled.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R4)</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is ON and a part is being received.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. On the receive surface, leave the vendor invoice number empty.
 2. Attempt to receive.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor invoice number.
 2. Once an invoice number is entered, receiving is allowed.</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R5 / §4)</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing part is on a receive surface.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. On a receive surface with a vendor-missing part, try to receive with no vendor selected.
 2. Select a vendor but leave the part number empty and try to receive.
@@ -7719,7 +8537,7 @@
 4. Provide vendor, part number and cost / sell price, then receive.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked while no vendor is selected.
 2. Receiving is blocked while the part number is empty.
@@ -7727,708 +8545,713 @@
 4. Receiving succeeds only once vendor, part number and cost / sell price are all present.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>SV-7705, SV-7707, SV-7708 (S10 / S12-R2 / S13-R6 / S13-R7)</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open on a WO with no VIN on the asset.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. Clear the VIN field.
 2. Check the Confirm Review button.
 3. Enter a VIN and check again.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Review is disabled while VIN is empty.
 2. Confirm Review enables after a VIN is entered.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7)</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part-bearing work order had completion started and cancelled once.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. Cancel the first completion attempt.
 2. Start and complete again.
 3. Inspect the POs.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>1. No duplicate POs are created on the second attempt.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>SV-7698 (S3-R9 (idempotency))</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid work order is on a receive surface.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the invoiced/paid WO part.
 2. Try to edit the sell field.
 3. Hover the lock icon.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>1. The sell field is locked (not editable).
 2. A lock icon and tooltip 'Locked — this part is already invoiced or paid' are shown.
 3. Only cost remains editable.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R7 / §4 field locking)</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same vendor are being received.</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. Enter the same invoice number on both POs.
 2. Receive both.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>1. The reused invoice number is accepted (uniqueness is relaxed).
 2. Both POs receive successfully.</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R3 / §4 (uniqueness relaxed))</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Verify an unapproved line disables the Complete Work Order button with a tooltip (regardless of the Require Vendor Invoice Number setting)</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Auto-approve Lines is OFF so a newly added line lands in Needs Approval.
 3. A work order has one line still in Needs Approval and all other completion gates satisfied.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. With Require Vendor Invoice Number ON, open a work order that has one line still in Needs Approval; look at the Complete Work Order button, then hover it.
 2. Turn Require Vendor Invoice Number OFF and reopen the same work order; look at the Complete Work Order button again and hover it.
 3. Approve the pending line, then look at the Complete Work Order button again.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>1. With Require Vendor Invoice Number ON, the Complete Work Order button is disabled; hovering it shows the tooltip 'Every line must be approved or declined in order to complete the work order.' (the tooltip is generic and does not name the specific line).
 2. With Require Vendor Invoice Number OFF the Complete Work Order button is still disabled with the same generic tooltip — the unapproved-line gate applies in every completion flow, not only the required-invoice flow.
 3. Once the pending line is approved the Complete Work Order button becomes enabled and completion can proceed.</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S4-R8 / S3-R9 / Key Decision (line approval))</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has an in-stock inventory part; its on-hand quantity is noted.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order via the simple (skip) path.
 2. Check the part's on-hand quantity and Part History.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>1. The in-stock part's on-hand quantity decrements.
 2. A Part History entry is written.
 3. The skip path's status setter does not bypass inventory movement / Part History / catalog / delivery.</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 1</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create Purchase Orders is OFF.
 3. A work order with a vendor/found part exists.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order with Create POs OFF.
 2. Check for any PO, vendor bill, AP sync.
 3. Check for any catalog/inventory sync of the vendor/found part.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>1. No purchase order, vendor bill or accounts-payable sync is produced.
 2. No catalog or inventory sync happens (the part is received at request time only).</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>§5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create POs is on and a work order has a receivable vendor part.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>1. Receive the part via Accept Delivery.
 2. Check that a Delivery, then a Vendor Bill, then a QuickBooks sync occur.
 3. Repeat via the Bulk Receive surface (once built) and confirm it also syncs.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>1. Receiving creates a Delivery, then a Vendor Bill, then syncs to QuickBooks.
 2. Both receive surfaces sync the vendor bill (only complete-simple bypasses this).</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 2</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless / no-PN part exists on a work order.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>1. Before adding a vendor/PN, check inventory and Part History for the part.
 2. Add a vendor and PN, then re-check.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>1. Before a vendor/PN, there is zero inventory interaction (no item, no history).
 2. After a vendor and PN are added, normal inventory handling applies.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>1. Check QuickBooks sync for the Vendor Missing PO.
 2. Provide a vendor and part number and re-check.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>1. While vendor/PN are missing, the PO is excluded from QuickBooks.
 2. Once both are provided, it becomes eligible for QuickBooks.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (§5 / S6-R3)</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a part with no cost recorded at completion.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order.
 2. Check the resulting cost/margin figures that flow to QuickBooks.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.
 2. For vendorless / no-part-number parts the mandatory sell price is captured at add time behind the See Financial Data gate, so a completing user has a sell figure and $0-cost margins are avoided.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>§8 (cost at completion)</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completed work order is ready to invoice.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>1. Create the invoice.
 2. Check for the Journal Entry / Inventory sync to QuickBooks.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>1. The Journal Entry / Inventory sync to QuickBooks fires on invoice creation.
 2. This sync is not dependent on a PO existing.</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Verify Part History is preserved for a part that is genuinely inventory-tracked</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A genuinely inventory-tracked part exists (an inventory item with stock).</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>1. Use / receive a genuinely inventory-tracked part on a work order and complete it.
 2. Open that part's Part History (Parts &gt; Inventory, the clock icon on the part row).</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>1. For a part that is genuinely inventory-tracked, its Part History is preserved / written.
 2. Simply entering a part number on a previously untracked part is not required to turn it into an inventory-tracked part in v1, so no Part History needs to be created from that entry alone.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (§5 invariant 3 (rescoped after S10-R2 strike))</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Investigate: Part Sales unaffected by the shared order/status logic (requested -&gt; orderable/waiting-to-receive)</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>1. PLACEHOLDER for a new V2.4 §8 open question (needs BE investigation).</t>
-        </is>
-      </c>
-      <c r="F164" s="2" t="inlineStr">
-        <is>
-          <t>1. Investigation pending — steps to be defined once dev confirms whether the shared order/status logic touches Part Sales.</t>
-        </is>
-      </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>1. OPEN / NEEDS INVESTIGATION — expected result to be defined after dev confirmation. Keep Part Sales unchanged unless the shared logic forces a change (V2.4 §8).</t>
-        </is>
-      </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>§8 open question (Part Sales impact — BE investigation)</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A Part Sale exists (or can be created) to which a vendor part can be added.</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>1. Add a vendor part to the Part Sale so a purchase order is created.
+2. Follow the order's status as it is ordered and then received (same PO/receive pipeline as work orders).
+3. Confirm the part sale itself progresses normally after receiving.</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>1. The part-sale purchase order moves through the normal statuses (requested, then waiting to receive, then received) with no errors.
+2. Receiving the part-sale PO behaves like receiving a work-order PO (same pipeline).
+3. The part sale is not broken by the shared order/status logic.</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>SV-7702, SV-7703 (§8 Part Sales — confirmed (Jul 14) + S7/S8 part-sale AC)</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>Verify resolving the last open line by completing a single line auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Require Review Before Completion is OFF (in the Work Orders settings tab).
 3. A work order is in Approved status with two or more open (not-yet-completed) lines.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and complete one line at a time using the per-line Complete action.
 2. After completing the first line (while at least one other line is still open), check the work order status.
@@ -8436,314 +9259,314 @@
 4. Check the work order status again.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>1. While at least one line is still open, the work order stays in Approved.
 2. The moment the last open line is completed, the work order moves to Complete on its own (invoice-ready).
 3. You do not have to click Complete Work Order separately for the work order to reach Complete.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (a) single line)</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>Verify resolving the last open lines in bulk (several at once) auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order is in Approved status with several open lines and nothing left to receive on those lines.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and select all the open lines.
 2. From the bulk actions menu choose Set line status and set the selected lines to Complete (resolving them all at once).
 3. Check the work order status.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>1. All selected lines become Complete in one action.
 2. Because that resolves the last open lines, the work order moves to Complete on its own (invoice-ready).
 3. No separate Complete Work Order step is needed.</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (b) bulk)</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>Verify a split that leaves a work order fully resolved auto-completes that work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order has several lines; some are already completed and at least one line is still open.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and complete all but one line, leaving one line still open (the work order stays Approved).
 2. Select the remaining open line and use the bulk actions menu Split work order to move it to a new work order.
 3. Check the status of the original work order after the split.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>1. The open line moves to a new work order.
 2. The original work order is now fully resolved (all its remaining lines are complete), so it moves to Complete on its own.
 3. No separate Complete Work Order step is needed on the original work order.</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (c) split)</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a line so the remaining lines are all resolved auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order has some completed lines and one remaining open line.</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order (its other lines are already complete; one line is still open).
 2. Select the open line and use the bulk actions menu Delete lines to remove it.
 3. Check the work order status.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>1. The open line is removed.
 2. Because the remaining lines are all complete, the work order moves to Complete on its own.
 3. No separate Complete Work Order step is needed.</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (d) delete line)</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>Verify that with Require Review on, resolving the last open line routes the work order to Ready for Review instead of auto-completing</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is ON and saved.
 3. A work order is in Approved status with two or more open lines.</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and complete the lines one at a time (or in bulk).
 2. After the last open line is resolved, check the work order status.
 3. Confirm whether the work order went straight to Complete or to review.</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>1. When the last open line is resolved, the work order moves to Ready for Review (Review) — it does NOT auto-complete.
 2. The work order must be signed off in the review step before it can reach Complete.</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 review ON)</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>Verify a clock-out that finishes the last line routes the work order to Ready for Review even when Require Review is off</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as a Technician who is clocked into the work on the work order.
 2. Require Review Before Completion is OFF.
 3. The work order has one remaining open line that the technician is working on.</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>1. As the technician, finish the last open line by clocking out of it.
 2. Check the work order status.</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>1. Even though Require Review is off, the work order routes to Ready for Review (not straight to Complete).
 2. This is the one path that does not auto-complete when review is off (a technician may not be allowed to complete a work order).</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R13 clock-out exception)</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t>Verify the work order status transitions on the backend when the last open line is resolved (auto-Complete when review off, Ready for Review when review on)</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B188" s="2" t="inlineStr">
         <is>
           <t>API — Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E188" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Approved status with two or more open lines.</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F188" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review off, resolve the last open line and read the work order record.
 2. Turn Require Review on, and on another work order resolve the last open line and read the work order record.</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G188" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review off, after the last open line resolves the work order record status becomes Complete (the resolve action returns success).
 2. With Require Review on, after the last open line resolves the work order record status becomes Ready for Review (Review), not Complete.</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H188" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 backend status transition)</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr"/>
+      <c r="J188" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J188"/>
+  <dimension ref="A1:J185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2566,12 +2566,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify the required-invoice flow asks to resolve special-order cores FIRST and then to receive them</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2585,657 +2585,652 @@
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A completed (optional-invoice) work order has an unresolved special-order core.</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>1. Click Create Invoice.
-2. In the resolve module, route to receive the cored line (core-only partial receive).
-3. Resolve each core Ok / Not OK.
-4. Continue to invoice.</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>1. The Create Invoice gate opens a resolve module for the unresolved cores.
-2. It routes to receive the cored line(s) (core-only partial receive supported).
-3. After resolving Ok/Not OK the invoice proceeds.
-4. Because a waiting core cannot be skipped, the core line must be received before completion; receiving it settles the core so invoicing can proceed.</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>SV-7698 (S3-C4)</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr"/>
-      <c r="J44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Core parts — Invoice gate</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A completed work order has an unresolved special-order core and you are in the invoice-gate resolve module.</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1. Cancel the resolve module.
-2. Inspect the work order and invoice state.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>1. The work order remains Completed.
-2. It remains un-invoiced.
-3. Cores remain pending.
-4. Note: because the core cannot be skipped at completion, this cancel path applies after completion at the Create Invoice gate; the core stays pending and the work order stays un-invoiced until it is received and resolved.</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>SV-7698 (S3-C4 (cancel path))</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Verify the required-invoice flow asks to resolve special-order cores FIRST and then to receive them</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Core parts — Required invoice (Story 4)</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is ON (Required).
 3. A work order has a special-order cored part.</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
 2. Observe the order of the core steps in the wizard.
 3. Decide the core OK / Not OK on the resolve screen, then Receive Parts and receive it, then Complete.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>1. The wizard asks to resolve the core FIRST (same resolve screen as the optional flow) and then to receive — not resolve-after-receive.
 2. At receive the saved decision is applied automatically; the user is not asked OK / Not OK again.
 3. After all parts are received, Complete succeeds to the Success screen.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>SV-7699, SV-8353 (S18 C-R6)</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr"/>
-      <c r="J46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Verify the completion and invoice gates detect an undecided special-order core that exists only as a requested part</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Core parts — Guardrail</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a special-order cored part that exists only as a part request (not received, no work-order part yet) and is still undecided.</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>1. Try to complete the work order and to create the invoice.
 2. Decide the core OK / Not OK and try again.</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>1. The undecided core is detected even though it exists only as a requested (un-received) part — completing and invoicing are blocked.
 2. Once the core is decided, the gates clear (no receive needed first).</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>SV-8353 (S18 C-R2/C-R4 (guardrail))</t>
         </is>
       </c>
-      <c r="I47" s="2" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Core parts — Guardrail</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A part-sale work order and a service work order, each with a cored part, exist.</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive the cored part on the part-sale work order and check core status.
-2. Receive the cored part on the service work order and check core status.</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>1. On the part-sale WO the core auto-resolves at receive.
-2. On the service WO the core requires manual Ok / Not OK.</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>SV-7698 (S3 Guardrail (part-sale vs service WO))</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Core parts — Resolve step UI</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You are in the Resolve Cores step with multiple cores.</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>1. On the line's Parts view, mark a Core sub-line Not-OK (keep + charge).
 2. Observe the $ amount on that Core sub-line.
 3. Mark the core Ok and observe the $ amount again.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>1. The Core sub-line shows a $ amount on the line's Parts view ($0 until it is marked Not-OK).
 2. Marking the core Not-OK sets the +$ to invoice on that line.
 3. There is no distinct Resolve Cores wizard step with a running total; the core $ is a line-level control.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Resolve Cores handoff (live +$ total)</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>Verify the Resolve cores screen lists every un-received vendor core with part info, core charge and OK / Not OK, plus an invoice-accuracy message</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is OFF (Optional).
 3. A work order has two special-order (vendor) cored parts that have not been received yet.</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
 2. Observe the screen shown right before the Receive parts / Complete without receiving choice.
 3. Read the message on the screen.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>1. A separate, consolidated Resolve cores screen appears, listing EVERY un-received vendor core (both parts).
 2. Each core shows its part info, its core charge and an OK / Not OK choice.
 3. A message explains that resolving now is for invoice accuracy.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>SV-8353 (S18 C-R1)</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr"/>
-      <c r="J50" s="2" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Verify marking a core Not OK immediately adds the core charge to the work order total and customer invoice, while OK adds no charge</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has two un-received vendor cores shown on the Resolve cores screen.</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>1. Mark one core Not OK and note the work order total.
 2. Mark the other core OK and note the total again.
 3. Create the customer invoice and check its amounts.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>1. Not OK: the core charge is priced into the work order total right away and flows to the customer invoice.
 2. OK: no charge is added (the vendor core return is created automatically later, at receive).
 3. The invoice matches the decisions even though no core part has been received.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>SV-8353 (S18 C-R3)</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Verify completion and invoice creation are blocked only while a core is undecided — a decided core does not block</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has two un-received vendor cores.</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>1. Decide one core (OK or Not OK), leave the other undecided; try to complete the work order and to create the invoice.
 2. Decide the remaining core and try again.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>1. With any core still undecided, completing and invoice creation are blocked and a cores-pending indication shows.
 2. Once every core is decided, completion and invoice creation proceed — no receive is required first.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>SV-8353 (S18 C-R4)</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr"/>
-      <c r="J52" s="2" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Verify receiving a pre-resolved core auto-applies the saved decision: OK creates exactly one vendor return, Not OK creates none, the invoice never changes, retries create no duplicates</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has one core pre-resolved OK and another pre-resolved Not OK, both not yet received; the customer invoice is created.</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>1. Receive the OK core; check vendor returns and the customer invoice.
 2. Receive the Not OK core; check again.
 3. Retry / re-submit the receive and re-check for duplicates.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The OK core is received already resolved, with exactly ONE vendor core return created automatically.
 2. The Not OK core is received already resolved, with NO return created.
 3. The user is never asked OK / Not OK again, the customer invoice does not change at receive, and retries create no duplicate cores or returns.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>SV-8353 (S18 C-R5)</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr"/>
-      <c r="J53" s="2" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Verify the receive dialog locks quantity to the full remaining amount once the work order is invoiced/paid, with the core auto-selected and an explanatory tooltip</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. An invoiced/paid work order has an un-received cored part; another (not yet invoiced) work order also has one.</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>1. Open the receive dialog for the invoiced/paid work order's part, try to change the quantity, and hover the field.
 2. Open the receive dialog for the not-yet-invoiced work order's part and change the quantity.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>1. On the invoiced/paid work order the quantity is locked to the full remaining amount, the core is auto-selected, and the tooltip reads 'This part is on a customer invoice and should be received in full'.
 2. Before invoicing, the quantity stays editable (partial receive allowed).
 3. The lock is on the screen only — the customer invoice itself never changes at receive.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>SV-8353 (S18 C-R8)</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr"/>
-      <c r="J54" s="2" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Verify the Lines tab shows the core decision state before and after receive: 'Core decision pending', 'Core OK — return to vendor, no charge', 'Core Not OK — customer charged'</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has three vendor cores: one undecided, one decided OK, one decided Not OK.</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order's Lines tab before receiving and read each core's state.
 2. Receive the two decided cores and re-check the Lines tab.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>1. Before receive: the undecided core shows 'Core decision pending'; the OK core shows 'Core OK — return to vendor, no charge'; the Not OK core shows 'Core Not OK — customer charged'.
 2. After receive, a pre-resolved core shows its resolved state with NO OK / Not OK buttons.
 3. No duplicate core prompts appear anywhere.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>SV-8353 (S18 C-R9)</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr"/>
-      <c r="J55" s="2" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>Verify a core decision cannot be changed once the work order has an active invoice</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Core parts — Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a decided core and an active customer invoice.</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>1. Try to change the core's OK / Not OK decision (on the resolve screen or the Lines tab).</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>1. The decision cannot be changed while the work order has an active invoice.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>SV-8353 (S18 AC (resolution immutable with an active invoice))</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>API: Verify POST /api/work-orders/{id}/pre-resolve-cores persists the core decision on the part request with no side-effect records</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>API — Core Pre-Resolve (Story 18)</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>1. A valid Admin session (API).
 2. A work order with an un-received special-order cored part request exists.</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. POST /api/work-orders/{id}/pre-resolve-cores with the core decision (ok / not_ok).
 2. Re-read the work order's lines / receive-view read models.
 3. Inspect for side-effect records (work-order part, statement item, vendor return).</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>1. The request succeeds (2xx) and core_resolution is persisted on the core work_order_part_request (ok | not_ok; NULL = undecided).
 2. NO WorkOrderPart, statement item, or vendor return is created at this point.
 3. cores_pending reflects only undecided (NULL) cores after the call.</t>
         </is>
       </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 C-R2 / technical plan)</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>API: Verify resolving a received core via the existing handle-core endpoints also writes the decision back to the linked core part request</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>API — Core Pre-Resolve (Story 18)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1. A valid Admin session (API).
+2. A received cored part exists that can be resolved via the existing handle-core(s) endpoints.</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Resolve the received core Ok / Not OK via the existing handle-core(s) endpoint.
+2. Read the linked core part request and its core_resolution value.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>1. The call succeeds and the decision is ALSO written to the linked core PartRequest (core_resolution matches the handle-core decision), keeping core_resolution the single source of history.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>SV-8353 (S18 C-R10)</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Tech Story Flow (Story 17)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Tech Story is ON.
+3. A work order has a line with no tech story yet.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. Open the work order Lines tab.
+2. Look under the line for a Story sub-row.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1. The line has a Story sub-row.
+2. When empty, it shows an 'Add tech story for this line' link.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>SV-7876 (TS-R1)</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Tech Story Flow (Story 17)</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Tech Story is ON.
+3. A work order has at least one line missing a story.</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Complete Work Order.
+2. Observe whether completion proceeds without stories.</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>1. Completion cannot proceed while any line is missing a tech story.
+2. The user is routed to enter the missing stories first.</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8353 (S18 C-R2 / technical plan)</t>
+          <t>SV-7876 (TS-R2)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3244,12 +3239,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>API: Verify resolving a received core via the existing handle-core endpoints also writes the decision back to the linked core part request</t>
+          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>API — Core Pre-Resolve (Story 18)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3259,159 +3254,17 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>1. A valid Admin session (API).
-2. A received cored part exists that can be resolved via the existing handle-core(s) endpoints.</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>1. Resolve the received core Ok / Not OK via the existing handle-core(s) endpoint.
-2. Read the linked core part request and its core_resolution value.</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>1. The call succeeds and the decision is ALSO written to the linked core PartRequest (core_resolution matches the handle-core decision), keeping core_resolution the single source of history.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>SV-8353 (S18 C-R10)</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
-      <c r="J58" s="2" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>Tech Story Flow (Story 17)</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. Require Tech Story is ON.
-3. A work order has a line with no tech story yet.</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>1. Open the work order Lines tab.
-2. Look under the line for a Story sub-row.</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>1. The line has a Story sub-row.
-2. When empty, it shows an 'Add tech story for this line' link.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>SV-7876 (TS-R1)</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Tech Story Flow (Story 17)</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. Require Tech Story is ON.
-3. A work order has at least one line missing a story.</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>1. Click Complete Work Order.
-2. Observe whether completion proceeds without stories.</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>1. Completion cannot proceed while any line is missing a tech story.
-2. The user is routed to enter the missing stories first.</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>SV-7876 (TS-R2)</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Tech Story Flow (Story 17)</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Tech Story is ON.
 3. A work order has a line missing a story.</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>1. Click Complete Work Order.
 2. Observe the first modal that appears.
@@ -3419,49 +3272,49 @@
 4. Observe the next step.</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>1. The tech-story modal opens FIRST (before the completion wizard).
 2. After Continue, the flow chains into the completion wizard (parts/pick → complete).
 3. Gate order is tech story → parts → complete/send-to-review.</t>
         </is>
       </c>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R3)</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open during completion.</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>1. Read the modal header.
 2. Read the per-line card (line #, name, technician).
@@ -3469,49 +3322,49 @@
 4. Leave the textarea empty and check the Next/Continue button.</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The header reads 'Tech story' with 'WO# · Customer'.
 2. A per-line card shows the line number, name and technician; a 'Line X of N' indicator is shown.
 3. The Next/Continue button is disabled until the textarea is non-empty.</t>
         </is>
       </c>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R4)</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has two or more lines all missing stories, and Require Tech Story is ON.</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>1. Start completion so the tech-story modal opens on Line 1 of N.
 2. Enter a story and click Next.
@@ -3519,193 +3372,193 @@
 4. On the last line, check the final button.</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>1. On line 1 there is no Back button; after line 1, a Back button appears.
 2. Each line requires a non-empty story to advance.
 3. The last line shows Continue (chained into completion) or Save.</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R4 (multi-line navigation))</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr"/>
-      <c r="J63" s="2" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A line has a saved tech story.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>1. View the line's Story sub-row.
 2. Confirm the story text and controls.</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>1. The saved story renders inline with a green check and the story text.
 2. An Edit link is available to change it.</t>
         </is>
       </c>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R5)</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr"/>
-      <c r="J64" s="2" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story modal has a text box for typing the story</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open.</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>1. Open the tech-story modal on a line.
 2. Locate the text box where the story is typed.
 3. Type a story into the text box.</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>1. The tech-story modal has a text box (textarea) for the story.
 2. The story text you type is accepted in the box.</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R6 (test id))</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr"/>
-      <c r="J65" s="2" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a line missing a story.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>1. Add a tech story inline via the line's 'Add tech story' link.
 2. On a separate line missing a story, trigger the gate modal by clicking Complete.
 3. Confirm both entry points save a story.</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>1. A tech story can be entered inline on the line (Story 17 is the authoritative behavior).
 2. A story can also be entered via the completion gate modal, which lets stories be completed individually or several at once.
 3. Both paths persist the story.</t>
         </is>
       </c>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>SV-7710, SV-7876 (TS Decision vs S15-R2)</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr"/>
-      <c r="J66" s="2" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. An open work order with a line is on its Lines tab.</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>1. Add a part to a line.
 2. Enter a description, a quantity and a category.
@@ -3713,7 +3566,7 @@
 4. Save the part.</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The part saves successfully with description, quantity and category entered; part number, cost, vendor and sell price may be left empty.
 2. Category is a required field for v1 — the part cannot be saved without a category.
@@ -3721,42 +3574,42 @@
 4. The part appears on the line with its description and quantity and is treated as a vendorless part downstream; it is orderable from the line (Order creates or joins the Vendor-Missing purchase order and moves it to waiting-to-receive).</t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R1)</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The add-part dialog is open on a work order line.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>1. Leave the description empty and try to save.
 2. Fill the description, leave the quantity empty and try to save.
@@ -3764,7 +3617,7 @@
 4. Fill the description, quantity and category but leave the sell price empty and try to save.</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>1. Saving is blocked inline when the description is empty ('Description is a required field').
 2. Saving is blocked inline when the quantity is empty ('Quantity is a required field').
@@ -3772,529 +3625,529 @@
 4. Saving is allowed when only the sell price is empty — sell price is not enforced as a required field for v1.</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R1 / S5 AC (validation))</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr"/>
-      <c r="J68" s="2" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless part has been added to a work order line.</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>1. Open the vendorless part's detail.
 2. Read its source / type field.</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The source is 'vendor' or 'found'.
 2. It is never set to 'inventory'.
 3. It is treated as vendorless downstream.</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R2)</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr"/>
-      <c r="J69" s="2" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless part exists on a work order line.</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>1. Open the vendorless part.
 2. Change its description or quantity and save.</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>1. The part can be edited after creation.
 2. The changes persist.</t>
         </is>
       </c>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R3)</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr"/>
-      <c r="J70" s="2" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part with description + qty + sell but no part number exists on a work order.</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>1. Search inventory for a new item matching the description.
 2. Check for any Part History entry for it.</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>1. No inventory item is created for the no-PN part.
 2. No Part History is written until a part number is added.</t>
         </is>
       </c>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R4 / S5 AC (no inventory interaction))</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr"/>
-      <c r="J71" s="2" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless part (no PN, no vendor) exists on a work order.</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>1. Edit the part and add a part number.
 2. Assign a vendor to it.
 3. Observe the part's vendorless status.</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. Once both a part number and a vendor are present, the part is no longer treated as vendorless.
 2. It becomes eligible for downstream inventory / QuickBooks handling.</t>
         </is>
       </c>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5 AC (transitions out of vendorless))</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr"/>
-      <c r="J72" s="2" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless / no-PN part is on a work order PO.</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>1. Open a receive surface (Accept Delivery / Bulk Receive) for that PO.
 2. Attempt to receive the part without a part number.
 3. Attempt to receive it without a vendor.</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked while the part number is missing.
 2. Receiving is blocked while the vendor is missing.
 3. Receiving is enabled only after both a part number and a vendor are provided.</t>
         </is>
       </c>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5-R4 / S5 AC (receive gate))</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr"/>
-      <c r="J73" s="2" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a vendor part with no vendor assigned and Create POs is on.
 3. The work order has been completed so POs are generated.</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>1. Open the PO list at /parts/orders.
 2. Find the PO for this work order.
 3. Confirm the vendorless part is on that PO.</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The vendorless part is placed on the work order's normal PO.
 2. No separate 'dummy PO' is created for it.</t>
         </is>
       </c>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R1)</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr"/>
-      <c r="J74" s="2" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO exists that holds a part with no vendor.</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>1. Open /parts/orders.
 2. Look for the Vendor Missing indication on the PO row.
 3. Open the PO detail and confirm the indication there.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. The PO list shows a 'Vendor Missing' indication (with '+N' when multiple vendors are involved).
 2. The PO detail also shows the Vendor Missing flag.</t>
         </is>
       </c>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R2)</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr"/>
-      <c r="J75" s="2" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists.
 3. QuickBooks integration is available for inspection.</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>1. Trigger / inspect QuickBooks sync for the PO.
 2. Confirm the Vendor Missing PO is excluded.</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>1. The Vendor Missing PO is flagged.
 2. It is excluded from QuickBooks sync while the vendor is missing.</t>
         </is>
       </c>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R3)</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr"/>
-      <c r="J76" s="2" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO detail is open.</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>1. Open the PO detail.
 2. Look for a way to select a vendor.
 3. Look for a way to enter/edit the missing part number.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. The Vendor Missing PO detail offers a way to select a vendor.
 2. It offers a way to enter or edit the part number.</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R4)</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr"/>
-      <c r="J77" s="2" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists with a part lacking vendor and part number.</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>1. Assign a vendor to the PO.
 2. Enter the missing part number.
 3. Observe the Vendor Missing flag.</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. Once both a vendor and a part number are provided the Vendor Missing flag is removed.
 2. The part becomes eligible for QuickBooks.</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R5)</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr"/>
-      <c r="J78" s="2" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>Verify a Vendor Missing PO's spend is excluded from the QuickBooks Vendor Bill export and the Vendors Expenses report until a vendor is assigned</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO with a non-zero cost exists.</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>1. Open the Vendors Expenses report and look for the vendor-missing PO's spend.
 2. Inspect the QuickBooks Vendor Bill export for that PO.
 3. Assign a vendor to the PO and check both again.</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>1. While the PO has no vendor, its spend is NOT counted in the Vendors Expenses report.
 2. Its spend is excluded from the QuickBooks Vendor Bill export.
@@ -4302,106 +4155,245 @@
 4. Once a vendor is assigned, the spend flows into both normally.</t>
         </is>
       </c>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R6)</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr"/>
-      <c r="J79" s="2" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. An open work order has a sell-price-only line part (sell price set; vendor and/or cost missing; part number empty).</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>1. On the line, use the Order action for the sell-price-only part.
 2. Open the PO list at /parts/orders and find the work order's PO.
 3. Confirm the part's status.</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>1. Ordering from the line creates or joins the work order's Vendor-Missing PO (no separate dummy PO).
 2. The part moves from 'requested' to 'waiting-to-receive' without completing the work order.
 3. At receive, a vendor and part number are still required (cost editable — Story 10).</t>
         </is>
       </c>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (S6-R7)</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr"/>
-      <c r="J80" s="2" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The PO list at /parts/orders has multiple POs.</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1. Open /parts/orders.
 2. Look for a select-all checkbox in the header.
 3. Look for a checkbox on each PO row.</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. A select-all checkbox is present.
 2. Each PO row has its own checkbox.</t>
         </is>
       </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>SV-7702 (S7-R1)</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>PO Multi-Select (Story 7)</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. The PO list has selectable POs.</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>1. Select one or more POs.
+2. Observe the action bar.</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>1. A bar appears reading 'N purchase orders selected'.
+2. The bar has Clear and Receive Selected actions.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>SV-7702 (S7-R2)</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>PO Multi-Select (Story 7)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Two or more POs are selected on the PO list.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>1. Click Receive Selected.
+2. Observe the destination page and the POs shown.</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>1. The PO Bulk Receive page opens (Story 8).
+2. It contains the POs that were selected.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>SV-7702 (S7-R3)</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>PO Multi-Select (Story 7)</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. The PO list contains at least one fulfilled PO.</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>1. Attempt to select a fulfilled PO's checkbox.</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>1. The fulfilled PO cannot be selected (checkbox disabled).</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>SV-7702 (S7-R1)</t>
+          <t>SV-7702 (S7-R4)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4410,7 +4402,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4425,30 +4417,30 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. The PO list has selectable POs.</t>
+2. The PO list contains a Vendor Missing PO.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>1. Select one or more POs.
-2. Observe the action bar.</t>
+          <t>1. Select a Vendor Missing PO.
+2. Confirm its Vendor Missing indication is shown while selected.</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. A bar appears reading 'N purchase orders selected'.
-2. The bar has Clear and Receive Selected actions.</t>
+          <t>1. The Vendor Missing PO is selectable.
+2. Its Vendor Missing status remains clearly indicated.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>SV-7702 (S7-R2)</t>
+          <t>SV-7702 (S7-R5)</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4457,7 +4449,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4472,392 +4464,253 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Two or more POs are selected on the PO list.</t>
+2. The PO list has more POs than fit on one page (or a filter is applied).</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>1. Click Receive Selected.
-2. Observe the destination page and the POs shown.</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>1. The PO Bulk Receive page opens (Story 8).
-2. It contains the POs that were selected.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>SV-7702 (S7-R3)</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
-      <c r="J83" s="2" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>PO Multi-Select (Story 7)</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. The PO list contains at least one fulfilled PO.</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>1. Attempt to select a fulfilled PO's checkbox.</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>1. The fulfilled PO cannot be selected (checkbox disabled).</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>SV-7702 (S7-R4)</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
-      <c r="J84" s="2" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>PO Multi-Select (Story 7)</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. The PO list contains a Vendor Missing PO.</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>1. Select a Vendor Missing PO.
-2. Confirm its Vendor Missing indication is shown while selected.</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>1. The Vendor Missing PO is selectable.
-2. Its Vendor Missing status remains clearly indicated.</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>SV-7702 (S7-R5)</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
-      <c r="J85" s="2" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>PO Multi-Select (Story 7)</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. The PO list has more POs than fit on one page (or a filter is applied).</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Apply a filter or page the list.
 2. Click select-all.
 3. Check which POs are selected.</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>1. Select-all only selects POs in the current page/filter, not the whole dataset.</t>
         </is>
       </c>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7 (select-all scope))</t>
         </is>
       </c>
-      <c r="I86" s="2" t="inlineStr"/>
-      <c r="J86" s="2" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>Verify part-sale-originated POs appear in the PO list and are selectable like work-order POs</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Part Sale with a vendor part exists, so a part-sale purchase order was created.</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>1. Open the Purchase Orders list and find the part-sale PO.
 2. Select it (checkbox) together with work-order POs and use Receive Selected.</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>1. The part-sale-originated PO appears in the PO list.
 2. It is selectable and joins the Receive Selected flow like a work-order PO.</t>
         </is>
       </c>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>SV-7702 (S7 AC (part-sale POs) + §8 Part Sales — confirmed)</t>
         </is>
       </c>
-      <c r="I87" s="2" t="inlineStr"/>
-      <c r="J87" s="2" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>Verify the Bulk Receive page has a 'Back To Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You reached the Bulk Receive page via Receive Selected.</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>1. Locate the top-left 'Back To Purchase Orders' link.
 2. Click it.</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. A 'Back To Purchase Orders' link is present top-left.
 2. Clicking it returns to the PO list.</t>
         </is>
       </c>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R1)</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Multiple POs across multiple vendors were sent to the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>1. Read the vendor group headers and counts.
 2. Use one vendor's Expand/Collapse all control.
 3. Confirm each vendor has its own control (not one global).</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr">
         <is>
           <t>1. POs are grouped by vendor with a count per vendor.
 2. Each vendor group has its own Expand/Collapse all control.
 3. POs within a group are collapsible.</t>
         </is>
       </c>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R2 / S8-R3)</t>
         </is>
       </c>
-      <c r="I89" s="2" t="inlineStr"/>
-      <c r="J89" s="2" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page is open with several POs.</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>1. Read a PO row's details.</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr">
         <is>
           <t>1. The row shows the PO number.
 2. It shows the related work order, or an inventory / no-WO indicator.
 3. It shows the parts count.</t>
         </is>
       </c>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R4)</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr"/>
-      <c r="J90" s="2" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page is open with POs and parts.</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>1. Confirm nothing is selected on load.
 2. Select a PO and confirm all its parts get selected.
@@ -4865,98 +4718,98 @@
 4. Confirm the receive action is locked when nothing is checked.</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. Nothing is selected by default.
 2. Selecting a PO selects all its parts; individual parts can be toggled.
 3. Actions are locked until at least one item is checked.</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R5)</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr"/>
-      <c r="J91" s="2" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO's parts are selected on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>1. Confirm the 'Receive parts (N)' button state with no invoice number.
 2. Enter a vendor invoice number.
 3. Confirm the button state again.</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr">
         <is>
           <t>1. The Receive button is disabled without a vendor invoice number.
 2. For a vendor-missing PO it also requires a vendor assigned and the missing part number entered.
 3. Once satisfied, the Receive button enables.</t>
         </is>
       </c>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R6)</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr"/>
-      <c r="J92" s="2" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>Verify Bulk Receive field editability: quantity editable (partial receive), cost editable ONLY when it is $0, sell locks after the WO is invoiced/paid</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has a part whose cost is $0, a part whose cost is not $0, and a PO whose work order IS invoiced/paid.</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>1. Edit the quantity on a part (partial receive).
 2. Try to edit the cost on the part whose cost is $0.
@@ -4964,7 +4817,7 @@
 4. On the invoiced/paid PO, try to edit the sell price and hover the locked field.</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr">
         <is>
           <t>1. Quantity is editable (partial receive supported).
 2. Cost is editable when it is $0 (pulled from the work order / PO when available).
@@ -4972,336 +4825,336 @@
 4. Sell price is editable until the work order is invoiced/paid, then locked with a lock icon and tooltip 'Locked — this part is already invoiced or paid'.</t>
         </is>
       </c>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>SV-7703, SV-7705 (S8-R7 / S10-R3)</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr"/>
-      <c r="J93" s="2" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has a Vendor Missing PO.</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>1. Assign a vendor to the Vendor Missing PO.
 2. Confirm it moves into that vendor's group.
 3. Enter the missing part number and confirm receiving becomes enabled.</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>1. Assigning a vendor moves the PO into that vendor's group.
 2. Entering the missing part number unflags it.
 3. Receiving is then enabled.</t>
         </is>
       </c>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R8)</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr"/>
-      <c r="J94" s="2" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>Verify Receive All receives everything selected at once and supports partial receive</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Multiple POs/parts are selected with valid invoice numbers on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>1. Reduce one part's received quantity below its ordered quantity.
 2. Click Receive All.
 3. Confirm the receipts.</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr">
         <is>
           <t>1. Everything selected is received at once.
 2. Partial receive (received qty below ordered) is supported.
 3. Remaining unreceived quantity stays waiting to receive.</t>
         </is>
       </c>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R10)</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr"/>
-      <c r="J95" s="2" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You received POs on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>1. After receiving, check that a Delivery record was created.
 2. Check that a Vendor Bill was created.
 3. Check that the vendor bill synced to QuickBooks.</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. A Delivery is created.
 2. A Vendor Bill is created.
 3. The vendor bill syncs to QuickBooks (same pipeline as single-PO receive).</t>
         </is>
       </c>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R11)</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr"/>
-      <c r="J96" s="2" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>Verify a pre-resolved core's decision is applied automatically at receive with no re-prompt, and core-only partial receive is supported</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO on the Bulk Receive page holds a cored part whose core was already decided (OK or Not OK) on the work order.</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>1. Receive only the cored line (core-only partial receive).
 2. Watch for any core prompt during the receive.
 3. Check the core's state on the work order lines and the customer invoice afterwards.</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr">
         <is>
           <t>1. Core-only partial receive is supported.
 2. The saved OK / Not OK decision is applied automatically at receive — the user is NOT asked again (no duplicate prompt).
 3. The received core shows its resolved state with no OK / Not OK buttons, and the customer invoice does not change at receive.</t>
         </is>
       </c>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>SV-7703, SV-8353 (S18 C-R5)</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr"/>
-      <c r="J97" s="2" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>Verify a part-sale-originated PO can be received on the Bulk Receive page like a work-order PO</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part-sale purchase order is waiting to receive and is on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>1. Find the part-sale PO under its vendor group on the Bulk Receive page.
 2. Select it, enter the vendor invoice number and receive it.
 3. Check the part sale afterwards.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr">
         <is>
           <t>1. The part-sale PO appears under its vendor group like a work-order PO.
 2. It can be received on this page via the same receive pipeline.
 3. The part sale progresses normally after receiving (no errors).</t>
         </is>
       </c>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8 AC (part-sale POs) + §8 Part Sales — confirmed)</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr"/>
-      <c r="J98" s="2" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Verify each vendor group has an invoice number field under the vendor name, available only when at least one PO of that vendor is selected (no Apply button)</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has a vendor group with multiple POs.</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>1. Look under the vendor name for the field to enter one invoice number.
 2. With no PO of that vendor selected, confirm the field is not available.
 3. Select at least one PO under that vendor and type an invoice number.</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr">
         <is>
           <t>1. A field to enter one invoice number for that vendor's POs sits under the vendor name.
 2. It is available only when at least one PO under that vendor is selected.
 3. There is no 'Apply' button — the number is remembered as typed.</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R1)</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr"/>
-      <c r="J99" s="2" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>Verify a typed invoice number fills only the selected POs of that vendor with no Apply click, still editable per PO</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor group has several POs; some are selected.</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>1. Select some POs under a vendor (leave others unselected).
 2. Type one invoice number in that vendor's invoice number field.
@@ -5309,203 +5162,203 @@
 4. Edit one PO's invoice number.</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>1. The typed number is filled into only the selected POs of that vendor — no Apply click needed (the number is remembered as typed).
 2. Unselected POs are not changed.
 3. Each PO's invoice number remains editable afterwards; then Receive all works for that vendor.</t>
         </is>
       </c>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R2)</t>
         </is>
       </c>
-      <c r="I100" s="2" t="inlineStr"/>
-      <c r="J100" s="2" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>Verify the vendor invoice number field is scoped per vendor, absent for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Bulk Receive page has multiple vendor groups plus a vendorless group.</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>1. Confirm each vendor group has its own invoice number field.
 2. Confirm the vendorless group shows no invoice number field.
 3. Type the same invoice number for POs of another vendor.</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr">
         <is>
           <t>1. The invoice number field is scoped to each vendor group — other vendors' POs and unselected POs are unaffected.
 2. The vendorless group shows no invoice-number field (assign a vendor first).
 3. The same invoice number can be reused (uniqueness relaxed).</t>
         </is>
       </c>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R3)</t>
         </is>
       </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part with no part number is on a PO or receive surface.</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>1. Locate the 'Missing part number' indicator on the part.
 2. Click Edit and enter a part number.
 3. Save and reload.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The part shows 'Missing part number' with an Edit action.
 2. Entering and saving a part number persists it immediately.
 3. A part number is mandatory to receive.</t>
         </is>
       </c>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10-R1)</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr"/>
-      <c r="J102" s="2" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="I99" s="2" t="inlineStr"/>
+      <c r="J99" s="2" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>Verify a NEW part number can be entered and saved so the part can be received</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part with a newly-entered part number (not matching any existing item) is ready to receive with a vendor assigned.</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>1. Enter a brand-new part number and save.
 2. Receive the part.
 3. Check inventory and Part History for the new item.</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. The new part number saves and stays on the part.
 2. Once the part has a part number (plus the required cost / sell price and a vendor invoice number), it can be received.
 3. The part-number entry does not have to create a new inventory or catalog item with stock for this to pass.</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10-R1 (PN mandatory to receive); S10-R2 struck (first-class part not required in v1))</t>
         </is>
       </c>
-      <c r="I103" s="2" t="inlineStr"/>
-      <c r="J103" s="2" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="I100" s="2" t="inlineStr"/>
+      <c r="J100" s="2" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>Verify an EXISTING part number can be entered so the part can be received, without overwriting the item's description or category</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. An inventory item with a known part number exists; a part on a PO can be given that number.</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>1. Enter the existing part number on the part and save.
 2. Receive the part.
 3. Check the linked item's stock, received cost, Part History, description and category.</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr">
         <is>
           <t>1. The existing part number saves on the part.
 2. The part can be received once it has the number (plus the required cost / sell price and a vendor invoice number).
@@ -5513,48 +5366,48 @@
 4. Linking the part into a first-class inventory item (updating its stock / cost / history) is not required for this to pass.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10-R1 (PN mandatory to receive); S10-R2 struck (linking to first-class item not required in v1))</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr"/>
-      <c r="J104" s="2" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="I101" s="2" t="inlineStr"/>
+      <c r="J101" s="2" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid WO and a part on an open WO are available.</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>1. On the open WO part, confirm qty/cost/sell are editable.
 2. On the invoiced/paid WO part, confirm sell is locked and cost is editable.</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. Open work order: quantity, cost and sell are editable.
 2. Invoiced/paid work order: sell is locked (lock icon + tooltip), only cost editable.
@@ -5562,49 +5415,49 @@
 4. Cost is editable when $0 or missing on either receive surface.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>SV-7703, SV-7705 (S10-R2 / S8-R7)</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr"/>
-      <c r="J105" s="2" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part without a part number is on a receive surface.</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>1. Attempt to receive the part with no part number.
 2. For a vendor-missing part, attempt to receive with no vendor.
 3. Attempt to receive with no cost / sell price entered.</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>1. A part cannot be received without a part number.
 2. A vendor-missing part cannot be received without a vendor.
@@ -5612,282 +5465,282 @@
 4. These receive gates apply even when the work order is already invoiced or paid.</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>SV-7705, SV-7708 (S10 Negative / S13-R6 / S13-R7)</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>Verify the inline part-number save persists and enables receiving</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A default part category exists and a vendor is assigned to the part.</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>1. Enter a part number inline and receive.
 2. Verify a CataloguePart and an inventory stock Part were created (not just a string on the request).
 3. Verify Part History exists.</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr">
         <is>
           <t>1. The part number entered inline is saved and persists (it is not lost).
 2. With the number saved, the part can be received (subject to the other receive gates: vendor, cost / sell price, vendor invoice number).
 3. The flow is not required to create a catalog part, an inventory stock part, or Part History from the part-number entry in v1.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (S10-R1 + S10 technical guardrails; S10-R2 struck (catalog/inventory creation not required in v1))</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO-originated PO exists.</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>1. Open /parts/orders and find the WO-originated PO.
 2. Confirm a Receive action on the PO row.
 3. Open the PO detail card and confirm a Receive action there too.</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr">
         <is>
           <t>1. The PO list row shows a Receive action.
 2. The PO detail card also shows a Receive action (the detail card previously hid it).</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R1)</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr"/>
-      <c r="J108" s="2" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="I105" s="2" t="inlineStr"/>
+      <c r="J105" s="2" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO-originated PO with an unreceived part exists.</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>1. Click Receive on the PO.
 2. Observe the destination surface.</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr">
         <is>
           <t>1. The shared Accept Delivery surface opens for that PO.</t>
         </is>
       </c>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R2)</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr"/>
-      <c r="J109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>1. An Office / read-only user credential (no Order Parts) exists.
 2. A fulfilled PO and an unfulfilled PO exist.</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as an Office / read-only user and open the PO list.
 2. Confirm the Receive action is hidden for them.
 3. As an authorized user, confirm the Receive action is hidden on a fulfilled PO.</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr">
         <is>
           <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or detail.
 2. Fulfilled POs do not show the Receive action.</t>
         </is>
       </c>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R3)</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr"/>
-      <c r="J110" s="2" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A multi-vendor delivery exists at /parts/deliveries.</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>1. Open Accept Delivery / Vendor Invoices at /parts/deliveries.
 2. Confirm grouping by vendor.
 3. Confirm each vendor group has its own invoice #, date, tax, note and Receive.</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr">
         <is>
           <t>1. The screen groups items by vendor.
 2. Each vendor group has its own invoice number, date, tax, note and Receive action.
 3. Multiple vendors on one PO are supported (existing behavior).</t>
         </is>
       </c>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12 (existing multi-vendor))</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr"/>
-      <c r="J111" s="2" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="I108" s="2" t="inlineStr"/>
+      <c r="J108" s="2" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Verify vendorless / no-part-number Work Order parts appear and can be received on the Receive (Accept Delivery) screen, and the Vendor Missing group sits per the agreed rule (top on Bulk Receive, bottom on the Receive screen)</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin (or a role with receiving access).
 2. A Work Order has a part with no vendor and no part number, plus a WO-created Purchase Order that is opened using the Receive button on the Work Order.</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>1. On the Work Order, click the Receive button to open the Receive (Accept Delivery) screen (headed Purchase Order Details).
 2. Confirm the vendorless / no-part-number parts are listed and can be received here.
@@ -5895,49 +5748,49 @@
 4. Open the Bulk Receive page (headed Receive Vendor Parts) for the same Purchase Orders and note where the Vendor Missing group sits there.</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. The vendorless / no-part-number Work Order parts appear in the Vendor Missing group and can be received once a vendor is chosen (Select Vendor) and a Part Number is entered.
 2. WO-created Purchase Orders opened with the Receive button appear on the Receive (Accept Delivery) screen and are receivable.
 3. The Vendor Missing group is positioned per the agreed rule (Milos, 2026-07-16): on the Bulk Receive page (Receive Vendor Parts) it leads at the TOP; on the Receive (Accept Delivery) screen it sits at the BOTTOM.</t>
         </is>
       </c>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R1 (+ Milos Round-3 2026-07-16))</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr"/>
-      <c r="J112" s="2" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr"/>
+      <c r="J109" s="2" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing / no-PN part is in an Accept Delivery group.</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>1. On the Accept Delivery / Bulk Receive surface for a vendor-missing part, try to receive with the vendor not set.
 2. Set the vendor but leave the part number empty and try to receive.
@@ -5945,7 +5798,7 @@
 4. Enter the vendor invoice number and all of the above, then receive.</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked until a vendor is set.
 2. Receiving is blocked until a part number is entered.
@@ -5953,963 +5806,1105 @@
 4. Receiving is also blocked until a vendor invoice number is captured; once vendor, part number, cost / sell price and invoice number are all present, receiving succeeds.</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>SV-7707, SV-7708 (S12-R2 / S13-R6 / S13-R7)</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr"/>
-      <c r="J113" s="2" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="I110" s="2" t="inlineStr"/>
+      <c r="J110" s="2" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Verify the multi-vendor '+N' indicator and the Vendor Missing group position on the receiving screens</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin (or a role with receiving access).
 2. A multi-vendor Purchase Order that also includes parts with no vendor (a Vendor Missing group) exists.</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>1. Open the Purchase Orders list (Parts &gt; Purchase Orders) and look at the vendor indicator on a multi-vendor Purchase Order.
 2. Open the Receive (Accept Delivery) screen from the Work Order Receive button and note where the Vendor Missing group sits.
 3. Open the Bulk Receive page (Receive Vendor Parts) and note where the Vendor Missing group sits.</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr">
         <is>
           <t>1. A multi-vendor Purchase Order shows a '+N' indicator (for example '+1' or '+4') on the Purchase Orders list summarizing the extra vendors. (On the Receive / Accept Delivery screen the vendor names are listed in full instead of a '+N' badge.)
 2. The Vendor Missing group is positioned per the agreed rule (Milos, 2026-07-16): on the Bulk Receive page (Receive Vendor Parts) it leads at the TOP; on the Receive (Accept Delivery) screen it sits at the BOTTOM.</t>
         </is>
       </c>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R3 (+ Milos Round-3 2026-07-16))</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr"/>
-      <c r="J114" s="2" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="I111" s="2" t="inlineStr"/>
+      <c r="J111" s="2" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A multi-vendor delivery is received.</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>1. Receive each vendor group with its own invoice number.
 2. Check QuickBooks / AP for the resulting bills.</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr">
         <is>
           <t>1. Each vendor group creates its own vendor bill.
 2. Each syncs to QuickBooks as a separate AP entry.</t>
         </is>
       </c>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R4)</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr"/>
-      <c r="J115" s="2" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="I112" s="2" t="inlineStr"/>
+      <c r="J112" s="2" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A delivery item with a known ordered quantity is on Accept Delivery.</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>1. Set the received quantity above the ordered quantity.
 2. Observe the warning.</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr">
         <is>
           <t>1. A 'received more than ordered' warning is shown (existing behavior).</t>
         </is>
       </c>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12 (existing) received-more-than-ordered)</t>
         </is>
       </c>
-      <c r="I116" s="2" t="inlineStr"/>
-      <c r="J116" s="2" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="I113" s="2" t="inlineStr"/>
+      <c r="J113" s="2" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. An Accept Delivery group has a line whose cost is $0 or missing (cost is pulled from the WO/PO when available).</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>1. Open Accept Delivery for the delivery.
 2. Locate a line with a $0 or missing cost and edit the cost.
 3. Confirm the quantity remains editable and the sell-price lock rule is unchanged.</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. Cost is editable on Accept Delivery when $0 or missing (matching Bulk Receive / Story 8 / Story 10).
 2. Quantity stays editable.
 3. The sell-price lock rule is unchanged (sell locks only after the work order is invoiced/paid).</t>
         </is>
       </c>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R5)</t>
         </is>
       </c>
-      <c r="I117" s="2" t="inlineStr"/>
-      <c r="J117" s="2" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="I114" s="2" t="inlineStr"/>
+      <c r="J114" s="2" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>Verify returning from receiving lands on the exact work order line the receive started from, not the top of the work order</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has several lines and a line far down the page has an un-received part.</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>1. From that line, click Receive (Receive opens Accept Delivery).
 2. Receive the part and go back to the work order.
 3. Observe where the page lands.</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr">
         <is>
           <t>1. The user is returned to the exact work order line they received from — the page scrolls/focuses to the originating line, not the top of the work order — giving instant visual confirmation of the received part.</t>
         </is>
       </c>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7706 (S11-R4 (+ S3-R5 amendment))</t>
         </is>
       </c>
-      <c r="I118" s="2" t="inlineStr"/>
-      <c r="J118" s="2" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="I115" s="2" t="inlineStr"/>
+      <c r="J115" s="2" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>Verify clicking Receive on a single work order part opens Accept Delivery showing all of that vendor's to-receive parts plus the vendorless group</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order part has a vendor that also has other parts waiting to receive, and a vendorless part is waiting to receive too.</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>1. Click Receive on the single work order part.
 2. Observe which parts the Accept Delivery screen shows.</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. Accept Delivery shows all to-receive parts for that part's vendor (other vendors' parts are not shown).
 2. The vendorless group is also shown alongside them.</t>
         </is>
       </c>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R6)</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr"/>
-      <c r="J119" s="2" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr"/>
+      <c r="J116" s="2" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless part can be assigned a vendor / merged into the single-part receive on the spot, reusing the same invoice number</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You are on the Accept Delivery screen opened from a single work order part, and the vendorless group is showing a part.</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>1. Assign a vendor to the vendorless part (or merge it into this receive).
 2. Receive both parts using the same invoice number.</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr">
         <is>
           <t>1. The vendorless part can be assigned a vendor / merged into this receive right there — no need to go back.
 2. The same invoice number is reused for the merged part.
 3. Both parts are received successfully.</t>
         </is>
       </c>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>SV-7707 (S12-R6)</t>
         </is>
       </c>
-      <c r="I120" s="2" t="inlineStr"/>
-      <c r="J120" s="2" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="I117" s="2" t="inlineStr"/>
+      <c r="J117" s="2" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing group is shown on the receive surface.</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>1. Open the vendor-missing group's vendor dropdown.
 2. Choose a vendor.
 3. Reload and confirm the assignment persists.</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr">
         <is>
           <t>1. The vendor dropdown assigns a vendor at PO level.
 2. The assignment is saved locally and to the backend.</t>
         </is>
       </c>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R1)</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr"/>
-      <c r="J121" s="2" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="I118" s="2" t="inlineStr"/>
+      <c r="J118" s="2" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO already has vendor X, and a vendor-missing group on the same PO is being assigned vendor X.</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>1. Assign the same vendor that is already on this PO.
 2. Observe the prompt.
 3. Try both 'Yes, Merge' and 'No, Keep Separate' in separate runs.</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. A prompt 'Add to {vendor}?' appears.
 2. 'Yes, Merge' combines into one group; 'No, Keep Separate' keeps two invoice numbers for the same vendor on one PO (valid).</t>
         </is>
       </c>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R2)</t>
         </is>
       </c>
-      <c r="I122" s="2" t="inlineStr"/>
-      <c r="J122" s="2" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="I119" s="2" t="inlineStr"/>
+      <c r="J119" s="2" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same WO exist; vendor Y is on the other PO.</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>1. Assign vendor Y to the vendor-missing group.
 2. Accept the merge prompt.
 3. Confirm items moved and the emptied source PO is removed.</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr">
         <is>
           <t>1. A prompt to merge the POs appears.
 2. Items move to the target PO; the emptied source PO is removed.
 3. The view redirects to the target PO.</t>
         </is>
       </c>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R3)</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr"/>
-      <c r="J123" s="2" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="I120" s="2" t="inlineStr"/>
+      <c r="J120" s="2" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing group is being assigned a brand-new vendor (no collision).</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>1. Assign a different vendor that is not already on any PO for this WO.
 2. Observe the QuickBooks flag.
 3. Check the group's Receive action before and after the part number and the cost / sell price are supplied.</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr">
         <is>
           <t>1. Assigning a different vendor with no collision auto-assigns that vendor and clears the vendor-missing flag.
 2. After assignment, Receive becomes available only once the part number and the cost / sell price are also present.</t>
         </is>
       </c>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R4 / S13-R5 / S13-R6 / S13-R7)</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr"/>
-      <c r="J124" s="2" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="I121" s="2" t="inlineStr"/>
+      <c r="J121" s="2" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two vendors share the same name but different IDs; an invoiced/paid WO with a vendor-missing PO exists.</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>1. Assign a vendor and confirm matching is by ID (same-name different-ID vendors are not treated as the same).
 2. Attempt a merge across different work orders.
 3. Attempt to receive on the invoiced/paid WO.</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr">
         <is>
           <t>1. Vendors are matched by ID, not name.
 2. Merge only applies within the same work order.
 3. Receiving is blocked when the WO is invoiced/paid.</t>
         </is>
       </c>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13 Technical guardrails)</t>
         </is>
       </c>
-      <c r="I125" s="2" t="inlineStr"/>
-      <c r="J125" s="2" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="I122" s="2" t="inlineStr"/>
+      <c r="J122" s="2" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. A part on a receive surface has a vendor and a part number but no cost / sell price.</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the part.
 2. Leave the cost / sell price empty and check the Receive action.
 3. Enter a cost / sell price and check the Receive action again.</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr">
         <is>
           <t>1. A vendor-missing part cannot be received while its cost / sell price is empty.
 2. Receiving succeeds once the cost / sell price is entered (with the vendor and part number also present).</t>
         </is>
       </c>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R7)</t>
         </is>
       </c>
-      <c r="I126" s="2" t="inlineStr"/>
-      <c r="J126" s="2" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="I123" s="2" t="inlineStr"/>
+      <c r="J123" s="2" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>Verify an assigned vendor stays changeable via the same dropdown until the part is received or the work order is invoiced/paid</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO part has a vendor assigned but is not yet received; another part is already received (or its work order is invoiced/paid).</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>1. On the un-received part, open the vendor dropdown and pick a different vendor.
 2. On the received (or invoiced/paid) part, try to change the vendor.</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr">
         <is>
           <t>1. The vendor is NOT locked on selection — it can be changed via the same dropdown, so a wrong pick can be corrected before receiving.
 2. Once the part is received or the work order is invoiced/paid, the vendor can no longer be changed.</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R8 (SV-8343))</t>
         </is>
       </c>
-      <c r="I127" s="2" t="inlineStr"/>
-      <c r="J127" s="2" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="I124" s="2" t="inlineStr"/>
+      <c r="J124" s="2" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>Verify the part number stays editable via the edit icon after entry until the part is received or the work order is invoiced/paid</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A PO part has a part number entered but is not yet received; another part is already received (or its work order is invoiced/paid).</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>1. On the un-received part, use the edit icon to change the part number.
 2. On the received (or invoiced/paid) part, try to edit the part number.</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>1. The part number remains editable (edit icon) after entry, under the same condition as the vendor — until the part is received or the work order is invoiced/paid.
 2. Once the part is received or the work order is invoiced/paid, the part number can no longer be edited.</t>
         </is>
       </c>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>SV-7708 (S13-R8 (SV-8343))</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr"/>
-      <c r="J128" s="2" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr"/>
+      <c r="J125" s="2" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Work Orders list is open with WOs that have unreceived parts.</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work Orders list column selector.
 2. Enable 'Waiting on Parts'.
 3. Read the column values across statuses.</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. The Work Orders list column selector offers a 'Waiting on Parts' column (off by default).
 2. When enabled, it shows the count of unreceived parts per work order across all statuses.</t>
         </is>
       </c>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R1)</t>
         </is>
       </c>
-      <c r="I129" s="2" t="inlineStr"/>
-      <c r="J129" s="2" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="I126" s="2" t="inlineStr"/>
+      <c r="J126" s="2" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Waiting on Parts column is enabled and a WO shows a count.</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>1. Click the count on a work order row.
 2. Observe the destination.</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>1. Clicking the count opens the receiving surface for the work order's first unreceived purchase order. In the current build this is the consolidated Bulk Receive page (/bulk-receive), which supersedes the legacy Accept Delivery screen for work-order POs.
 2. Receiving from there behaves as it does on the Bulk Receive page.</t>
         </is>
       </c>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R2)</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr"/>
-      <c r="J130" s="2" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="I127" s="2" t="inlineStr"/>
+      <c r="J127" s="2" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A WO with nothing to receive (or POs off) is in the list with the column enabled.</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>1. Find a WO with nothing waiting to receive.
 2. Read its Waiting on Parts cell.</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr">
         <is>
           <t>1. A work order with nothing to receive shows an em dash ('—') in the Waiting on Parts column, with no clickable link.</t>
         </is>
       </c>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (S14-R3)</t>
         </is>
       </c>
-      <c r="I131" s="2" t="inlineStr"/>
-      <c r="J131" s="2" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="I128" s="2" t="inlineStr"/>
+      <c r="J128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>Verify part-sale orders behave with the Waiting on Parts column — unreceived count and receive shortcut work without errors</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Waiting on Parts column is enabled and a Part Sale has an unreceived vendor part.</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>1. Locate the part-sale order on the list where the Waiting on Parts column shows.
 2. Check its unreceived-parts count and click it.
 3. Receive via the shortcut and re-check the count.</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr">
         <is>
           <t>1. The part-sale order's unreceived parts are counted consistently in the Waiting on Parts column (or the order is cleanly excluded — no error, no broken link).
 2. The receive shortcut behaves like it does for work orders.
 3. After receiving, the count updates correctly.</t>
         </is>
       </c>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>SV-7709 (§8 Part Sales — confirmed (remaining check))</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr"/>
-      <c r="J132" s="2" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="I129" s="2" t="inlineStr"/>
+      <c r="J129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Require Review Before Completion is ON and saved.</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>1. Open a work order with approved lines.
 2. Start completion.
 3. Observe that the review flow is used.</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review ON, completing routes into the review flow rather than completing directly.
 2. When the last open line is resolved (by any path) while Require Review is on, the work order routes to Ready for Review — it never auto-completes.</t>
         </is>
       </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (R1 + S16-R12)</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr"/>
+      <c r="J130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Verify the completion action reads 'Send To Review' when Require Review is on</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review is ON.
+3. A work order with approved lines is ready to complete.</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>1. Open a work order that is ready to complete, with Require Review Before Completion turned on.
+2. Read the primary action button on the work order (and, for a work order that still has parts to receive, the heading of the dialog that opens).</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>1. With Require Review Before Completion ON, a ready work order's primary action button reads 'Send To Review' (it replaces 'Complete Work Order').
+2. For a work order that still has parts waiting to receive, clicking 'Send To Review' opens a dialog headed 'Complete &amp; Send to Review' that shows how many parts are waiting to receive and offers 'Receive Parts' and 'Send To Review'.</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (R2)</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr"/>
+      <c r="J131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review is ON.
+3. A work order missing mileage/hours/VIN is ready to complete.</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>1. Start completion and reach the Details step.
+2. Note which vehicle fields are collected.</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>1. When Require Review is on, the completion Details step collects Mileage and Engine Hours only.
+2. There is no VIN field in the completion modal; VIN is captured later by the reviewer in the Mark Reviewed dialog.</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>SV-7870 (R3)</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr"/>
+      <c r="J132" s="2" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Review ON (Story 16)</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. Require Review is ON with a part-bearing work order.</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>1. Start completion and click Receive Parts.
+2. Observe the destination.</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive Parts opens the shared receive page (not an inline modal).</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>SV-7870 (R1 + S16-R12)</t>
+          <t>SV-7870 (R4)</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -6918,7 +6913,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Verify the completion action reads 'Send To Review' when Require Review is on</t>
+          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6933,165 +6928,23 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. Require Review is ON.
-3. A work order with approved lines is ready to complete.</t>
+2. Require Review is ON and a work order with approved lines is ready to send to review (for a work order with parts still to receive, the 'Complete &amp; Send to Review' dialog is open).</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>1. Open a work order that is ready to complete, with Require Review Before Completion turned on.
-2. Read the primary action button on the work order (and, for a work order that still has parts to receive, the heading of the dialog that opens).</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>1. With Require Review Before Completion ON, a ready work order's primary action button reads 'Send To Review' (it replaces 'Complete Work Order').
-2. For a work order that still has parts waiting to receive, clicking 'Send To Review' opens a dialog headed 'Complete &amp; Send to Review' that shows how many parts are waiting to receive and offers 'Receive Parts' and 'Send To Review'.</t>
-        </is>
-      </c>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>SV-7870 (R2)</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr"/>
-      <c r="J134" s="2" t="inlineStr"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. Require Review is ON.
-3. A work order missing mileage/hours/VIN is ready to complete.</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>1. Start completion and reach the Details step.
-2. Note which vehicle fields are collected.</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>1. When Require Review is on, the completion Details step collects Mileage and Engine Hours only.
-2. There is no VIN field in the completion modal; VIN is captured later by the reviewer in the Mark Reviewed dialog.</t>
-        </is>
-      </c>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>SV-7870 (R3)</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr"/>
-      <c r="J135" s="2" t="inlineStr"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. Require Review is ON with a part-bearing work order.</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>1. Start completion and click Receive Parts.
-2. Observe the destination.</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>1. Receive Parts opens the shared receive page (not an inline modal).</t>
-        </is>
-      </c>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>SV-7870 (R4)</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr"/>
-      <c r="J136" s="2" t="inlineStr"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. Require Review is ON and a work order with approved lines is ready to send to review (for a work order with parts still to receive, the 'Complete &amp; Send to Review' dialog is open).</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Click Send To Review (the primary action button, or the 'Send To Review' button in the 'Complete &amp; Send to Review' dialog for a part-bearing work order).
 2. Observe the work order status and banner.
 3. Check the lines state and inventory pick state.</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr">
         <is>
           <t>1. The work order status becomes Review (amber).
 2. A 'Ready for Review' / 'Sent for review' indication is shown.
@@ -7099,956 +6952,956 @@
 4. The same Review / Ready-for-Review end state is reached when the last open line auto-resolves under Require Review on, not only when Send To Review is clicked explicitly.</t>
         </is>
       </c>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R5 / R6 + S16-R12)</t>
         </is>
       </c>
-      <c r="I137" s="2" t="inlineStr"/>
-      <c r="J137" s="2" t="inlineStr"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="I134" s="2" t="inlineStr"/>
+      <c r="J134" s="2" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Review state.</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>1. Click Mark Reviewed.
 2. Observe the VIN field.
 3. Clear the VIN and check the Confirm Review button, then enter a VIN.</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr">
         <is>
           <t>1. The Mark Reviewed dialog shows a VIN / Serial # field, required if the work order is missing a valid VIN.
 2. Confirm Review is disabled until a VIN is present.
 3. Once a VIN is entered, Confirm Review is enabled.</t>
         </is>
       </c>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 / R10)</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr"/>
-      <c r="J138" s="2" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="I135" s="2" t="inlineStr"/>
+      <c r="J135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order with an inventory line just went to Review.</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order in Review state.
 2. Check the line states.
 3. Check whether inventory was auto-picked.</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr">
         <is>
           <t>1. Lines are locked to Complete.
 2. Inventory has been auto-picked.</t>
         </is>
       </c>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R6)</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr"/>
-      <c r="J139" s="2" t="inlineStr"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="I136" s="2" t="inlineStr"/>
+      <c r="J136" s="2" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Review with the Mark Reviewed dialog filled (VIN present).</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>1. Click Confirm Review.
 2. Observe the resulting work order state.
 3. Look for a separate final 'Complete Work Order' action.</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr">
         <is>
           <t>1. After Confirm Review the sign-off completes and the work order moves directly Review -&gt; Complete.
 2. There is no distinct 'Reviewed' holding state and no separate final 'Complete Work Order' click.
 3. Note: with Require Review on, resolving the last open line first routes the work order to Ready for Review; sign-off (Confirm Review) then moves it to Complete.</t>
         </is>
       </c>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R5 / R8 (direct sign-off, no separate Complete) + S16-R12)</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="I137" s="2" t="inlineStr"/>
+      <c r="J137" s="2" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>1. A role with Review Work Orders and a role without it both exist.
 2. A work order is in Review state, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as a role without Review Work Orders and open the work order in Review.
 2. Confirm Mark Reviewed is disabled with 'Awaiting review'.
 3. Sign in as a role with Review Work Orders (system defaults grant it broadly; it can be limited to manager/foreman via custom roles) and confirm Mark Reviewed is available.</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr">
         <is>
           <t>1. A role without the Review Work Orders permission sees Mark Reviewed disabled with an 'Awaiting review' indicator.
 2. A role with the Review Work Orders permission can Mark Reviewed and sign off.
 3. A user who holds the Review Work Orders permission may Mark Reviewed a work order they completed themselves — self-review is allowed in v1 with NO reviewer != completer identity restriction (the gate is purely the permission).</t>
         </is>
       </c>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 (role-gating))</t>
         </is>
       </c>
-      <c r="I141" s="2" t="inlineStr"/>
-      <c r="J141" s="2" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="I138" s="2" t="inlineStr"/>
+      <c r="J138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open.</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>1. Open the Mark Reviewed dialog.
 2. Confirm a required VIN / Serial # field (Confirm disabled until VIN entered).
 3. Confirm there is no review note field, then complete the sign-off.</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr">
         <is>
           <t>1. The Mark Reviewed dialog shows a VIN / Serial # field that is required (Confirm Reviewed is disabled until VIN is entered).
 2. There is no review note field on the dialog.
 3. The sign-off completes using the VIN / Serial # only.</t>
         </is>
       </c>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 (VIN required, no note))</t>
         </is>
       </c>
-      <c r="I142" s="2" t="inlineStr"/>
-      <c r="J142" s="2" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="I139" s="2" t="inlineStr"/>
+      <c r="J139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Reviewed state (or a Review state before sign-off for the invoicing-block check).</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>1. Before sign-off, attempt to invoice the work order.
 2. Complete the review sign-off (Confirm Review).
 3. Confirm the work order becomes Complete (invoice-ready).</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>1. Invoicing is blocked until the work order is reviewed.
 2. After sign-off the work order moves directly Review -&gt; Complete (invoice-ready), with no separate final Complete Work Order click.
 3. With Require Review on the work order never auto-completes on last-line-resolve; it routes to Ready for Review and invoicing stays blocked until it is reviewed.</t>
         </is>
       </c>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R8 + S16-R12)</t>
         </is>
       </c>
-      <c r="I143" s="2" t="inlineStr"/>
-      <c r="J143" s="2" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr"/>
+      <c r="J140" s="2" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. At least one work order is in Review state.</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>1. Open the Work Orders list.
 2. Look for a 'Ready for Review' filter or column.
 3. Confirm work orders in Review appear in it.</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. A 'Ready for Review' filter/column lists work orders awaiting review.</t>
         </is>
       </c>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R9)</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr"/>
-      <c r="J144" s="2" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="I141" s="2" t="inlineStr"/>
+      <c r="J141" s="2" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>Verify all lines must be approved before Send To Review (the 'Send To Review' action is disabled until every line is approved)</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order has one unapproved line.</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and locate the 'Send To Review' action while a line is still unapproved.
 2. Attempt to use Send To Review with the unapproved line.</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. The 'Send To Review' action cannot be used while any line is unapproved - the 'Send To Review' button is disabled until every line has been approved.</t>
         </is>
       </c>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R11)</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr"/>
-      <c r="J145" s="2" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="I142" s="2" t="inlineStr"/>
+      <c r="J142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>Verify cores are decided before receiving ahead of Send to Review, and invoicing stays blocked until Reviewed and every core is decided</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review is ON and a work order has inventory and special-order cores.</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>1. Resolve inventory cores in the completion modal (after Pick) before Send to Review.
 2. Decide the special-order cores OK / Not OK on the resolve screen BEFORE receiving, before Send to Review (same in required- and optional-invoice flows).
 3. Attempt to invoice before the work order is Reviewed and before every core is decided.</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr">
         <is>
           <t>1. Inventory cores are resolved before Send to Review.
 2. Special-order cores are pre-resolved before receiving on the resolve screen before Send to Review — no longer deferred to the Create Invoice gate.
 3. Invoicing is blocked until the work order is Reviewed AND every core is decided; only an undecided core blocks — a decided (un-received) core does not.</t>
         </is>
       </c>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>SV-7870, SV-8353 (S18 / Story 16 core paragraph)</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr"/>
-      <c r="J146" s="2" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="I143" s="2" t="inlineStr"/>
+      <c r="J143" s="2" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>Verify Require Review Before Completion starts ON for a brand-new organization, and existing organizations keep today's behavior</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>Review ON (Story 16)</t>
         </is>
       </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>1. A brand-new organization / account (no settings changed yet) and an existing organization are available.
 2. Signed in as Admin for each.</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>1. On a brand-new organization, open Settings &gt; Work Orders and check the Require Review Before Completion setting.
 2. On an existing organization, confirm its completion behavior is unchanged (the setting is backfilled).</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. On a brand-new organization / account, Require Review Before Completion defaults to ON (Milos decision, 2026-07-16: it stays ON for every new organization).
 2. Existing organizations keep their current completion behavior (the setting is backfilled so their behavior does not change).</t>
         </is>
       </c>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R Open (default) - Milos Round-3 2026-07-16: ON for new orgs)</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr"/>
-      <c r="J147" s="2" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="I144" s="2" t="inlineStr"/>
+      <c r="J144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. You are on the Create Work Order form (/workorders → Create).</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>1. Open the Create Work Order form.
 2. Read the primary button label.</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr">
         <is>
           <t>1. The primary button reads 'Create Work Order'.</t>
         </is>
       </c>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R1)</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr"/>
-      <c r="J148" s="2" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="I145" s="2" t="inlineStr"/>
+      <c r="J145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order requiring mileage/VIN is being completed.</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Observe where required fields are collected.
 3. Confirm the tech story is handled by its own flow, not inside this modal.</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. The required vehicle fields (Mileage and Engine Hours) are collected in a centralized center modal titled 'Complete Work Order'.
 2. The tech story is NOT part of this modal (it is handled by its own line-level flow).</t>
         </is>
       </c>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R2)</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr"/>
-      <c r="J149" s="2" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="I146" s="2" t="inlineStr"/>
+      <c r="J146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has just been completed.</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>1. Read the success screen.
 2. Confirm WO number, total, Done and Go to Invoice.
 3. Confirm the invoice number is shown on the Finance step, not the success screen.</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr">
         <is>
           <t>1. The success screen shows the WO number and total with Done and Go to Invoice.
 2. The invoice number appears on the Finance step, not on the success screen.</t>
         </is>
       </c>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R3)</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr"/>
-      <c r="J150" s="2" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="I147" s="2" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>UX Refinements (Story 15)</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completion modal is open.</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>1. Trigger the close-confirmation modal.
 2. Click Close (prominent/red) and observe.
 3. Trigger it again and click Cancel (text link, far left) and observe.</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. Close (prominent/red button) closes the confirmation modal only, discards nothing (no discard warning), and stays on the work order.
 2. Cancel (text link, far left) closes the modal and returns to the previous screen.
 3. Other consumers of the shared confirmation dialog keep their existing action labels.</t>
         </is>
       </c>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>SV-7710 (S15-R4)</t>
         </is>
       </c>
-      <c r="I151" s="2" t="inlineStr"/>
-      <c r="J151" s="2" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="I148" s="2" t="inlineStr"/>
+      <c r="J148" s="2" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>1. A role with the App Settings permission (e.g. Admin) and a role without it (e.g. Service Advisor or Technician) both exist.
 2. You can sign in as each.</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as a role with App Settings and open and modify /administration/settings → Work Orders.
 2. Sign in as a role without App Settings and attempt to open and modify the same page.
 3. As the role without App Settings, attempt to save a Work Order settings change directly (API), and note the response.</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can view and modify the Work Order settings page.
 2. A role without App Settings cannot open or change the Work Order settings.
 3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
         </is>
       </c>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>SV-7696 (S1 AC / §8 Permissions)</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr"/>
-      <c r="J152" s="2" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="I149" s="2" t="inlineStr"/>
+      <c r="J149" s="2" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for several roles exist.
 2. A work order ready to complete exists.</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to complete a work order.
 2. Record which roles can and cannot.</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. Roles with Work Orders: Create &amp; Edit plus WO Lines: Create &amp; Edit and Full View (needed to approve all lines) can complete a work order: Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
 2. Technician and Parts Tech cannot complete (Technician cannot approve lines in Tech View and/or lacks Work Orders: Create &amp; Edit; Parts Tech is a receiver, not a completer).
 3. Office, Sales Rep and Time Clock cannot complete a work order.</t>
         </is>
       </c>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>§8 Permissions</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr"/>
-      <c r="J153" s="2" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="I150" s="2" t="inlineStr"/>
+      <c r="J150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for several roles exist.
 2. The Bulk Receive flow is available (Story 7/8 built).</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to reach and use Bulk Receive.
 2. Record the outcomes.</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
 2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot receive.
 3. Sales Rep and Time Clock cannot reach Bulk Receive.</t>
         </is>
       </c>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>§8 Permissions</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr"/>
+      <c r="J151" s="2" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for roles with and without Review Work Orders exist.
 2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>1. For each role, attempt to Mark Reviewed.
 2. Record which roles can and cannot.</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. Mark Reviewed (review sign-off) requires the Review Work Orders permission; system defaults grant it broadly, and it can be narrowed to manager/foreman via custom roles.
 2. A role without Review Work Orders sees Mark Reviewed disabled with an 'Awaiting review' indicator.
 3. A user who holds the Review Work Orders / Mark Reviewed permission may Mark Reviewed a work order they completed themselves — self-review is allowed in v1. There is NO reviewer != completer identity restriction; the gate is purely the permission.</t>
         </is>
       </c>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 / §8 role-gating review)</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr"/>
-      <c r="J155" s="2" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="I152" s="2" t="inlineStr"/>
+      <c r="J152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>1. An Office / read-only credential (no Order Parts) exists.
 2. A WO-originated PO exists, plus a fulfilled PO.</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as an Office / read-only user.
 2. Open the PO list and detail.
 3. Confirm the Receive action is not shown, and confirm it is also absent on a fulfilled PO.</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. The Receive action requires the Order Parts permission; Office and read-only users (no Order Parts) do not see Receive on the PO list or PO detail.
 2. Receive is also hidden for fulfilled (already-received) POs.</t>
         </is>
       </c>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>SV-7706 (S11-R3)</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr"/>
-      <c r="J156" s="2" t="inlineStr"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="I153" s="2" t="inlineStr"/>
+      <c r="J153" s="2" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>API — Permissions</t>
         </is>
       </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>1. Signed in with API access.
 2. A relevant Simple-Flow setting (e.g. Require Vendor Invoice Number) is ON.</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>1. As a role that lacks the mapped permission, confirm the gated setting or action is hidden or unavailable in the app.
 2. As that same role, try the same setting change directly through the API (bypassing the app) and note the response.
@@ -8056,7 +7909,7 @@
 4. As a role that only has Work Orders: Create &amp; Edit, try to receive parts onto a work order through the API and note the response.</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. In the app, a role without the mapped permission does not see or cannot use the gated setting or action (this is the v1 pass criterion).
 2. The Work Order settings save is also blocked at the backend: the unauthorized API request is rejected with HTTP 403.
@@ -8064,185 +7917,185 @@
 4. Because several work-order permissions share the same backend check, any role with Work Orders: Create &amp; Edit can receive parts onto a work order through the API.</t>
         </is>
       </c>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>§8 BE enforcement</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr"/>
-      <c r="J157" s="2" t="inlineStr"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="I154" s="2" t="inlineStr"/>
+      <c r="J154" s="2" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for roles with and without Review Work Orders exist.
 2. A work order in Review state exists, sent to review by a known user.</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>1. Confirm that only roles holding Review Work Orders can sign off, and roles without it cannot.</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. Review sign-off is governed by the Review Work Orders custom-role permission (it is NOT open to all users for v1).
 2. The permission gates the Mark Reviewed action (a role without Review Work Orders cannot sign off; a role with it can).
 3. A user who holds the Review Work Orders permission may sign off a work order they completed themselves — self-review is allowed in v1 with NO reviewer != completer identity restriction (the gate is purely the permission).</t>
         </is>
       </c>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>§8 role-gating review</t>
         </is>
       </c>
-      <c r="I158" s="2" t="inlineStr"/>
-      <c r="J158" s="2" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="I155" s="2" t="inlineStr"/>
+      <c r="J155" s="2" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>1. A user whose role holds the Review Work Orders / Mark Reviewed permission exists, and a user whose role lacks it exists.
 2. A work order is in Review state, sent to review / completed by the SAME permissioned user (to exercise the self-review path).</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>1. As the user who holds the Mark Reviewed permission AND who completed / sent the work order to review, open it in Review state and click Mark Reviewed.
 2. Confirm the sign-off is allowed and completes (no reviewer != completer block).
 3. As a user whose role does NOT hold the Mark Reviewed permission, open a work order in Review and check the Mark Reviewed control.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr">
         <is>
           <t>1. A user who holds the Review Work Orders / Mark Reviewed permission CAN Mark Reviewed a work order they completed themselves — self-review is allowed in v1 (there is NO reviewer != completer identity restriction).
 2. A user whose role does NOT hold the Mark Reviewed permission cannot sign off — the Mark Reviewed control is disabled with an 'Awaiting review' indicator.
 3. The only gate on Mark Reviewed is the Review Work Orders permission; who completed the work order is irrelevant.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7 (review sign-off) — self-review permission-gated (identity rule NOT in v1))</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I156" s="2" t="inlineStr"/>
+      <c r="J156" s="2" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>1. A Technician credential exists (WO Lines: Create &amp; Edit, no See Financial Data).
 2. An open work order with a line is available.</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>1. Sign in as the Technician and open the work order line.
 2. Attempt to add a vendorless / no-part-number part (description + quantity + sell price).</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr">
         <is>
           <t>1. The Technician cannot add a vendorless / no-part-number part.
 2. The mandatory sell price cannot be entered without See Financial Data, so the add is prevented.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>SV-7700 (S5 / §9 (See Financial Data gate))</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I157" s="2" t="inlineStr"/>
+      <c r="J157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>Permissions</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>1. Credentials for each system role exist (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Technician, Parts Manager, Parts Tech, Office, Sales Rep, Time Clock).
 2. A work order ready to complete is available.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>1. For each role, open the work order and check whether the Complete Work Order action is available and usable.
 2. Record the result per role against the checklist below.
@@ -8250,89 +8103,89 @@
 4. Roles expected NOT to be able to complete: Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr">
         <is>
           <t>1. Complete Work Order is available for Admin, Service Manager, Senior SA, Service Advisor, Foreman and Parts Manager.
 2. Complete Work Order is NOT available for Technician, Parts Tech, Office, Sales Rep or Time Clock.
 3. Technician and Parts Tech are blocked because they cannot approve lines and/or lack Work Orders: Create &amp; Edit; Office is view-only; Sales Rep and Time Clock have no work-order edit access.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>§9 per-role completion matrix</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I158" s="2" t="inlineStr"/>
+      <c r="J158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage is ON and the work order has no mileage.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave mileage empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until mileage is entered.</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>SV-7697, SV-7698, SV-7699 (S2-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. VIN is required for this org's completion and the work order has no VIN.
@@ -8340,196 +8193,196 @@
 4. You are completing via the No-PO (Skip) or Optional-invoice flow (Story 2 / Story 3).</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>1. Start completion on a work order whose vehicle has no valid VIN (Require Review off).
 2. Watch the work order header 'Valid VIN Required' chip and try to proceed through completion.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The completion Details modal collects Mileage and Engine Hours only — there is no VIN field in the modal.
 2. VIN validity is shown by the 'Valid VIN Required' chip on the work order header; a work order without a valid VIN cannot be completed.
 3. For a review-on work order the VIN is captured later by the reviewer in the Mark Reviewed dialog, not at completion.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699, SV-7710 (S15-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Engine Hours is ON and the work order has no engine hours.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave engine hours empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until engine hours are entered.</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open on a line.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Leave the story textarea empty.
 2. Check the Next/Continue button.
 3. Type any text and check again.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. With the textarea empty, Next/Continue is disabled.
 2. After typing text, Next/Continue becomes enabled.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R4)</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is ON and a part is being received.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. On the receive surface, leave the vendor invoice number empty.
 2. Attempt to receive.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor invoice number.
 2. Once an invoice number is entered, receiving is allowed.</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R5 / §4)</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing part is on a receive surface.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. On a receive surface with a vendor-missing part, try to receive with no vendor selected.
 2. Select a vendor but leave the part number empty and try to receive.
@@ -8537,7 +8390,7 @@
 4. Provide vendor, part number and cost / sell price, then receive.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked while no vendor is selected.
 2. Receiving is blocked while the part number is empty.
@@ -8545,395 +8398,536 @@
 4. Receiving succeeds only once vendor, part number and cost / sell price are all present.</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>SV-7705, SV-7707, SV-7708 (S10 / S12-R2 / S13-R6 / S13-R7)</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open on a WO with no VIN on the asset.</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. Clear the VIN field.
 2. Check the Confirm Review button.
 3. Enter a VIN and check again.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Review is disabled while VIN is empty.
 2. Confirm Review enables after a VIN is entered.</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7)</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part-bearing work order had completion started and cancelled once.</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. Cancel the first completion attempt.
 2. Start and complete again.
 3. Inspect the POs.</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. No duplicate POs are created on the second attempt.</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>SV-7698 (S3-R9 (idempotency))</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid work order is on a receive surface.</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the invoiced/paid WO part.
 2. Try to edit the sell field.
 3. Hover the lock icon.</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>1. The sell field is locked (not editable).
 2. A lock icon and tooltip 'Locked — this part is already invoiced or paid' are shown.
 3. Only cost remains editable.</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R7 / §4 field locking)</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same vendor are being received.</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. Enter the same invoice number on both POs.
 2. Receive both.</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>1. The reused invoice number is accepted (uniqueness is relaxed).
 2. Both POs receive successfully.</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R3 / §4 (uniqueness relaxed))</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Verify an unapproved line disables the Complete Work Order button with a tooltip (regardless of the Require Vendor Invoice Number setting)</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Auto-approve Lines is OFF so a newly added line lands in Needs Approval.
 3. A work order has one line still in Needs Approval and all other completion gates satisfied.</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. With Require Vendor Invoice Number ON, open a work order that has one line still in Needs Approval; look at the Complete Work Order button, then hover it.
 2. Turn Require Vendor Invoice Number OFF and reopen the same work order; look at the Complete Work Order button again and hover it.
 3. Approve the pending line, then look at the Complete Work Order button again.</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>1. With Require Vendor Invoice Number ON, the Complete Work Order button is disabled; hovering it shows the tooltip 'Every line must be approved or declined in order to complete the work order.' (the tooltip is generic and does not name the specific line).
 2. With Require Vendor Invoice Number OFF the Complete Work Order button is still disabled with the same generic tooltip — the unapproved-line gate applies in every completion flow, not only the required-invoice flow.
 3. Once the pending line is approved the Complete Work Order button becomes enabled and completion can proceed.</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S4-R8 / S3-R9 / Key Decision (line approval))</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has an in-stock inventory part; its on-hand quantity is noted.</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order via the simple (skip) path.
 2. Check the part's on-hand quantity and Part History.</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>1. The in-stock part's on-hand quantity decrements.
 2. A Part History entry is written.
 3. The skip path's status setter does not bypass inventory movement / Part History / catalog / delivery.</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 1</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create Purchase Orders is OFF.
 3. A work order with a vendor/found part exists.</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order with Create POs OFF.
 2. Check for any PO, vendor bill, AP sync.
 3. Check for any catalog/inventory sync of the vendor/found part.</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>1. No purchase order, vendor bill or accounts-payable sync is produced.
 2. No catalog or inventory sync happens (the part is received at request time only).</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>§5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create POs is on and a work order has a receivable vendor part.</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. Receive the part via Accept Delivery.
 2. Check that a Delivery, then a Vendor Bill, then a QuickBooks sync occur.
 3. Repeat via the Bulk Receive surface (once built) and confirm it also syncs.</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>1. Receiving creates a Delivery, then a Vendor Bill, then syncs to QuickBooks.
 2. Both receive surfaces sync the vendor bill (only complete-simple bypasses this).</t>
         </is>
       </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>§5 invariant 2</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A vendorless / no-PN part exists on a work order.</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>1. Before adding a vendor/PN, check inventory and Part History for the part.
+2. Add a vendor and PN, then re-check.</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>1. Before a vendor/PN, there is zero inventory interaction (no item, no history).
+2. After a vendor and PN are added, normal inventory handling applies.</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>§5 (vendorless/no-PN)</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A Vendor Missing PO exists.</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>1. Check QuickBooks sync for the Vendor Missing PO.
+2. Provide a vendor and part number and re-check.</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>1. While vendor/PN are missing, the PO is excluded from QuickBooks.
+2. Once both are provided, it becomes eligible for QuickBooks.</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>SV-7701 (§5 / S6-R3)</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>1. Signed in as Admin.
+2. A work order has a part with no cost recorded at completion.</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>1. Complete the work order.
+2. Check the resulting cost/margin figures that flow to QuickBooks.</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.
+2. For vendorless / no-part-number parts the mandatory sell price is captured at add time behind the See Financial Data gate, so a completing user has a sell figure and $0-cost margins are avoided.</t>
+        </is>
+      </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>§5 invariant 2</t>
+          <t>§8 (cost at completion)</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr"/>
@@ -8942,7 +8936,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -8963,24 +8957,24 @@
       <c r="E176" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. A vendorless / no-PN part exists on a work order.</t>
+2. A completed work order is ready to invoice.</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>1. Before adding a vendor/PN, check inventory and Part History for the part.
-2. Add a vendor and PN, then re-check.</t>
+          <t>1. Create the invoice.
+2. Check for the Journal Entry / Inventory sync to QuickBooks.</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>1. Before a vendor/PN, there is zero inventory interaction (no item, no history).
-2. After a vendor and PN are added, normal inventory handling applies.</t>
+          <t>1. The Journal Entry / Inventory sync to QuickBooks fires on invoice creation.
+2. This sync is not dependent on a PO existing.</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>§5 (vendorless/no-PN)</t>
+          <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
@@ -8989,7 +8983,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify Part History is preserved for a part that is genuinely inventory-tracked</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -9010,24 +9004,24 @@
       <c r="E177" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. A Vendor Missing PO exists.</t>
+2. A genuinely inventory-tracked part exists (an inventory item with stock).</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>1. Check QuickBooks sync for the Vendor Missing PO.
-2. Provide a vendor and part number and re-check.</t>
+          <t>1. Use / receive a genuinely inventory-tracked part on a work order and complete it.
+2. Open that part's Part History (Parts &gt; Inventory, the clock icon on the part row).</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>1. While vendor/PN are missing, the PO is excluded from QuickBooks.
-2. Once both are provided, it becomes eligible for QuickBooks.</t>
+          <t>1. For a part that is genuinely inventory-tracked, its Part History is preserved / written.
+2. Simply entering a part number on a previously untracked part is not required to turn it into an inventory-tracked part in v1, so no Part History needs to be created from that entry alone.</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>SV-7701 (§5 / S6-R3)</t>
+          <t>SV-7705 (§5 invariant 3 (rescoped after S10-R2 strike))</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
@@ -9036,7 +9030,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+          <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -9051,207 +9045,66 @@
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
-2. A work order has a part with no cost recorded at completion.</t>
+2. A Part Sale exists (or can be created) to which a vendor part can be added.</t>
         </is>
       </c>
       <c r="F178" s="2" t="inlineStr">
-        <is>
-          <t>1. Complete the work order.
-2. Check the resulting cost/margin figures that flow to QuickBooks.</t>
-        </is>
-      </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.
-2. For vendorless / no-part-number parts the mandatory sell price is captured at add time behind the See Financial Data gate, so a completing user has a sell figure and $0-cost margins are avoided.</t>
-        </is>
-      </c>
-      <c r="H178" s="2" t="inlineStr">
-        <is>
-          <t>§8 (cost at completion)</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A completed work order is ready to invoice.</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>1. Create the invoice.
-2. Check for the Journal Entry / Inventory sync to QuickBooks.</t>
-        </is>
-      </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>1. The Journal Entry / Inventory sync to QuickBooks fires on invoice creation.
-2. This sync is not dependent on a PO existing.</t>
-        </is>
-      </c>
-      <c r="H179" s="2" t="inlineStr">
-        <is>
-          <t>§5 (Journal Entry / Inventory → QBO)</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
-        <is>
-          <t>Verify Part History is preserved for a part that is genuinely inventory-tracked</t>
-        </is>
-      </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="E180" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A genuinely inventory-tracked part exists (an inventory item with stock).</t>
-        </is>
-      </c>
-      <c r="F180" s="2" t="inlineStr">
-        <is>
-          <t>1. Use / receive a genuinely inventory-tracked part on a work order and complete it.
-2. Open that part's Part History (Parts &gt; Inventory, the clock icon on the part row).</t>
-        </is>
-      </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>1. For a part that is genuinely inventory-tracked, its Part History is preserved / written.
-2. Simply entering a part number on a previously untracked part is not required to turn it into an inventory-tracked part in v1, so no Part History needs to be created from that entry alone.</t>
-        </is>
-      </c>
-      <c r="H180" s="2" t="inlineStr">
-        <is>
-          <t>SV-7705 (§5 invariant 3 (rescoped after S10-R2 strike))</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
-        <is>
-          <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
-        </is>
-      </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E181" s="2" t="inlineStr">
-        <is>
-          <t>1. Signed in as Admin.
-2. A Part Sale exists (or can be created) to which a vendor part can be added.</t>
-        </is>
-      </c>
-      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>1. Add a vendor part to the Part Sale so a purchase order is created.
 2. Follow the order's status as it is ordered and then received (same PO/receive pipeline as work orders).
 3. Confirm the part sale itself progresses normally after receiving.</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>1. The part-sale purchase order moves through the normal statuses (requested, then waiting to receive, then received) with no errors.
 2. Receiving the part-sale PO behaves like receiving a work-order PO (same pipeline).
 3. The part sale is not broken by the shared order/status logic.</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>SV-7702, SV-7703 (§8 Part Sales — confirmed (Jul 14) + S7/S8 part-sale AC)</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>Verify resolving the last open line by completing a single line auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Require Review Before Completion is OFF (in the Work Orders settings tab).
 3. A work order is in Approved status with two or more open (not-yet-completed) lines.</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and complete one line at a time using the per-line Complete action.
 2. After completing the first line (while at least one other line is still open), check the work order status.
@@ -9259,314 +9112,314 @@
 4. Check the work order status again.</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>1. While at least one line is still open, the work order stays in Approved.
 2. The moment the last open line is completed, the work order moves to Complete on its own (invoice-ready).
 3. You do not have to click Complete Work Order separately for the work order to reach Complete.</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (a) single line)</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Verify resolving the last open lines in bulk (several at once) auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order is in Approved status with several open lines and nothing left to receive on those lines.</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and select all the open lines.
 2. From the bulk actions menu choose Set line status and set the selected lines to Complete (resolving them all at once).
 3. Check the work order status.</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>1. All selected lines become Complete in one action.
 2. Because that resolves the last open lines, the work order moves to Complete on its own (invoice-ready).
 3. No separate Complete Work Order step is needed.</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (b) bulk)</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>Verify a split that leaves a work order fully resolved auto-completes that work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order has several lines; some are already completed and at least one line is still open.</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and complete all but one line, leaving one line still open (the work order stays Approved).
 2. Select the remaining open line and use the bulk actions menu Split work order to move it to a new work order.
 3. Check the status of the original work order after the split.</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>1. The open line moves to a new work order.
 2. The original work order is now fully resolved (all its remaining lines are complete), so it moves to Complete on its own.
 3. No separate Complete Work Order step is needed on the original work order.</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (c) split)</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a line so the remaining lines are all resolved auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order has some completed lines and one remaining open line.</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order (its other lines are already complete; one line is still open).
 2. Select the open line and use the bulk actions menu Delete lines to remove it.
 3. Check the work order status.</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>1. The open line is removed.
 2. Because the remaining lines are all complete, the work order moves to Complete on its own.
 3. No separate Complete Work Order step is needed.</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (d) delete line)</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>Verify that with Require Review on, resolving the last open line routes the work order to Ready for Review instead of auto-completing</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is ON and saved.
 3. A work order is in Approved status with two or more open lines.</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and complete the lines one at a time (or in bulk).
 2. After the last open line is resolved, check the work order status.
 3. Confirm whether the work order went straight to Complete or to review.</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>1. When the last open line is resolved, the work order moves to Ready for Review (Review) — it does NOT auto-complete.
 2. The work order must be signed off in the review step before it can reach Complete.</t>
         </is>
       </c>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 review ON)</t>
         </is>
       </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>Verify a clock-out that finishes the last line routes the work order to Ready for Review even when Require Review is off</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as a Technician who is clocked into the work on the work order.
 2. Require Review Before Completion is OFF.
 3. The work order has one remaining open line that the technician is working on.</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>1. As the technician, finish the last open line by clocking out of it.
 2. Check the work order status.</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>1. Even though Require Review is off, the work order routes to Ready for Review (not straight to Complete).
 2. This is the one path that does not auto-complete when review is off (a technician may not be allowed to complete a work order).</t>
         </is>
       </c>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R13 clock-out exception)</t>
         </is>
       </c>
-      <c r="I187" s="2" t="inlineStr"/>
-      <c r="J187" s="2" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>Verify the work order status transitions on the backend when the last open line is resolved (auto-Complete when review off, Ready for Review when review on)</t>
         </is>
       </c>
-      <c r="B188" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>API — Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E188" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Approved status with two or more open lines.</t>
         </is>
       </c>
-      <c r="F188" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review off, resolve the last open line and read the work order record.
 2. Turn Require Review on, and on another work order resolve the last open line and read the work order record.</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review off, after the last open line resolves the work order record status becomes Complete (the resolve action returns success).
 2. With Require Review on, after the last open line resolves the work order record status becomes Ready for Review (Review), not Complete.</t>
         </is>
       </c>
-      <c r="H188" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 backend status transition)</t>
         </is>
       </c>
-      <c r="I188" s="2" t="inlineStr"/>
-      <c r="J188" s="2" t="inlineStr"/>
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -2495,17 +2495,17 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>1. Click Complete Work Order.
-2. Observe the screen shown right before the Receive parts / Complete without receiving choice.
-3. Leave the core undecided and try Complete Without Receiving.
-4. Mark the core OK or Not OK on the resolve screen and try again.</t>
+          <t>1. On a work order that has an un-received special-order (vendor) cored part, click Complete Work Order.
+2. Observe the completion wizard steps (Missing Details, Resolve cores, Receive parts &amp; invoice) and open the Resolve cores step.
+3. Leave the core undecided and try to move on with Continue.
+4. Set the core using OK · Returned or Not OK · Keep + Charge, then try Continue again.</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. A separate Resolve cores screen lists the un-received vendor core with its part info, core charge and an OK / Not OK choice, and explains that resolving now keeps the invoice accurate.
-2. While the core is still undecided, completing is blocked.
-3. Once every core is decided (OK or Not OK), Complete Without Receiving works — a decided core no longer blocks completing without receiving (no receive needed first).</t>
+          <t>1. The completion wizard shows a Resolve cores step (before Receive parts &amp; invoice) that lists the un-received vendor core under 'SPECIAL ORDER CORES' with its description, line and core charge, plus OK · Returned / Not OK · Keep + Charge buttons, and the message that resolving now decides whether the core charge is billed (invoice accuracy).
+2. While the core is undecided (shows '0 / 1 resolved'), the Continue button is disabled — completion is blocked.
+3. Once every core is set (shows '1 / 1 resolved'), Continue is enabled and the wizard proceeds — a decided core no longer blocks moving on (no receive needed first).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2746,9 +2746,9 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. A separate, consolidated Resolve cores screen appears, listing EVERY un-received vendor core (both parts).
-2. Each core shows its part info, its core charge and an OK / Not OK choice.
-3. A message explains that resolving now is for invoice accuracy.</t>
+          <t>1. A consolidated Resolve cores step appears under a 'SPECIAL ORDER CORES · N' group, listing every un-received vendor core.
+2. Each core shows its description, line and core charge with OK · Returned / Not OK · Keep + Charge buttons.
+3. The message 'core part can now be resolved — mark whether each old unit was returned. This decides whether the core charge is billed.' explains the resolution is for invoice accuracy.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3074,16 +3074,16 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>1. POST /api/work-orders/{id}/pre-resolve-cores with the core decision (ok / not_ok).
-2. Re-read the work order's lines / receive-view read models.
-3. Inspect for side-effect records (work-order part, statement item, vendor return).</t>
+          <t>1. POST /api/work-orders/{id}/pre-resolve-cores with body {cores:[{partRequestId, isCoreOk}]} (isCoreOk true = OK/Returned, false = Not OK).
+2. Re-read the work order lines read model and check the core part request's core_resolution and the pending-core count.
+3. Inspect for side-effect records (work-order part, statement item, vendor return, order).</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The request succeeds (2xx) and core_resolution is persisted on the core work_order_part_request (ok | not_ok; NULL = undecided).
-2. NO WorkOrderPart, statement item, or vendor return is created at this point.
-3. cores_pending reflects only undecided (NULL) cores after the call.</t>
+          <t>1. The request succeeds (201) returning {data:{resolvedCount:N}} and core_resolution is persisted on the core part request (ok | not_ok; NULL = undecided; isCoreOk cannot be null).
+2. NO WorkOrderPart, statement item, vendor return or order is created — part request stays authorized_to_order with quantity_remaining and total_core_charge unchanged.
+3. cores_pending reflects only undecided (NULL) cores after the call (decided cores drop out).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -7669,9 +7669,9 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can view and modify the Work Order settings page.
-2. A role without App Settings cannot open or change the Work Order settings.
-3. The backend rejects a Work Order settings save attempted by a role that lacks App Settings.</t>
+          <t>1. Only a role with the App Settings permission (system defaults Admin, Service Manager and Office) can open and change the Work Order settings page.
+2. A role without App Settings cannot reach the Work Order settings page (it is redirected away) and so cannot change those settings from the screen.
+3. A role that cannot open the Work Order settings page cannot save changes to it.</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J185"/>
+  <dimension ref="A1:J187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7759,14 +7759,15 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>1. For each role, attempt to reach and use Bulk Receive.
-2. Record the outcomes.</t>
+          <t>1. For each role, attempt to reach and use Bulk Receive by BOTH entry points: (a) the per-purchase-order Receive button on the Purchase Orders list, and (b) multi-selecting purchase orders with the checkboxes and using 'Receive Selected'.
+2. Where a receive screen opens, attempt to actually complete the receive (enter invoice details and submit).
+3. Record the outcomes for each role and each entry point.</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
-2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot receive.
+          <t>1. Roles with Vendor &amp; Order Mgmt: Create &amp; Edit plus See Financial Data can reach and use Bulk Receive by both entry points: Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager and Parts Tech.
+2. Office (Vendor &amp; Order Mgmt: View only) can open the Bulk Receive page but cannot complete a receive by any path — neither the per-purchase-order Receive button nor the multi-select 'Receive Selected' route may lead to a usable receive.
 3. Sales Rep and Time Clock cannot reach Bulk Receive.</t>
         </is>
       </c>
@@ -8121,71 +8122,168 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>Verify a Vendor &amp; Order Management View-only user cannot receive purchase orders by any path on the Bulk Receive screen</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>1. A user whose role has Vendor &amp; Order Management set to View only exists (for example, Office).
+2. At least one purchase order that can be received exists on the Purchase Orders list.</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign in as the View-only user and open the Purchase Orders list.
+2. Confirm no per-purchase-order Receive button is shown on the list.
+3. Tick the checkboxes to multi-select one or more purchase orders, then use 'Receive Selected'.
+4. If a receive screen opens, try to complete the receive (enter the invoice number, date and cost and use Receive All / Receive Parts).</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>1. The View-only user must not be able to reach an editable receive screen or complete a receive by any path — neither the per-purchase-order Receive button nor the multi-select 'Receive Selected' route may lead to a usable receive.
+2. No purchase order is received and no inventory is changed.</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>§9.1 Bulk Receive gate / §9.2 Office footnote-4</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr"/>
+      <c r="J159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Verify a no-access role (Time Clock) cannot edit, cancel or change the vendor of a work order part from the part menu</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Permissions</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>1. A user with a no-access role exists (for example, Time Clock).
+2. A work order with at least one part on a line exists.</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>1. Sign in as the no-access (Time Clock) user and open the work order's parts.
+2. On a part row, open the three-dot (⋮) menu.
+3. Review the actions offered in the menu.</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>1. The part menu must not offer Edit, Cancel or Change Vendor for a no-access user (only Return may appear).
+2. The actions being hidden in the interface is the pass condition.</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>§9.2 Time Clock part-actions</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr"/>
+      <c r="J160" s="2" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
           <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Mileage is ON and the work order has no mileage.</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave mileage empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until mileage is entered.</t>
         </is>
       </c>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>SV-7697, SV-7698, SV-7699 (S2-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I159" s="2" t="inlineStr"/>
-      <c r="J159" s="2" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="I161" s="2" t="inlineStr"/>
+      <c r="J161" s="2" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. VIN is required for this org's completion and the work order has no VIN.
@@ -8193,196 +8291,196 @@
 4. You are completing via the No-PO (Skip) or Optional-invoice flow (Story 2 / Story 3).</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>1. Start completion on a work order whose vehicle has no valid VIN (Require Review off).
 2. Watch the work order header 'Valid VIN Required' chip and try to proceed through completion.</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr">
         <is>
           <t>1. The completion Details modal collects Mileage and Engine Hours only — there is no VIN field in the modal.
 2. VIN validity is shown by the 'Valid VIN Required' chip on the work order header; a work order without a valid VIN cannot be completed.
 3. For a review-on work order the VIN is captured later by the reviewer in the Mark Reviewed dialog, not at completion.</t>
         </is>
       </c>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699, SV-7710 (S15-R2 / S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="I162" s="2" t="inlineStr"/>
+      <c r="J162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Engine Hours is ON and the work order has no engine hours.</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>1. Start completion.
 2. Leave engine hours empty and try to proceed.</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr">
         <is>
           <t>1. Completion is blocked until engine hours are entered.</t>
         </is>
       </c>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R3)</t>
         </is>
       </c>
-      <c r="I161" s="2" t="inlineStr"/>
-      <c r="J161" s="2" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="I163" s="2" t="inlineStr"/>
+      <c r="J163" s="2" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The tech-story modal is open on a line.</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>1. Leave the story textarea empty.
 2. Check the Next/Continue button.
 3. Type any text and check again.</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr">
         <is>
           <t>1. With the textarea empty, Next/Continue is disabled.
 2. After typing text, Next/Continue becomes enabled.</t>
         </is>
       </c>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>SV-7876 (TS-R4)</t>
         </is>
       </c>
-      <c r="I162" s="2" t="inlineStr"/>
-      <c r="J162" s="2" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="I164" s="2" t="inlineStr"/>
+      <c r="J164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Vendor Invoice Number is ON and a part is being received.</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>1. On the receive surface, leave the vendor invoice number empty.
 2. Attempt to receive.</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked without a vendor invoice number.
 2. Once an invoice number is entered, receiving is allowed.</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S3-R3 / S4-R5 / §4)</t>
         </is>
       </c>
-      <c r="I163" s="2" t="inlineStr"/>
-      <c r="J163" s="2" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr"/>
+      <c r="J165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendor-missing part is on a receive surface.</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>1. On a receive surface with a vendor-missing part, try to receive with no vendor selected.
 2. Select a vendor but leave the part number empty and try to receive.
@@ -8390,7 +8488,7 @@
 4. Provide vendor, part number and cost / sell price, then receive.</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>1. Receiving is blocked while no vendor is selected.
 2. Receiving is blocked while the part number is empty.
@@ -8398,713 +8496,713 @@
 4. Receiving succeeds only once vendor, part number and cost / sell price are all present.</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>SV-7705, SV-7707, SV-7708 (S10 / S12-R2 / S13-R6 / S13-R7)</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr"/>
-      <c r="J164" s="2" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="I166" s="2" t="inlineStr"/>
+      <c r="J166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. The Mark Reviewed dialog is open on a WO with no VIN on the asset.</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>1. Clear the VIN field.
 2. Check the Confirm Review button.
 3. Enter a VIN and check again.</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr">
         <is>
           <t>1. Confirm Review is disabled while VIN is empty.
 2. Confirm Review enables after a VIN is entered.</t>
         </is>
       </c>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (R7)</t>
         </is>
       </c>
-      <c r="I165" s="2" t="inlineStr"/>
-      <c r="J165" s="2" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="I167" s="2" t="inlineStr"/>
+      <c r="J167" s="2" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part-bearing work order had completion started and cancelled once.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>1. Cancel the first completion attempt.
 2. Start and complete again.
 3. Inspect the POs.</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr">
         <is>
           <t>1. No duplicate POs are created on the second attempt.</t>
         </is>
       </c>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>SV-7698 (S3-R9 (idempotency))</t>
         </is>
       </c>
-      <c r="I166" s="2" t="inlineStr"/>
-      <c r="J166" s="2" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="I168" s="2" t="inlineStr"/>
+      <c r="J168" s="2" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A part on an invoiced/paid work order is on a receive surface.</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>1. Open the receive surface for the invoiced/paid WO part.
 2. Try to edit the sell field.
 3. Hover the lock icon.</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>1. The sell field is locked (not editable).
 2. A lock icon and tooltip 'Locked — this part is already invoiced or paid' are shown.
 3. Only cost remains editable.</t>
         </is>
       </c>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t>SV-7703 (S8-R7 / §4 field locking)</t>
         </is>
       </c>
-      <c r="I167" s="2" t="inlineStr"/>
-      <c r="J167" s="2" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="I169" s="2" t="inlineStr"/>
+      <c r="J169" s="2" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Two POs for the same vendor are being received.</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>1. Enter the same invoice number on both POs.
 2. Receive both.</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr">
         <is>
           <t>1. The reused invoice number is accepted (uniqueness is relaxed).
 2. Both POs receive successfully.</t>
         </is>
       </c>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>SV-7704 (S9-R3 / §4 (uniqueness relaxed))</t>
         </is>
       </c>
-      <c r="I168" s="2" t="inlineStr"/>
-      <c r="J168" s="2" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="I170" s="2" t="inlineStr"/>
+      <c r="J170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>Verify an unapproved line disables the Complete Work Order button with a tooltip (regardless of the Require Vendor Invoice Number setting)</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Auto-approve Lines is OFF so a newly added line lands in Needs Approval.
 3. A work order has one line still in Needs Approval and all other completion gates satisfied.</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>1. With Require Vendor Invoice Number ON, open a work order that has one line still in Needs Approval; look at the Complete Work Order button, then hover it.
 2. Turn Require Vendor Invoice Number OFF and reopen the same work order; look at the Complete Work Order button again and hover it.
 3. Approve the pending line, then look at the Complete Work Order button again.</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr">
         <is>
           <t>1. With Require Vendor Invoice Number ON, the Complete Work Order button is disabled; hovering it shows the tooltip 'Every line must be approved or declined in order to complete the work order.' (the tooltip is generic and does not name the specific line).
 2. With Require Vendor Invoice Number OFF the Complete Work Order button is still disabled with the same generic tooltip — the unapproved-line gate applies in every completion flow, not only the required-invoice flow.
 3. Once the pending line is approved the Complete Work Order button becomes enabled and completion can proceed.</t>
         </is>
       </c>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t>SV-7698, SV-7699 (S4-R8 / S3-R9 / Key Decision (line approval))</t>
         </is>
       </c>
-      <c r="I169" s="2" t="inlineStr"/>
-      <c r="J169" s="2" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="I171" s="2" t="inlineStr"/>
+      <c r="J171" s="2" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has an in-stock inventory part; its on-hand quantity is noted.</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order via the simple (skip) path.
 2. Check the part's on-hand quantity and Part History.</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr">
         <is>
           <t>1. The in-stock part's on-hand quantity decrements.
 2. A Part History entry is written.
 3. The skip path's status setter does not bypass inventory movement / Part History / catalog / delivery.</t>
         </is>
       </c>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 1</t>
         </is>
       </c>
-      <c r="I170" s="2" t="inlineStr"/>
-      <c r="J170" s="2" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="I172" s="2" t="inlineStr"/>
+      <c r="J172" s="2" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create Purchase Orders is OFF.
 3. A work order with a vendor/found part exists.</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order with Create POs OFF.
 2. Check for any PO, vendor bill, AP sync.
 3. Check for any catalog/inventory sync of the vendor/found part.</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr">
         <is>
           <t>1. No purchase order, vendor bill or accounts-payable sync is produced.
 2. No catalog or inventory sync happens (the part is received at request time only).</t>
         </is>
       </c>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>§5 / §4 (Create POs OFF)</t>
         </is>
       </c>
-      <c r="I171" s="2" t="inlineStr"/>
-      <c r="J171" s="2" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="I173" s="2" t="inlineStr"/>
+      <c r="J173" s="2" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Create POs is on and a work order has a receivable vendor part.</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>1. Receive the part via Accept Delivery.
 2. Check that a Delivery, then a Vendor Bill, then a QuickBooks sync occur.
 3. Repeat via the Bulk Receive surface (once built) and confirm it also syncs.</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr">
         <is>
           <t>1. Receiving creates a Delivery, then a Vendor Bill, then syncs to QuickBooks.
 2. Both receive surfaces sync the vendor bill (only complete-simple bypasses this).</t>
         </is>
       </c>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>§5 invariant 2</t>
         </is>
       </c>
-      <c r="I172" s="2" t="inlineStr"/>
-      <c r="J172" s="2" t="inlineStr"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="I174" s="2" t="inlineStr"/>
+      <c r="J174" s="2" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A vendorless / no-PN part exists on a work order.</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>1. Before adding a vendor/PN, check inventory and Part History for the part.
 2. Add a vendor and PN, then re-check.</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr">
         <is>
           <t>1. Before a vendor/PN, there is zero inventory interaction (no item, no history).
 2. After a vendor and PN are added, normal inventory handling applies.</t>
         </is>
       </c>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t>§5 (vendorless/no-PN)</t>
         </is>
       </c>
-      <c r="I173" s="2" t="inlineStr"/>
-      <c r="J173" s="2" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="I175" s="2" t="inlineStr"/>
+      <c r="J175" s="2" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Vendor Missing PO exists.</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>1. Check QuickBooks sync for the Vendor Missing PO.
 2. Provide a vendor and part number and re-check.</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr">
         <is>
           <t>1. While vendor/PN are missing, the PO is excluded from QuickBooks.
 2. Once both are provided, it becomes eligible for QuickBooks.</t>
         </is>
       </c>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>SV-7701 (§5 / S6-R3)</t>
         </is>
       </c>
-      <c r="I174" s="2" t="inlineStr"/>
-      <c r="J174" s="2" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="I176" s="2" t="inlineStr"/>
+      <c r="J176" s="2" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order has a part with no cost recorded at completion.</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>1. Complete the work order.
 2. Check the resulting cost/margin figures that flow to QuickBooks.</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr">
         <is>
           <t>1. The cost and margin values sent to QuickBooks at completion are recorded and checked for any $0-cost margins.
 2. For vendorless / no-part-number parts the mandatory sell price is captured at add time behind the See Financial Data gate, so a completing user has a sell figure and $0-cost margins are avoided.</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>§8 (cost at completion)</t>
         </is>
       </c>
-      <c r="I175" s="2" t="inlineStr"/>
-      <c r="J175" s="2" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="I177" s="2" t="inlineStr"/>
+      <c r="J177" s="2" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A completed work order is ready to invoice.</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>1. Create the invoice.
 2. Check for the Journal Entry / Inventory sync to QuickBooks.</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>1. The Journal Entry / Inventory sync to QuickBooks fires on invoice creation.
 2. This sync is not dependent on a PO existing.</t>
         </is>
       </c>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>§5 (Journal Entry / Inventory → QBO)</t>
         </is>
       </c>
-      <c r="I176" s="2" t="inlineStr"/>
-      <c r="J176" s="2" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr"/>
+      <c r="J178" s="2" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>Verify Part History is preserved for a part that is genuinely inventory-tracked</t>
         </is>
       </c>
-      <c r="B177" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E177" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A genuinely inventory-tracked part exists (an inventory item with stock).</t>
         </is>
       </c>
-      <c r="F177" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>1. Use / receive a genuinely inventory-tracked part on a work order and complete it.
 2. Open that part's Part History (Parts &gt; Inventory, the clock icon on the part row).</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr">
         <is>
           <t>1. For a part that is genuinely inventory-tracked, its Part History is preserved / written.
 2. Simply entering a part number on a previously untracked part is not required to turn it into an inventory-tracked part in v1, so no Part History needs to be created from that entry alone.</t>
         </is>
       </c>
-      <c r="H177" s="2" t="inlineStr">
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>SV-7705 (§5 invariant 3 (rescoped after S10-R2 strike))</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr"/>
-      <c r="J177" s="2" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="I179" s="2" t="inlineStr"/>
+      <c r="J179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>Verify part-sale order status transitions are not regressed by the shared order/status logic (requested to waiting-to-receive to received)</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A Part Sale exists (or can be created) to which a vendor part can be added.</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>1. Add a vendor part to the Part Sale so a purchase order is created.
 2. Follow the order's status as it is ordered and then received (same PO/receive pipeline as work orders).
 3. Confirm the part sale itself progresses normally after receiving.</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr">
         <is>
           <t>1. The part-sale purchase order moves through the normal statuses (requested, then waiting to receive, then received) with no errors.
 2. Receiving the part-sale PO behaves like receiving a work-order PO (same pipeline).
 3. The part sale is not broken by the shared order/status logic.</t>
         </is>
       </c>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>SV-7702, SV-7703 (§8 Part Sales — confirmed (Jul 14) + S7/S8 part-sale AC)</t>
         </is>
       </c>
-      <c r="I178" s="2" t="inlineStr"/>
-      <c r="J178" s="2" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="I180" s="2" t="inlineStr"/>
+      <c r="J180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>Verify resolving the last open line by completing a single line auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin at https://sv7301.qa.shopview.com.
 2. Require Review Before Completion is OFF (in the Work Orders settings tab).
 3. A work order is in Approved status with two or more open (not-yet-completed) lines.</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and complete one line at a time using the per-line Complete action.
 2. After completing the first line (while at least one other line is still open), check the work order status.
@@ -9112,314 +9210,314 @@
 4. Check the work order status again.</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr">
         <is>
           <t>1. While at least one line is still open, the work order stays in Approved.
 2. The moment the last open line is completed, the work order moves to Complete on its own (invoice-ready).
 3. You do not have to click Complete Work Order separately for the work order to reach Complete.</t>
         </is>
       </c>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (a) single line)</t>
         </is>
       </c>
-      <c r="I179" s="2" t="inlineStr"/>
-      <c r="J179" s="2" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="I181" s="2" t="inlineStr"/>
+      <c r="J181" s="2" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>Verify resolving the last open lines in bulk (several at once) auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order is in Approved status with several open lines and nothing left to receive on those lines.</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and select all the open lines.
 2. From the bulk actions menu choose Set line status and set the selected lines to Complete (resolving them all at once).
 3. Check the work order status.</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr">
         <is>
           <t>1. All selected lines become Complete in one action.
 2. Because that resolves the last open lines, the work order moves to Complete on its own (invoice-ready).
 3. No separate Complete Work Order step is needed.</t>
         </is>
       </c>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (b) bulk)</t>
         </is>
       </c>
-      <c r="I180" s="2" t="inlineStr"/>
-      <c r="J180" s="2" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="I182" s="2" t="inlineStr"/>
+      <c r="J182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>Verify a split that leaves a work order fully resolved auto-completes that work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order has several lines; some are already completed and at least one line is still open.</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and complete all but one line, leaving one line still open (the work order stays Approved).
 2. Select the remaining open line and use the bulk actions menu Split work order to move it to a new work order.
 3. Check the status of the original work order after the split.</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>1. The open line moves to a new work order.
 2. The original work order is now fully resolved (all its remaining lines are complete), so it moves to Complete on its own.
 3. No separate Complete Work Order step is needed on the original work order.</t>
         </is>
       </c>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (c) split)</t>
         </is>
       </c>
-      <c r="I181" s="2" t="inlineStr"/>
-      <c r="J181" s="2" t="inlineStr"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="I183" s="2" t="inlineStr"/>
+      <c r="J183" s="2" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>Verify deleting a line so the remaining lines are all resolved auto-completes the work order when Require Review is off</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is OFF.
 3. A work order has some completed lines and one remaining open line.</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order (its other lines are already complete; one line is still open).
 2. Select the open line and use the bulk actions menu Delete lines to remove it.
 3. Check the work order status.</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr">
         <is>
           <t>1. The open line is removed.
 2. Because the remaining lines are all complete, the work order moves to Complete on its own.
 3. No separate Complete Work Order step is needed.</t>
         </is>
       </c>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 (d) delete line)</t>
         </is>
       </c>
-      <c r="I182" s="2" t="inlineStr"/>
-      <c r="J182" s="2" t="inlineStr"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="I184" s="2" t="inlineStr"/>
+      <c r="J184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>Verify that with Require Review on, resolving the last open line routes the work order to Ready for Review instead of auto-completing</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Critical</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. Require Review Before Completion is ON and saved.
 3. A work order is in Approved status with two or more open lines.</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>1. Open the work order and complete the lines one at a time (or in bulk).
 2. After the last open line is resolved, check the work order status.
 3. Confirm whether the work order went straight to Complete or to review.</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr">
         <is>
           <t>1. When the last open line is resolved, the work order moves to Ready for Review (Review) — it does NOT auto-complete.
 2. The work order must be signed off in the review step before it can reach Complete.</t>
         </is>
       </c>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 review ON)</t>
         </is>
       </c>
-      <c r="I183" s="2" t="inlineStr"/>
-      <c r="J183" s="2" t="inlineStr"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="I185" s="2" t="inlineStr"/>
+      <c r="J185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
         <is>
           <t>Verify a clock-out that finishes the last line routes the work order to Ready for Review even when Require Review is off</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E186" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as a Technician who is clocked into the work on the work order.
 2. Require Review Before Completion is OFF.
 3. The work order has one remaining open line that the technician is working on.</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F186" s="2" t="inlineStr">
         <is>
           <t>1. As the technician, finish the last open line by clocking out of it.
 2. Check the work order status.</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr">
+      <c r="G186" s="2" t="inlineStr">
         <is>
           <t>1. Even though Require Review is off, the work order routes to Ready for Review (not straight to Complete).
 2. This is the one path that does not auto-complete when review is off (a technician may not be allowed to complete a work order).</t>
         </is>
       </c>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="H186" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R13 clock-out exception)</t>
         </is>
       </c>
-      <c r="I184" s="2" t="inlineStr"/>
-      <c r="J184" s="2" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="I186" s="2" t="inlineStr"/>
+      <c r="J186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
         <is>
           <t>Verify the work order status transitions on the backend when the last open line is resolved (auto-Complete when review off, Ready for Review when review on)</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
+      <c r="B187" s="2" t="inlineStr">
         <is>
           <t>API — Auto-Complete Trigger (Story 16 R12/R13)</t>
         </is>
       </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E187" s="2" t="inlineStr">
         <is>
           <t>1. Signed in as Admin.
 2. A work order is in Approved status with two or more open lines.</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F187" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review off, resolve the last open line and read the work order record.
 2. Turn Require Review on, and on another work order resolve the last open line and read the work order record.</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
+      <c r="G187" s="2" t="inlineStr">
         <is>
           <t>1. With Require Review off, after the last open line resolves the work order record status becomes Complete (the resolve action returns success).
 2. With Require Review on, after the last open line resolves the work order record status becomes Ready for Review (Review), not Complete.</t>
         </is>
       </c>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="H187" s="2" t="inlineStr">
         <is>
           <t>SV-7870 (S16-R12 backend status transition)</t>
         </is>
       </c>
-      <c r="I185" s="2" t="inlineStr"/>
-      <c r="J185" s="2" t="inlineStr"/>
+      <c r="I187" s="2" t="inlineStr"/>
+      <c r="J187" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/testrail-import/simple-flow-v1-testrail-import.xlsx
+++ b/testrail-import/simple-flow-v1-testrail-import.xlsx
@@ -7907,7 +7907,8 @@
           <t>1. As a role that lacks the mapped permission, confirm the gated setting or action is hidden or unavailable in the app.
 2. As that same role, try the same setting change directly through the API (bypassing the app) and note the response.
 3. As a role that lacks the completion or review sign-off permission, try to complete a work order and to sign off a review directly through the API and note the responses.
-4. As a role that only has Work Orders: Create &amp; Edit, try to receive parts onto a work order through the API and note the response.</t>
+4. As a role that only has Work Orders: Create &amp; Edit, try to receive parts onto a work order through the API and note the response.
+5. For each of the eleven roles in turn, call the Bulk Receive 'accept' action directly through the API (the 'Receive Selected' / Bulk Receive submit) and note the response for each role.</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
@@ -7915,7 +7916,8 @@
           <t>1. In the app, a role without the mapped permission does not see or cannot use the gated setting or action (this is the v1 pass criterion).
 2. The Work Order settings save is also blocked at the backend: the unauthorized API request is rejected with HTTP 403.
 3. Work order completion and review sign-off are NOT blocked at the backend today: a direct API call from a role lacking the permission still succeeds (HTTP 200). This still passes v1 on the app-level restriction, but the backend gap is a known issue to fix later — note it as 'app blocks / backend allows'.
-4. Because several work-order permissions share the same backend check, any role with Work Orders: Create &amp; Edit can receive parts onto a work order through the API.</t>
+4. Because several work-order permissions share the same backend check, any role with Work Orders: Create &amp; Edit can receive parts onto a work order through the API.
+5. Unlike work order completion and review sign-off, the Bulk Receive 'accept' action IS enforced at the backend per role: the direct API call is rejected with HTTP 403 for the four roles that should not have it — Office, Sales Representative, Technician, Time Clock — and is allowed for the seven roles that should (Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager, Parts Technician). This matches the permission matrix exactly, so Bulk Receive is genuinely backend-enforced.</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8205,7 +8207,8 @@
       <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The part menu must not offer Edit, Cancel or Change Vendor for a no-access user (only Return may appear).
-2. The actions being hidden in the interface is the pass condition.</t>
+2. The actions being hidden in the interface is the pass condition.
+3. QA note: for a no-access role, editing a part or changing its vendor is hidden on screen but can still be done through the API. Per the product ruling (2026-07-24), this front-end-only gating is accepted — it counts as a PASS, not a defect. (The same applies to adding or deleting a work-order part, which the backend also does not block for any role.)</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
